--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.47</v>
+        <v>4.23</v>
       </c>
       <c r="F14" t="n">
-        <v>11.66</v>
+        <v>11.57</v>
       </c>
       <c r="G14" t="n">
-        <v>18.4</v>
+        <v>14.6</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>200.24</v>
+        <v>74.39</v>
       </c>
       <c r="K14" t="n">
-        <v>-211.46</v>
+        <v>18.8</v>
       </c>
       <c r="L14" t="n">
-        <v>291.23</v>
+        <v>76.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:17:30</t>
+          <t>07:17:41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.36</v>
+        <v>4.21</v>
       </c>
       <c r="F15" t="n">
-        <v>11.55</v>
+        <v>11.67</v>
       </c>
       <c r="G15" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>233.68</v>
       </c>
       <c r="K15" t="n">
-        <v>-86.06999999999999</v>
+        <v>-40.9</v>
       </c>
       <c r="L15" t="n">
-        <v>86.13</v>
+        <v>237.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:19:42</t>
+          <t>07:19:25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.68</v>
+        <v>3.91</v>
       </c>
       <c r="F16" t="n">
-        <v>10.43</v>
+        <v>11.65</v>
       </c>
       <c r="G16" t="n">
-        <v>15.7</v>
+        <v>7.3</v>
       </c>
       <c r="H16" t="n">
-        <v>94.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>206.72</v>
+        <v>-136.1</v>
       </c>
       <c r="K16" t="n">
-        <v>148.04</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>254.27</v>
+        <v>136.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:24:10</t>
+          <t>07:23:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.32</v>
+        <v>3.99</v>
       </c>
       <c r="F17" t="n">
-        <v>11.62</v>
+        <v>11.69</v>
       </c>
       <c r="G17" t="n">
-        <v>18.4</v>
+        <v>27.3</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-40.37</v>
+        <v>49.66</v>
       </c>
       <c r="K17" t="n">
-        <v>13.26</v>
+        <v>-121.34</v>
       </c>
       <c r="L17" t="n">
-        <v>42.49</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:25:32</t>
+          <t>07:24:30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="F18" t="n">
-        <v>11.58</v>
+        <v>11.43</v>
       </c>
       <c r="G18" t="n">
-        <v>12.3</v>
+        <v>17.8</v>
       </c>
       <c r="H18" t="n">
         <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-101.94</v>
+        <v>-106.79</v>
       </c>
       <c r="K18" t="n">
-        <v>53.46</v>
+        <v>-75.45</v>
       </c>
       <c r="L18" t="n">
-        <v>115.1</v>
+        <v>130.76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:26:47</t>
+          <t>07:26:19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
       <c r="F19" t="n">
-        <v>11.32</v>
+        <v>10.76</v>
       </c>
       <c r="G19" t="n">
-        <v>25.2</v>
+        <v>17.5</v>
       </c>
       <c r="H19" t="n">
-        <v>96.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>265.78</v>
+        <v>226.5</v>
       </c>
       <c r="K19" t="n">
-        <v>388.97</v>
+        <v>188.95</v>
       </c>
       <c r="L19" t="n">
-        <v>471.1</v>
+        <v>294.96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:30:58</t>
+          <t>07:30:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.47</v>
+        <v>4.6</v>
       </c>
       <c r="F20" t="n">
-        <v>10.73</v>
+        <v>11.69</v>
       </c>
       <c r="G20" t="n">
-        <v>12.4</v>
+        <v>22.2</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>126.69</v>
+        <v>-127.96</v>
       </c>
       <c r="K20" t="n">
-        <v>129.95</v>
+        <v>-245</v>
       </c>
       <c r="L20" t="n">
-        <v>181.48</v>
+        <v>276.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:32:00</t>
+          <t>07:32:13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.28</v>
+        <v>4.8</v>
       </c>
       <c r="F21" t="n">
-        <v>11.85</v>
+        <v>11.02</v>
       </c>
       <c r="G21" t="n">
-        <v>33.1</v>
+        <v>28.3</v>
       </c>
       <c r="H21" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-372.78</v>
+        <v>-309.87</v>
       </c>
       <c r="K21" t="n">
-        <v>-13.69</v>
+        <v>321.8</v>
       </c>
       <c r="L21" t="n">
-        <v>373.04</v>
+        <v>446.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:33:05</t>
+          <t>07:34:07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.79</v>
+        <v>3.58</v>
       </c>
       <c r="F22" t="n">
-        <v>10.92</v>
+        <v>11.57</v>
       </c>
       <c r="G22" t="n">
-        <v>8.6</v>
+        <v>25.1</v>
       </c>
       <c r="H22" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-287.11</v>
+        <v>-141.79</v>
       </c>
       <c r="K22" t="n">
-        <v>-153.03</v>
+        <v>289.55</v>
       </c>
       <c r="L22" t="n">
-        <v>325.35</v>
+        <v>322.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:37:35</t>
+          <t>07:38:55</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.86</v>
+        <v>4.4</v>
       </c>
       <c r="F23" t="n">
-        <v>10.96</v>
+        <v>11.5</v>
       </c>
       <c r="G23" t="n">
-        <v>28.2</v>
+        <v>25.6</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>244.21</v>
+        <v>-414.12</v>
       </c>
       <c r="K23" t="n">
-        <v>544.37</v>
+        <v>339.11</v>
       </c>
       <c r="L23" t="n">
-        <v>596.64</v>
+        <v>535.25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:39:12</t>
+          <t>07:41:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.03</v>
+        <v>4.41</v>
       </c>
       <c r="F24" t="n">
-        <v>11.2</v>
+        <v>11.51</v>
       </c>
       <c r="G24" t="n">
-        <v>14.6</v>
+        <v>21.5</v>
       </c>
       <c r="H24" t="n">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.19</v>
+        <v>258.04</v>
       </c>
       <c r="K24" t="n">
-        <v>380.72</v>
+        <v>157.71</v>
       </c>
       <c r="L24" t="n">
-        <v>380.76</v>
+        <v>302.42</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:39:58</t>
+          <t>07:43:33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.02</v>
+        <v>4.19</v>
       </c>
       <c r="F25" t="n">
-        <v>11.74</v>
+        <v>11.58</v>
       </c>
       <c r="G25" t="n">
-        <v>23.2</v>
+        <v>18.8</v>
       </c>
       <c r="H25" t="n">
         <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>450.6</v>
+        <v>-87.73</v>
       </c>
       <c r="K25" t="n">
-        <v>-240.21</v>
+        <v>250.83</v>
       </c>
       <c r="L25" t="n">
-        <v>510.63</v>
+        <v>265.73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:43:58</t>
+          <t>07:48:02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.18</v>
+        <v>4.38</v>
       </c>
       <c r="F26" t="n">
-        <v>11.76</v>
+        <v>11.23</v>
       </c>
       <c r="G26" t="n">
-        <v>23.6</v>
+        <v>25.2</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>153.3</v>
+        <v>-362.02</v>
       </c>
       <c r="K26" t="n">
-        <v>-164.26</v>
+        <v>81.34</v>
       </c>
       <c r="L26" t="n">
-        <v>224.69</v>
+        <v>371.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:46:05</t>
+          <t>07:49:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.03</v>
+        <v>4.14</v>
       </c>
       <c r="F27" t="n">
-        <v>10.87</v>
+        <v>11.25</v>
       </c>
       <c r="G27" t="n">
-        <v>13.7</v>
+        <v>24.3</v>
       </c>
       <c r="H27" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-623.84</v>
+        <v>-273.01</v>
       </c>
       <c r="K27" t="n">
-        <v>-197.49</v>
+        <v>-504.97</v>
       </c>
       <c r="L27" t="n">
-        <v>654.35</v>
+        <v>574.04</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:47:25</t>
+          <t>07:50:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.64</v>
+        <v>4.61</v>
       </c>
       <c r="F28" t="n">
-        <v>10.55</v>
+        <v>10.83</v>
       </c>
       <c r="G28" t="n">
-        <v>25.6</v>
+        <v>20.3</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>7.94</v>
+        <v>-660.37</v>
       </c>
       <c r="K28" t="n">
-        <v>220.91</v>
+        <v>252.94</v>
       </c>
       <c r="L28" t="n">
-        <v>221.06</v>
+        <v>707.16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:55:42</t>
+          <t>08:00:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.29</v>
+        <v>3.87</v>
       </c>
       <c r="F29" t="n">
-        <v>11.83</v>
+        <v>11.65</v>
       </c>
       <c r="G29" t="n">
-        <v>24.3</v>
+        <v>23.6</v>
       </c>
       <c r="H29" t="n">
-        <v>97.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-128.25</v>
+        <v>-104.91</v>
       </c>
       <c r="K29" t="n">
-        <v>231.21</v>
+        <v>-0.61</v>
       </c>
       <c r="L29" t="n">
-        <v>264.39</v>
+        <v>104.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:58:35</t>
+          <t>08:02:41</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.97</v>
+        <v>4.75</v>
       </c>
       <c r="F30" t="n">
-        <v>11.45</v>
+        <v>11.52</v>
       </c>
       <c r="G30" t="n">
-        <v>13.8</v>
+        <v>16.1</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>192.18</v>
+        <v>101.46</v>
       </c>
       <c r="K30" t="n">
-        <v>20.94</v>
+        <v>-14.41</v>
       </c>
       <c r="L30" t="n">
-        <v>193.32</v>
+        <v>102.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:59:30</t>
+          <t>08:04:11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.71</v>
+        <v>4.17</v>
       </c>
       <c r="F31" t="n">
-        <v>12.03</v>
+        <v>11.48</v>
       </c>
       <c r="G31" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>23.4</v>
+        <v>228.23</v>
       </c>
       <c r="K31" t="n">
-        <v>-54.53</v>
+        <v>58.24</v>
       </c>
       <c r="L31" t="n">
-        <v>59.34</v>
+        <v>235.54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:04:13</t>
+          <t>08:09:48</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.56</v>
+        <v>4.44</v>
       </c>
       <c r="F32" t="n">
-        <v>11.43</v>
+        <v>10.79</v>
       </c>
       <c r="G32" t="n">
-        <v>31.6</v>
+        <v>17.3</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.61</v>
+        <v>43.97</v>
       </c>
       <c r="K32" t="n">
-        <v>-273.84</v>
+        <v>-162.2</v>
       </c>
       <c r="L32" t="n">
-        <v>273.84</v>
+        <v>168.05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:06:01</t>
+          <t>08:12:03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.13</v>
+        <v>4.38</v>
       </c>
       <c r="F33" t="n">
-        <v>10.66</v>
+        <v>10.88</v>
       </c>
       <c r="G33" t="n">
-        <v>27.7</v>
+        <v>29.4</v>
       </c>
       <c r="H33" t="n">
-        <v>91.2</v>
+        <v>99.8</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>84.27</v>
+        <v>-1.39</v>
       </c>
       <c r="K33" t="n">
-        <v>-73.68000000000001</v>
+        <v>137.21</v>
       </c>
       <c r="L33" t="n">
-        <v>111.94</v>
+        <v>137.22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:07:34</t>
+          <t>08:14:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.7</v>
+        <v>4.48</v>
       </c>
       <c r="F34" t="n">
-        <v>11.38</v>
+        <v>11.8</v>
       </c>
       <c r="G34" t="n">
-        <v>28.5</v>
+        <v>15.3</v>
       </c>
       <c r="H34" t="n">
-        <v>99.5</v>
+        <v>95.8</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>26.36</v>
+        <v>-168.78</v>
       </c>
       <c r="K34" t="n">
-        <v>96.53</v>
+        <v>43.75</v>
       </c>
       <c r="L34" t="n">
-        <v>100.06</v>
+        <v>174.36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:12:25</t>
+          <t>08:19:20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.47</v>
+        <v>5.52</v>
       </c>
       <c r="F35" t="n">
-        <v>11.48</v>
+        <v>11.26</v>
       </c>
       <c r="G35" t="n">
-        <v>24.3</v>
+        <v>31</v>
       </c>
       <c r="H35" t="n">
-        <v>99.2</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>65.20999999999999</v>
+        <v>-120.74</v>
       </c>
       <c r="K35" t="n">
-        <v>-151.06</v>
+        <v>171.28</v>
       </c>
       <c r="L35" t="n">
-        <v>164.53</v>
+        <v>209.56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:13:43</t>
+          <t>08:21:39</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.74</v>
+        <v>4.39</v>
       </c>
       <c r="F36" t="n">
-        <v>11.1</v>
+        <v>10.62</v>
       </c>
       <c r="G36" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="H36" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>265.59</v>
+        <v>-130.09</v>
       </c>
       <c r="K36" t="n">
-        <v>17.81</v>
+        <v>-164.94</v>
       </c>
       <c r="L36" t="n">
-        <v>266.19</v>
+        <v>210.07</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:14:37</t>
+          <t>08:23:08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.24</v>
+        <v>4.55</v>
       </c>
       <c r="F37" t="n">
-        <v>11.41</v>
+        <v>11.54</v>
       </c>
       <c r="G37" t="n">
-        <v>10.6</v>
+        <v>19.6</v>
       </c>
       <c r="H37" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>60.03</v>
+        <v>-193.79</v>
       </c>
       <c r="K37" t="n">
-        <v>-165.65</v>
+        <v>362.5</v>
       </c>
       <c r="L37" t="n">
-        <v>176.19</v>
+        <v>411.05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:18:08</t>
+          <t>08:28:14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.64</v>
+        <v>4.46</v>
       </c>
       <c r="F38" t="n">
-        <v>11.49</v>
+        <v>11.04</v>
       </c>
       <c r="G38" t="n">
-        <v>12.8</v>
+        <v>31</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-575.03</v>
+        <v>-274.31</v>
       </c>
       <c r="K38" t="n">
-        <v>-261.84</v>
+        <v>378.94</v>
       </c>
       <c r="L38" t="n">
-        <v>631.84</v>
+        <v>467.81</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:19:26</t>
+          <t>08:29:39</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.84</v>
+        <v>4.39</v>
       </c>
       <c r="F39" t="n">
-        <v>11.16</v>
+        <v>12.4</v>
       </c>
       <c r="G39" t="n">
-        <v>18.3</v>
+        <v>357.1</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>269.6</v>
+        <v>-941.87</v>
       </c>
       <c r="K39" t="n">
-        <v>-131.34</v>
+        <v>148.21</v>
       </c>
       <c r="L39" t="n">
-        <v>299.89</v>
+        <v>953.46</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:20:57</t>
+          <t>08:31:49</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.91</v>
+        <v>4.78</v>
       </c>
       <c r="F40" t="n">
-        <v>12.01</v>
+        <v>11.88</v>
       </c>
       <c r="G40" t="n">
-        <v>17.1</v>
+        <v>19.3</v>
       </c>
       <c r="H40" t="n">
-        <v>98.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="I40" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>598.1900000000001</v>
+        <v>550.15</v>
       </c>
       <c r="K40" t="n">
-        <v>-67.41</v>
+        <v>469.24</v>
       </c>
       <c r="L40" t="n">
-        <v>601.98</v>
+        <v>723.08</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:25:18</t>
+          <t>08:37:05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.17</v>
+        <v>4.47</v>
       </c>
       <c r="F41" t="n">
-        <v>11.7</v>
+        <v>11.61</v>
       </c>
       <c r="G41" t="n">
-        <v>6.5</v>
+        <v>17.7</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>155.52</v>
+        <v>315.3</v>
       </c>
       <c r="K41" t="n">
-        <v>550.1799999999999</v>
+        <v>482.42</v>
       </c>
       <c r="L41" t="n">
-        <v>571.74</v>
+        <v>576.3200000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:27:21</t>
+          <t>08:38:01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.12</v>
+        <v>4.76</v>
       </c>
       <c r="F42" t="n">
-        <v>11.99</v>
+        <v>10.8</v>
       </c>
       <c r="G42" t="n">
-        <v>21.5</v>
+        <v>37.4</v>
       </c>
       <c r="H42" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-32.19</v>
+        <v>858.85</v>
       </c>
       <c r="K42" t="n">
-        <v>485.67</v>
+        <v>-429.97</v>
       </c>
       <c r="L42" t="n">
-        <v>486.74</v>
+        <v>960.47</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:29:33</t>
+          <t>08:40:15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.22</v>
+        <v>4.94</v>
       </c>
       <c r="F43" t="n">
-        <v>12.53</v>
+        <v>11.38</v>
       </c>
       <c r="G43" t="n">
-        <v>5.2</v>
+        <v>17.3</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>143.54</v>
+        <v>628.13</v>
       </c>
       <c r="K43" t="n">
-        <v>401.46</v>
+        <v>54.46</v>
       </c>
       <c r="L43" t="n">
-        <v>426.35</v>
+        <v>630.49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:36:52</t>
+          <t>08:50:14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.89</v>
+        <v>4.46</v>
       </c>
       <c r="F44" t="n">
-        <v>10.74</v>
+        <v>11.21</v>
       </c>
       <c r="G44" t="n">
-        <v>23.2</v>
+        <v>10.9</v>
       </c>
       <c r="H44" t="n">
-        <v>93.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>-94.68000000000001</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-62.71</v>
+        <v>206.03</v>
       </c>
       <c r="L44" t="n">
-        <v>113.57</v>
+        <v>217.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:37:52</t>
+          <t>08:52:06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.27</v>
+        <v>4.72</v>
       </c>
       <c r="F45" t="n">
-        <v>11.31</v>
+        <v>11.37</v>
       </c>
       <c r="G45" t="n">
-        <v>14.7</v>
+        <v>18.6</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>86.18000000000001</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-38.18</v>
+        <v>54.35</v>
       </c>
       <c r="L45" t="n">
-        <v>94.26000000000001</v>
+        <v>109.66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:40:09</t>
+          <t>08:53:23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.77</v>
+        <v>4.58</v>
       </c>
       <c r="F46" t="n">
-        <v>11.08</v>
+        <v>11.23</v>
       </c>
       <c r="G46" t="n">
-        <v>16.2</v>
+        <v>26.3</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I46" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>5.69</v>
+        <v>197.59</v>
       </c>
       <c r="K46" t="n">
-        <v>-169.55</v>
+        <v>-153.43</v>
       </c>
       <c r="L46" t="n">
-        <v>169.65</v>
+        <v>250.16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:44:12</t>
+          <t>08:58:07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.38</v>
+        <v>4.68</v>
       </c>
       <c r="F47" t="n">
-        <v>11.52</v>
+        <v>11.93</v>
       </c>
       <c r="G47" t="n">
-        <v>19</v>
+        <v>22.6</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>159.73</v>
+        <v>-389.49</v>
       </c>
       <c r="K47" t="n">
-        <v>-35.21</v>
+        <v>404.05</v>
       </c>
       <c r="L47" t="n">
-        <v>163.57</v>
+        <v>561.22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:46:34</t>
+          <t>09:00:10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.38</v>
+        <v>4.19</v>
       </c>
       <c r="F48" t="n">
-        <v>12.03</v>
+        <v>11.43</v>
       </c>
       <c r="G48" t="n">
-        <v>28.3</v>
+        <v>23.1</v>
       </c>
       <c r="H48" t="n">
         <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>228.53</v>
+        <v>222.77</v>
       </c>
       <c r="K48" t="n">
-        <v>-326.55</v>
+        <v>1.34</v>
       </c>
       <c r="L48" t="n">
-        <v>398.58</v>
+        <v>222.77</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:47:53</t>
+          <t>09:01:32</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.16</v>
+        <v>4.11</v>
       </c>
       <c r="F49" t="n">
-        <v>12.35</v>
+        <v>12.36</v>
       </c>
       <c r="G49" t="n">
-        <v>25.3</v>
+        <v>24.1</v>
       </c>
       <c r="H49" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>-203.69</v>
+        <v>6.8</v>
       </c>
       <c r="K49" t="n">
-        <v>-72.48</v>
+        <v>141.71</v>
       </c>
       <c r="L49" t="n">
-        <v>216.2</v>
+        <v>141.87</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:52:57</t>
+          <t>09:06:40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.44</v>
+        <v>4.59</v>
       </c>
       <c r="F50" t="n">
-        <v>11.04</v>
+        <v>11.36</v>
       </c>
       <c r="G50" t="n">
-        <v>23.1</v>
+        <v>18.9</v>
       </c>
       <c r="H50" t="n">
-        <v>99.2</v>
+        <v>88.2</v>
       </c>
       <c r="I50" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>455.43</v>
+        <v>-224.08</v>
       </c>
       <c r="K50" t="n">
-        <v>-168.53</v>
+        <v>270.13</v>
       </c>
       <c r="L50" t="n">
-        <v>485.62</v>
+        <v>350.97</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:54:25</t>
+          <t>09:07:44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.72</v>
+        <v>4.53</v>
       </c>
       <c r="F51" t="n">
-        <v>11.09</v>
+        <v>11.48</v>
       </c>
       <c r="G51" t="n">
-        <v>13.9</v>
+        <v>30.9</v>
       </c>
       <c r="H51" t="n">
         <v>100</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>102.3</v>
+        <v>69.66</v>
       </c>
       <c r="K51" t="n">
-        <v>-258.57</v>
+        <v>-141.42</v>
       </c>
       <c r="L51" t="n">
-        <v>278.07</v>
+        <v>157.64</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:55:20</t>
+          <t>09:08:38</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.23</v>
+        <v>4.66</v>
       </c>
       <c r="F52" t="n">
-        <v>10.81</v>
+        <v>11.08</v>
       </c>
       <c r="G52" t="n">
-        <v>17.5</v>
+        <v>20.4</v>
       </c>
       <c r="H52" t="n">
-        <v>98.7</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>224.53</v>
+        <v>-366.39</v>
       </c>
       <c r="K52" t="n">
-        <v>-806</v>
+        <v>-19.01</v>
       </c>
       <c r="L52" t="n">
-        <v>836.6900000000001</v>
+        <v>366.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:59:49</t>
+          <t>09:14:11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.38</v>
+        <v>4.74</v>
       </c>
       <c r="F53" t="n">
-        <v>11.52</v>
+        <v>11.49</v>
       </c>
       <c r="G53" t="n">
-        <v>11.2</v>
+        <v>21.1</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-709.74</v>
+        <v>-64.5</v>
       </c>
       <c r="K53" t="n">
-        <v>-303.41</v>
+        <v>-118.61</v>
       </c>
       <c r="L53" t="n">
-        <v>771.87</v>
+        <v>135.01</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:01:01</t>
+          <t>09:14:53</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.96</v>
+        <v>5.43</v>
       </c>
       <c r="F54" t="n">
-        <v>12.36</v>
+        <v>11.73</v>
       </c>
       <c r="G54" t="n">
-        <v>14.6</v>
+        <v>359.3</v>
       </c>
       <c r="H54" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>313.57</v>
+        <v>-466.42</v>
       </c>
       <c r="K54" t="n">
-        <v>-24.03</v>
+        <v>-137.74</v>
       </c>
       <c r="L54" t="n">
-        <v>314.49</v>
+        <v>486.34</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:03:41</t>
+          <t>09:16:26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.98</v>
+        <v>4.92</v>
       </c>
       <c r="F55" t="n">
-        <v>11.53</v>
+        <v>11.13</v>
       </c>
       <c r="G55" t="n">
-        <v>17.2</v>
+        <v>34.4</v>
       </c>
       <c r="H55" t="n">
-        <v>97.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>-64.81</v>
+        <v>496.13</v>
       </c>
       <c r="K55" t="n">
-        <v>-254.4</v>
+        <v>362.35</v>
       </c>
       <c r="L55" t="n">
-        <v>262.52</v>
+        <v>614.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:09:43</t>
+          <t>09:22:02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.11</v>
+        <v>4.4</v>
       </c>
       <c r="F56" t="n">
-        <v>11.12</v>
+        <v>10.84</v>
       </c>
       <c r="G56" t="n">
-        <v>36</v>
+        <v>2.5</v>
       </c>
       <c r="H56" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>261.47</v>
+        <v>-72.58</v>
       </c>
       <c r="K56" t="n">
-        <v>-1116.15</v>
+        <v>-175.86</v>
       </c>
       <c r="L56" t="n">
-        <v>1146.37</v>
+        <v>190.25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:11:26</t>
+          <t>09:24:17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.03</v>
+        <v>5.18</v>
       </c>
       <c r="F57" t="n">
-        <v>11.76</v>
+        <v>10.71</v>
       </c>
       <c r="G57" t="n">
-        <v>28.5</v>
+        <v>23.6</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-456.26</v>
+        <v>-830.72</v>
       </c>
       <c r="K57" t="n">
-        <v>-85</v>
+        <v>-42.89</v>
       </c>
       <c r="L57" t="n">
-        <v>464.11</v>
+        <v>831.83</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:13:30</t>
+          <t>09:25:53</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.63</v>
+        <v>5.06</v>
       </c>
       <c r="F58" t="n">
-        <v>10.14</v>
+        <v>11.33</v>
       </c>
       <c r="G58" t="n">
-        <v>9.300000000000001</v>
+        <v>23.8</v>
       </c>
       <c r="H58" t="n">
-        <v>93</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>101.07</v>
+        <v>-13.88</v>
       </c>
       <c r="K58" t="n">
-        <v>-99.68000000000001</v>
+        <v>-1294.42</v>
       </c>
       <c r="L58" t="n">
-        <v>141.96</v>
+        <v>1294.49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:24:27</t>
+          <t>09:37:04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.36</v>
+        <v>5.17</v>
       </c>
       <c r="F59" t="n">
-        <v>11.54</v>
+        <v>11.43</v>
       </c>
       <c r="G59" t="n">
-        <v>20.1</v>
+        <v>8.1</v>
       </c>
       <c r="H59" t="n">
-        <v>96.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-25.04</v>
+        <v>74.41</v>
       </c>
       <c r="K59" t="n">
-        <v>297.5</v>
+        <v>-113.02</v>
       </c>
       <c r="L59" t="n">
-        <v>298.55</v>
+        <v>135.32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:26:23</t>
+          <t>09:38:19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.17</v>
+        <v>5.21</v>
       </c>
       <c r="F60" t="n">
-        <v>11.01</v>
+        <v>11.52</v>
       </c>
       <c r="G60" t="n">
-        <v>39.2</v>
+        <v>18.4</v>
       </c>
       <c r="H60" t="n">
-        <v>98.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>131.53</v>
+        <v>211.1</v>
       </c>
       <c r="K60" t="n">
-        <v>118.13</v>
+        <v>56.45</v>
       </c>
       <c r="L60" t="n">
-        <v>176.79</v>
+        <v>218.52</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:28:06</t>
+          <t>09:39:35</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.81</v>
+        <v>4.88</v>
       </c>
       <c r="F61" t="n">
-        <v>11.99</v>
+        <v>11.84</v>
       </c>
       <c r="G61" t="n">
-        <v>15.6</v>
+        <v>5</v>
       </c>
       <c r="H61" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.880000000000001</v>
+        <v>130.78</v>
       </c>
       <c r="K61" t="n">
-        <v>-243.11</v>
+        <v>-70.34</v>
       </c>
       <c r="L61" t="n">
-        <v>243.31</v>
+        <v>148.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:33:37</t>
+          <t>09:44:45</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.6</v>
+        <v>4.21</v>
       </c>
       <c r="F62" t="n">
-        <v>11.38</v>
+        <v>11.92</v>
       </c>
       <c r="G62" t="n">
-        <v>27.4</v>
+        <v>23.6</v>
       </c>
       <c r="H62" t="n">
-        <v>90.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-146.08</v>
+        <v>-164.08</v>
       </c>
       <c r="K62" t="n">
-        <v>-93.06999999999999</v>
+        <v>-117.18</v>
       </c>
       <c r="L62" t="n">
-        <v>173.21</v>
+        <v>201.62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:34:52</t>
+          <t>09:46:23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="F63" t="n">
-        <v>11.4</v>
+        <v>11.55</v>
       </c>
       <c r="G63" t="n">
-        <v>41.5</v>
+        <v>36.6</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>-156.01</v>
+        <v>89.66</v>
       </c>
       <c r="K63" t="n">
-        <v>74.34</v>
+        <v>217.86</v>
       </c>
       <c r="L63" t="n">
-        <v>172.81</v>
+        <v>235.59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:36:01</t>
+          <t>09:48:45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.92</v>
+        <v>4.65</v>
       </c>
       <c r="F64" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="G64" t="n">
-        <v>21.4</v>
+        <v>13.3</v>
       </c>
       <c r="H64" t="n">
-        <v>98.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-156.99</v>
+        <v>19.51</v>
       </c>
       <c r="K64" t="n">
-        <v>512.5599999999999</v>
+        <v>186.21</v>
       </c>
       <c r="L64" t="n">
-        <v>536.0599999999999</v>
+        <v>187.23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:41:43</t>
+          <t>09:53:03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.91</v>
+        <v>5.37</v>
       </c>
       <c r="F65" t="n">
-        <v>10.96</v>
+        <v>11.91</v>
       </c>
       <c r="G65" t="n">
-        <v>17.5</v>
+        <v>27.7</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>403.4</v>
+        <v>477.86</v>
       </c>
       <c r="K65" t="n">
-        <v>137.69</v>
+        <v>-152.87</v>
       </c>
       <c r="L65" t="n">
-        <v>426.25</v>
+        <v>501.71</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:44:04</t>
+          <t>09:55:24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.44</v>
+        <v>5.13</v>
       </c>
       <c r="F66" t="n">
-        <v>11.27</v>
+        <v>11</v>
       </c>
       <c r="G66" t="n">
-        <v>23.7</v>
+        <v>17.8</v>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-130.91</v>
+        <v>-68.92</v>
       </c>
       <c r="K66" t="n">
-        <v>125.09</v>
+        <v>-331.24</v>
       </c>
       <c r="L66" t="n">
-        <v>181.06</v>
+        <v>338.34</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:46:16</t>
+          <t>09:56:51</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>5.03</v>
+        <v>4.54</v>
       </c>
       <c r="F67" t="n">
-        <v>10.73</v>
+        <v>11.79</v>
       </c>
       <c r="G67" t="n">
-        <v>17.2</v>
+        <v>13.8</v>
       </c>
       <c r="H67" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-198.61</v>
+        <v>-93.09999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>-531.79</v>
+        <v>44.39</v>
       </c>
       <c r="L67" t="n">
-        <v>567.67</v>
+        <v>103.14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:50:48</t>
+          <t>10:00:08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.72</v>
+        <v>5.44</v>
       </c>
       <c r="F68" t="n">
-        <v>12.08</v>
+        <v>11.39</v>
       </c>
       <c r="G68" t="n">
-        <v>15.3</v>
+        <v>27.2</v>
       </c>
       <c r="H68" t="n">
         <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>929.9299999999999</v>
+        <v>-106.77</v>
       </c>
       <c r="K68" t="n">
-        <v>-106.58</v>
+        <v>214.94</v>
       </c>
       <c r="L68" t="n">
-        <v>936.02</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:52:23</t>
+          <t>10:01:07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.21</v>
+        <v>4.74</v>
       </c>
       <c r="F69" t="n">
-        <v>11.67</v>
+        <v>11.82</v>
       </c>
       <c r="G69" t="n">
-        <v>30.4</v>
+        <v>24.9</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-135.42</v>
+        <v>299.89</v>
       </c>
       <c r="K69" t="n">
-        <v>-611.36</v>
+        <v>-298.59</v>
       </c>
       <c r="L69" t="n">
-        <v>626.1799999999999</v>
+        <v>423.19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:54:42</t>
+          <t>10:02:39</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.51</v>
+        <v>4.16</v>
       </c>
       <c r="F70" t="n">
-        <v>11.39</v>
+        <v>11.19</v>
       </c>
       <c r="G70" t="n">
-        <v>12.7</v>
+        <v>19.4</v>
       </c>
       <c r="H70" t="n">
-        <v>96.5</v>
+        <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>337.59</v>
+        <v>23.49</v>
       </c>
       <c r="K70" t="n">
-        <v>168.31</v>
+        <v>245.32</v>
       </c>
       <c r="L70" t="n">
-        <v>377.22</v>
+        <v>246.44</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:58:55</t>
+          <t>10:06:51</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.51</v>
+        <v>4.37</v>
       </c>
       <c r="F71" t="n">
-        <v>11.72</v>
+        <v>11.25</v>
       </c>
       <c r="G71" t="n">
-        <v>21.7</v>
+        <v>8.5</v>
       </c>
       <c r="H71" t="n">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-65.31999999999999</v>
+        <v>23.86</v>
       </c>
       <c r="K71" t="n">
-        <v>58.27</v>
+        <v>-186.96</v>
       </c>
       <c r="L71" t="n">
-        <v>87.53</v>
+        <v>188.48</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:00:58</t>
+          <t>10:07:40</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.89</v>
+        <v>4.74</v>
       </c>
       <c r="F72" t="n">
-        <v>11.48</v>
+        <v>10.51</v>
       </c>
       <c r="G72" t="n">
-        <v>13.9</v>
+        <v>29.5</v>
       </c>
       <c r="H72" t="n">
-        <v>91.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>-257.32</v>
+        <v>1.92</v>
       </c>
       <c r="K72" t="n">
-        <v>-76.14</v>
+        <v>372.79</v>
       </c>
       <c r="L72" t="n">
-        <v>268.35</v>
+        <v>372.79</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:02:26</t>
+          <t>10:10:07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.59</v>
+        <v>5.4</v>
       </c>
       <c r="F73" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="G73" t="n">
-        <v>34.4</v>
+        <v>20.5</v>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>218.12</v>
+        <v>-487.41</v>
       </c>
       <c r="K73" t="n">
-        <v>330.56</v>
+        <v>362.82</v>
       </c>
       <c r="L73" t="n">
-        <v>396.04</v>
+        <v>607.63</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:12:48</t>
+          <t>10:20:02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.23</v>
+        <v>5.58</v>
       </c>
       <c r="F74" t="n">
-        <v>12.52</v>
+        <v>11.28</v>
       </c>
       <c r="G74" t="n">
-        <v>16.3</v>
+        <v>26.3</v>
       </c>
       <c r="H74" t="n">
         <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>76.59</v>
+        <v>-96.47</v>
       </c>
       <c r="K74" t="n">
-        <v>-25.44</v>
+        <v>-18.61</v>
       </c>
       <c r="L74" t="n">
-        <v>80.7</v>
+        <v>98.23999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:13:52</t>
+          <t>10:22:11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="F75" t="n">
-        <v>11.74</v>
+        <v>11.13</v>
       </c>
       <c r="G75" t="n">
-        <v>33</v>
+        <v>14.4</v>
       </c>
       <c r="H75" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>12.75</v>
+        <v>248.1</v>
       </c>
       <c r="K75" t="n">
-        <v>-210.78</v>
+        <v>116.89</v>
       </c>
       <c r="L75" t="n">
-        <v>211.16</v>
+        <v>274.26</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:15:56</t>
+          <t>10:24:02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.08</v>
+        <v>5.69</v>
       </c>
       <c r="F76" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="G76" t="n">
-        <v>18.8</v>
+        <v>24.9</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-110.92</v>
+        <v>-219.44</v>
       </c>
       <c r="K76" t="n">
-        <v>83.56999999999999</v>
+        <v>172.45</v>
       </c>
       <c r="L76" t="n">
-        <v>138.88</v>
+        <v>279.09</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:21:59</t>
+          <t>10:27:39</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.41</v>
+        <v>5.12</v>
       </c>
       <c r="F77" t="n">
-        <v>11.07</v>
+        <v>10.81</v>
       </c>
       <c r="G77" t="n">
-        <v>23.9</v>
+        <v>16.6</v>
       </c>
       <c r="H77" t="n">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>459.98</v>
+        <v>177.4</v>
       </c>
       <c r="K77" t="n">
-        <v>149.86</v>
+        <v>-126.1</v>
       </c>
       <c r="L77" t="n">
-        <v>483.78</v>
+        <v>217.65</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:24:31</t>
+          <t>10:28:55</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.58</v>
+        <v>5.06</v>
       </c>
       <c r="F78" t="n">
-        <v>10.99</v>
+        <v>10.83</v>
       </c>
       <c r="G78" t="n">
-        <v>3.5</v>
+        <v>23.6</v>
       </c>
       <c r="H78" t="n">
         <v>100</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-13.76</v>
+        <v>-242.94</v>
       </c>
       <c r="K78" t="n">
-        <v>118.68</v>
+        <v>110.74</v>
       </c>
       <c r="L78" t="n">
-        <v>119.48</v>
+        <v>266.99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:25:29</t>
+          <t>10:30:36</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.99</v>
+        <v>5.1</v>
       </c>
       <c r="F79" t="n">
-        <v>11.06</v>
+        <v>11.2</v>
       </c>
       <c r="G79" t="n">
-        <v>10.3</v>
+        <v>22.2</v>
       </c>
       <c r="H79" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I79" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-192.84</v>
+        <v>-14.29</v>
       </c>
       <c r="K79" t="n">
-        <v>153.86</v>
+        <v>-53.32</v>
       </c>
       <c r="L79" t="n">
-        <v>246.7</v>
+        <v>55.21</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:31:34</t>
+          <t>10:34:47</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.08</v>
+        <v>5.8</v>
       </c>
       <c r="F80" t="n">
-        <v>11.92</v>
+        <v>11.96</v>
       </c>
       <c r="G80" t="n">
-        <v>25.4</v>
+        <v>23.2</v>
       </c>
       <c r="H80" t="n">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>119.61</v>
+        <v>469.44</v>
       </c>
       <c r="K80" t="n">
-        <v>449.39</v>
+        <v>-5.44</v>
       </c>
       <c r="L80" t="n">
-        <v>465.03</v>
+        <v>469.47</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:33:17</t>
+          <t>10:36:19</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.78</v>
+        <v>5.96</v>
       </c>
       <c r="F81" t="n">
-        <v>11.29</v>
+        <v>11.43</v>
       </c>
       <c r="G81" t="n">
-        <v>25.3</v>
+        <v>30.2</v>
       </c>
       <c r="H81" t="n">
-        <v>96.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-60.39</v>
+        <v>293.05</v>
       </c>
       <c r="K81" t="n">
-        <v>-315.34</v>
+        <v>-80.66</v>
       </c>
       <c r="L81" t="n">
-        <v>321.07</v>
+        <v>303.95</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:35:26</t>
+          <t>10:37:13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.73</v>
+        <v>4.98</v>
       </c>
       <c r="F82" t="n">
-        <v>11.08</v>
+        <v>11.47</v>
       </c>
       <c r="G82" t="n">
-        <v>20.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H82" t="n">
         <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>133.19</v>
+        <v>1.91</v>
       </c>
       <c r="K82" t="n">
-        <v>-1.49</v>
+        <v>-308.35</v>
       </c>
       <c r="L82" t="n">
-        <v>133.2</v>
+        <v>308.36</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:40:21</t>
+          <t>10:43:21</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.68</v>
+        <v>4.71</v>
       </c>
       <c r="F83" t="n">
-        <v>10.68</v>
+        <v>11.55</v>
       </c>
       <c r="G83" t="n">
-        <v>23.9</v>
+        <v>2.9</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>84.58</v>
+        <v>278.41</v>
       </c>
       <c r="K83" t="n">
-        <v>50.96</v>
+        <v>-12.15</v>
       </c>
       <c r="L83" t="n">
-        <v>98.75</v>
+        <v>278.67</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:43:14</t>
+          <t>10:45:17</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>5.5</v>
+        <v>4.99</v>
       </c>
       <c r="F84" t="n">
-        <v>11.51</v>
+        <v>11.3</v>
       </c>
       <c r="G84" t="n">
-        <v>22.8</v>
+        <v>12.9</v>
       </c>
       <c r="H84" t="n">
-        <v>96.8</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>171.85</v>
+        <v>341.59</v>
       </c>
       <c r="K84" t="n">
-        <v>-503.52</v>
+        <v>-57.82</v>
       </c>
       <c r="L84" t="n">
-        <v>532.03</v>
+        <v>346.45</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:44:43</t>
+          <t>10:47:06</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>5.13</v>
+        <v>4.55</v>
       </c>
       <c r="F85" t="n">
-        <v>12.24</v>
+        <v>11.63</v>
       </c>
       <c r="G85" t="n">
-        <v>18.6</v>
+        <v>22.7</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>530.1900000000001</v>
+        <v>430.77</v>
       </c>
       <c r="K85" t="n">
-        <v>325.54</v>
+        <v>-525.01</v>
       </c>
       <c r="L85" t="n">
-        <v>622.16</v>
+        <v>679.11</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:48:53</t>
+          <t>10:52:49</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.06</v>
+        <v>4.96</v>
       </c>
       <c r="F86" t="n">
-        <v>11.47</v>
+        <v>11.19</v>
       </c>
       <c r="G86" t="n">
-        <v>360</v>
+        <v>12</v>
       </c>
       <c r="H86" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-51.95</v>
+        <v>-325.64</v>
       </c>
       <c r="K86" t="n">
-        <v>787.2</v>
+        <v>-192.56</v>
       </c>
       <c r="L86" t="n">
-        <v>788.92</v>
+        <v>378.32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:51:06</t>
+          <t>10:53:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.88</v>
+        <v>4.98</v>
       </c>
       <c r="F87" t="n">
-        <v>11.16</v>
+        <v>11.41</v>
       </c>
       <c r="G87" t="n">
-        <v>28.7</v>
+        <v>7.9</v>
       </c>
       <c r="H87" t="n">
         <v>100</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>438</v>
+        <v>612.25</v>
       </c>
       <c r="K87" t="n">
-        <v>-257.09</v>
+        <v>826.28</v>
       </c>
       <c r="L87" t="n">
-        <v>507.88</v>
+        <v>1028.39</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:53:04</t>
+          <t>10:56:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.24</v>
+        <v>5.08</v>
       </c>
       <c r="F88" t="n">
-        <v>11.96</v>
+        <v>11.36</v>
       </c>
       <c r="G88" t="n">
-        <v>17.1</v>
+        <v>15.9</v>
       </c>
       <c r="H88" t="n">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-616.2</v>
+        <v>464.4</v>
       </c>
       <c r="K88" t="n">
-        <v>367.08</v>
+        <v>549.36</v>
       </c>
       <c r="L88" t="n">
-        <v>717.26</v>
+        <v>719.35</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>74.39</v>
+        <v>131.99</v>
       </c>
       <c r="K14" t="n">
-        <v>18.8</v>
+        <v>33.36</v>
       </c>
       <c r="L14" t="n">
-        <v>76.73</v>
+        <v>136.14</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>233.68</v>
+        <v>239.68</v>
       </c>
       <c r="K15" t="n">
-        <v>-40.9</v>
+        <v>-41.95</v>
       </c>
       <c r="L15" t="n">
-        <v>237.23</v>
+        <v>243.32</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-136.1</v>
+        <v>-148.9</v>
       </c>
       <c r="K16" t="n">
-        <v>-9.279999999999999</v>
+        <v>-10.16</v>
       </c>
       <c r="L16" t="n">
-        <v>136.42</v>
+        <v>149.25</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>49.66</v>
+        <v>73.5</v>
       </c>
       <c r="K17" t="n">
-        <v>-121.34</v>
+        <v>-179.59</v>
       </c>
       <c r="L17" t="n">
-        <v>131.1</v>
+        <v>194.05</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-106.79</v>
+        <v>-134.83</v>
       </c>
       <c r="K18" t="n">
-        <v>-75.45</v>
+        <v>-95.26000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>130.76</v>
+        <v>165.09</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>226.5</v>
+        <v>257.71</v>
       </c>
       <c r="K19" t="n">
-        <v>188.95</v>
+        <v>214.98</v>
       </c>
       <c r="L19" t="n">
-        <v>294.96</v>
+        <v>335.6</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-127.96</v>
+        <v>-162.84</v>
       </c>
       <c r="K20" t="n">
-        <v>-245</v>
+        <v>-311.78</v>
       </c>
       <c r="L20" t="n">
-        <v>276.4</v>
+        <v>351.74</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-309.87</v>
+        <v>-379.8</v>
       </c>
       <c r="K21" t="n">
-        <v>321.8</v>
+        <v>394.41</v>
       </c>
       <c r="L21" t="n">
-        <v>446.74</v>
+        <v>547.54</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-141.79</v>
+        <v>-159.82</v>
       </c>
       <c r="K22" t="n">
-        <v>289.55</v>
+        <v>326.37</v>
       </c>
       <c r="L22" t="n">
-        <v>322.4</v>
+        <v>363.41</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-414.12</v>
+        <v>-511.43</v>
       </c>
       <c r="K23" t="n">
-        <v>339.11</v>
+        <v>418.8</v>
       </c>
       <c r="L23" t="n">
-        <v>535.25</v>
+        <v>661.02</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>258.04</v>
+        <v>417.24</v>
       </c>
       <c r="K24" t="n">
-        <v>157.71</v>
+        <v>255.01</v>
       </c>
       <c r="L24" t="n">
-        <v>302.42</v>
+        <v>489</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-87.73</v>
+        <v>-140.24</v>
       </c>
       <c r="K25" t="n">
-        <v>250.83</v>
+        <v>400.95</v>
       </c>
       <c r="L25" t="n">
-        <v>265.73</v>
+        <v>424.77</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-362.02</v>
+        <v>-649.75</v>
       </c>
       <c r="K26" t="n">
-        <v>81.34</v>
+        <v>145.98</v>
       </c>
       <c r="L26" t="n">
-        <v>371.05</v>
+        <v>665.9400000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-273.01</v>
+        <v>-378.56</v>
       </c>
       <c r="K27" t="n">
-        <v>-504.97</v>
+        <v>-700.1799999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>574.04</v>
+        <v>795.97</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-660.37</v>
+        <v>-880.61</v>
       </c>
       <c r="K28" t="n">
-        <v>252.94</v>
+        <v>337.3</v>
       </c>
       <c r="L28" t="n">
-        <v>707.16</v>
+        <v>943</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-104.91</v>
+        <v>-158.71</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.61</v>
+        <v>-0.92</v>
       </c>
       <c r="L29" t="n">
-        <v>104.91</v>
+        <v>158.71</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>101.46</v>
+        <v>166.01</v>
       </c>
       <c r="K30" t="n">
-        <v>-14.41</v>
+        <v>-23.58</v>
       </c>
       <c r="L30" t="n">
-        <v>102.47</v>
+        <v>167.68</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>228.23</v>
+        <v>234.2</v>
       </c>
       <c r="K31" t="n">
-        <v>58.24</v>
+        <v>59.76</v>
       </c>
       <c r="L31" t="n">
-        <v>235.54</v>
+        <v>241.7</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>43.97</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-162.2</v>
+        <v>-243.63</v>
       </c>
       <c r="L32" t="n">
-        <v>168.05</v>
+        <v>252.42</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.39</v>
+        <v>-2.28</v>
       </c>
       <c r="K33" t="n">
-        <v>137.21</v>
+        <v>224.22</v>
       </c>
       <c r="L33" t="n">
-        <v>137.22</v>
+        <v>224.23</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-168.78</v>
+        <v>-236.17</v>
       </c>
       <c r="K34" t="n">
-        <v>43.75</v>
+        <v>61.22</v>
       </c>
       <c r="L34" t="n">
-        <v>174.36</v>
+        <v>243.98</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-120.74</v>
+        <v>-209.39</v>
       </c>
       <c r="K35" t="n">
-        <v>171.28</v>
+        <v>297.02</v>
       </c>
       <c r="L35" t="n">
-        <v>209.56</v>
+        <v>363.41</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-130.09</v>
+        <v>-181.71</v>
       </c>
       <c r="K36" t="n">
-        <v>-164.94</v>
+        <v>-230.38</v>
       </c>
       <c r="L36" t="n">
-        <v>210.07</v>
+        <v>293.42</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-193.79</v>
+        <v>-244.81</v>
       </c>
       <c r="K37" t="n">
-        <v>362.5</v>
+        <v>457.95</v>
       </c>
       <c r="L37" t="n">
-        <v>411.05</v>
+        <v>519.28</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-274.31</v>
+        <v>-333.32</v>
       </c>
       <c r="K38" t="n">
-        <v>378.94</v>
+        <v>460.46</v>
       </c>
       <c r="L38" t="n">
-        <v>467.81</v>
+        <v>568.4400000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-941.87</v>
+        <v>-1043.56</v>
       </c>
       <c r="K39" t="n">
-        <v>148.21</v>
+        <v>164.22</v>
       </c>
       <c r="L39" t="n">
-        <v>953.46</v>
+        <v>1056.4</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>550.15</v>
+        <v>692.4299999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>469.24</v>
+        <v>590.6</v>
       </c>
       <c r="L40" t="n">
-        <v>723.08</v>
+        <v>910.09</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>315.3</v>
+        <v>442.07</v>
       </c>
       <c r="K41" t="n">
-        <v>482.42</v>
+        <v>676.38</v>
       </c>
       <c r="L41" t="n">
-        <v>576.3200000000001</v>
+        <v>808.03</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>858.85</v>
+        <v>1047.21</v>
       </c>
       <c r="K42" t="n">
-        <v>-429.97</v>
+        <v>-524.27</v>
       </c>
       <c r="L42" t="n">
-        <v>960.47</v>
+        <v>1171.11</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>628.13</v>
+        <v>856.8</v>
       </c>
       <c r="K43" t="n">
-        <v>54.46</v>
+        <v>74.28</v>
       </c>
       <c r="L43" t="n">
-        <v>630.49</v>
+        <v>860.01</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>68.43000000000001</v>
+        <v>80.28</v>
       </c>
       <c r="K44" t="n">
-        <v>206.03</v>
+        <v>241.72</v>
       </c>
       <c r="L44" t="n">
-        <v>217.1</v>
+        <v>254.7</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>95.23999999999999</v>
+        <v>134.37</v>
       </c>
       <c r="K45" t="n">
-        <v>54.35</v>
+        <v>76.69</v>
       </c>
       <c r="L45" t="n">
-        <v>109.66</v>
+        <v>154.71</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>197.59</v>
+        <v>224.95</v>
       </c>
       <c r="K46" t="n">
-        <v>-153.43</v>
+        <v>-174.67</v>
       </c>
       <c r="L46" t="n">
-        <v>250.16</v>
+        <v>284.8</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-389.49</v>
+        <v>-379.97</v>
       </c>
       <c r="K47" t="n">
-        <v>404.05</v>
+        <v>394.17</v>
       </c>
       <c r="L47" t="n">
-        <v>561.22</v>
+        <v>547.5</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>222.77</v>
+        <v>236.95</v>
       </c>
       <c r="K48" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="L48" t="n">
-        <v>222.77</v>
+        <v>236.95</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>6.8</v>
+        <v>9.17</v>
       </c>
       <c r="K49" t="n">
-        <v>141.71</v>
+        <v>191.15</v>
       </c>
       <c r="L49" t="n">
-        <v>141.87</v>
+        <v>191.37</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-224.08</v>
+        <v>-283.3</v>
       </c>
       <c r="K50" t="n">
-        <v>270.13</v>
+        <v>341.51</v>
       </c>
       <c r="L50" t="n">
-        <v>350.97</v>
+        <v>443.72</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>69.66</v>
+        <v>137.16</v>
       </c>
       <c r="K51" t="n">
-        <v>-141.42</v>
+        <v>-278.44</v>
       </c>
       <c r="L51" t="n">
-        <v>157.64</v>
+        <v>310.39</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-366.39</v>
+        <v>-415.03</v>
       </c>
       <c r="K52" t="n">
-        <v>-19.01</v>
+        <v>-21.53</v>
       </c>
       <c r="L52" t="n">
-        <v>366.88</v>
+        <v>415.58</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-64.5</v>
+        <v>-181.74</v>
       </c>
       <c r="K53" t="n">
-        <v>-118.61</v>
+        <v>-334.22</v>
       </c>
       <c r="L53" t="n">
-        <v>135.01</v>
+        <v>380.44</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-466.42</v>
+        <v>-712.45</v>
       </c>
       <c r="K54" t="n">
-        <v>-137.74</v>
+        <v>-210.4</v>
       </c>
       <c r="L54" t="n">
-        <v>486.34</v>
+        <v>742.87</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>496.13</v>
+        <v>624.77</v>
       </c>
       <c r="K55" t="n">
-        <v>362.35</v>
+        <v>456.31</v>
       </c>
       <c r="L55" t="n">
-        <v>614.37</v>
+        <v>773.67</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-72.58</v>
+        <v>-160.21</v>
       </c>
       <c r="K56" t="n">
-        <v>-175.86</v>
+        <v>-388.17</v>
       </c>
       <c r="L56" t="n">
-        <v>190.25</v>
+        <v>419.93</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-830.72</v>
+        <v>-1181.72</v>
       </c>
       <c r="K57" t="n">
-        <v>-42.89</v>
+        <v>-61.02</v>
       </c>
       <c r="L57" t="n">
-        <v>831.83</v>
+        <v>1183.29</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-13.88</v>
+        <v>-16.93</v>
       </c>
       <c r="K58" t="n">
-        <v>-1294.42</v>
+        <v>-1578.54</v>
       </c>
       <c r="L58" t="n">
-        <v>1294.49</v>
+        <v>1578.63</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>74.41</v>
+        <v>116.19</v>
       </c>
       <c r="K59" t="n">
-        <v>-113.02</v>
+        <v>-176.48</v>
       </c>
       <c r="L59" t="n">
-        <v>135.32</v>
+        <v>211.3</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>211.1</v>
+        <v>245.32</v>
       </c>
       <c r="K60" t="n">
-        <v>56.45</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>218.52</v>
+        <v>253.94</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>130.78</v>
+        <v>193.69</v>
       </c>
       <c r="K61" t="n">
-        <v>-70.34</v>
+        <v>-104.18</v>
       </c>
       <c r="L61" t="n">
-        <v>148.5</v>
+        <v>219.92</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-164.08</v>
+        <v>-179.99</v>
       </c>
       <c r="K62" t="n">
-        <v>-117.18</v>
+        <v>-128.54</v>
       </c>
       <c r="L62" t="n">
-        <v>201.62</v>
+        <v>221.18</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>89.66</v>
+        <v>122.48</v>
       </c>
       <c r="K63" t="n">
-        <v>217.86</v>
+        <v>297.59</v>
       </c>
       <c r="L63" t="n">
-        <v>235.59</v>
+        <v>321.81</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>19.51</v>
+        <v>23.4</v>
       </c>
       <c r="K64" t="n">
-        <v>186.21</v>
+        <v>223.38</v>
       </c>
       <c r="L64" t="n">
-        <v>187.23</v>
+        <v>224.61</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>477.86</v>
+        <v>546.12</v>
       </c>
       <c r="K65" t="n">
-        <v>-152.87</v>
+        <v>-174.71</v>
       </c>
       <c r="L65" t="n">
-        <v>501.71</v>
+        <v>573.39</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-68.92</v>
+        <v>-93.06</v>
       </c>
       <c r="K66" t="n">
-        <v>-331.24</v>
+        <v>-447.24</v>
       </c>
       <c r="L66" t="n">
-        <v>338.34</v>
+        <v>456.82</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-93.09999999999999</v>
+        <v>-208.49</v>
       </c>
       <c r="K67" t="n">
-        <v>44.39</v>
+        <v>99.42</v>
       </c>
       <c r="L67" t="n">
-        <v>103.14</v>
+        <v>230.98</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-106.77</v>
+        <v>-207.48</v>
       </c>
       <c r="K68" t="n">
-        <v>214.94</v>
+        <v>417.66</v>
       </c>
       <c r="L68" t="n">
-        <v>240</v>
+        <v>466.35</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>299.89</v>
+        <v>430.56</v>
       </c>
       <c r="K69" t="n">
-        <v>-298.59</v>
+        <v>-428.69</v>
       </c>
       <c r="L69" t="n">
-        <v>423.19</v>
+        <v>607.59</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>23.49</v>
+        <v>34.79</v>
       </c>
       <c r="K70" t="n">
-        <v>245.32</v>
+        <v>363.35</v>
       </c>
       <c r="L70" t="n">
-        <v>246.44</v>
+        <v>365.02</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>23.86</v>
+        <v>51.73</v>
       </c>
       <c r="K71" t="n">
-        <v>-186.96</v>
+        <v>-405.35</v>
       </c>
       <c r="L71" t="n">
-        <v>188.48</v>
+        <v>408.64</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="K72" t="n">
-        <v>372.79</v>
+        <v>669.92</v>
       </c>
       <c r="L72" t="n">
-        <v>372.79</v>
+        <v>669.9299999999999</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-487.41</v>
+        <v>-806.91</v>
       </c>
       <c r="K73" t="n">
-        <v>362.82</v>
+        <v>600.65</v>
       </c>
       <c r="L73" t="n">
-        <v>607.63</v>
+        <v>1005.93</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-96.47</v>
+        <v>-170.96</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.61</v>
+        <v>-32.97</v>
       </c>
       <c r="L74" t="n">
-        <v>98.23999999999999</v>
+        <v>174.11</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>248.1</v>
+        <v>292.42</v>
       </c>
       <c r="K75" t="n">
-        <v>116.89</v>
+        <v>137.76</v>
       </c>
       <c r="L75" t="n">
-        <v>274.26</v>
+        <v>323.24</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-219.44</v>
+        <v>-273.75</v>
       </c>
       <c r="K76" t="n">
-        <v>172.45</v>
+        <v>215.14</v>
       </c>
       <c r="L76" t="n">
-        <v>279.09</v>
+        <v>348.18</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>177.4</v>
+        <v>259.79</v>
       </c>
       <c r="K77" t="n">
-        <v>-126.1</v>
+        <v>-184.66</v>
       </c>
       <c r="L77" t="n">
-        <v>217.65</v>
+        <v>318.73</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-242.94</v>
+        <v>-269.06</v>
       </c>
       <c r="K78" t="n">
-        <v>110.74</v>
+        <v>122.65</v>
       </c>
       <c r="L78" t="n">
-        <v>266.99</v>
+        <v>295.69</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-14.29</v>
+        <v>-38.16</v>
       </c>
       <c r="K79" t="n">
-        <v>-53.32</v>
+        <v>-142.37</v>
       </c>
       <c r="L79" t="n">
-        <v>55.21</v>
+        <v>147.39</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>469.44</v>
+        <v>661.61</v>
       </c>
       <c r="K80" t="n">
-        <v>-5.44</v>
+        <v>-7.66</v>
       </c>
       <c r="L80" t="n">
-        <v>469.47</v>
+        <v>661.66</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>293.05</v>
+        <v>495.09</v>
       </c>
       <c r="K81" t="n">
-        <v>-80.66</v>
+        <v>-136.26</v>
       </c>
       <c r="L81" t="n">
-        <v>303.95</v>
+        <v>513.5</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="K82" t="n">
-        <v>-308.35</v>
+        <v>-398.37</v>
       </c>
       <c r="L82" t="n">
-        <v>308.36</v>
+        <v>398.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>278.41</v>
+        <v>511.81</v>
       </c>
       <c r="K83" t="n">
-        <v>-12.15</v>
+        <v>-22.34</v>
       </c>
       <c r="L83" t="n">
-        <v>278.67</v>
+        <v>512.3</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>341.59</v>
+        <v>605.58</v>
       </c>
       <c r="K84" t="n">
-        <v>-57.82</v>
+        <v>-102.5</v>
       </c>
       <c r="L84" t="n">
-        <v>346.45</v>
+        <v>614.2</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>430.77</v>
+        <v>540.15</v>
       </c>
       <c r="K85" t="n">
-        <v>-525.01</v>
+        <v>-658.3200000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>679.11</v>
+        <v>851.5599999999999</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-325.64</v>
+        <v>-648.21</v>
       </c>
       <c r="K86" t="n">
-        <v>-192.56</v>
+        <v>-383.31</v>
       </c>
       <c r="L86" t="n">
-        <v>378.32</v>
+        <v>753.0599999999999</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>612.25</v>
+        <v>732.11</v>
       </c>
       <c r="K87" t="n">
-        <v>826.28</v>
+        <v>988.03</v>
       </c>
       <c r="L87" t="n">
-        <v>1028.39</v>
+        <v>1229.71</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>464.4</v>
+        <v>598.24</v>
       </c>
       <c r="K88" t="n">
-        <v>549.36</v>
+        <v>707.6799999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>719.35</v>
+        <v>926.66</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>131.99</v>
+        <v>93.36</v>
       </c>
       <c r="K14" t="n">
-        <v>33.36</v>
+        <v>23.6</v>
       </c>
       <c r="L14" t="n">
-        <v>136.14</v>
+        <v>96.29000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>239.68</v>
+        <v>181.2</v>
       </c>
       <c r="K15" t="n">
-        <v>-41.95</v>
+        <v>-31.72</v>
       </c>
       <c r="L15" t="n">
-        <v>243.32</v>
+        <v>183.96</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-148.9</v>
+        <v>-123.06</v>
       </c>
       <c r="K16" t="n">
-        <v>-10.16</v>
+        <v>-8.4</v>
       </c>
       <c r="L16" t="n">
-        <v>149.25</v>
+        <v>123.35</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>73.5</v>
+        <v>48.55</v>
       </c>
       <c r="K17" t="n">
-        <v>-179.59</v>
+        <v>-118.63</v>
       </c>
       <c r="L17" t="n">
-        <v>194.05</v>
+        <v>128.18</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-134.83</v>
+        <v>-102.22</v>
       </c>
       <c r="K18" t="n">
-        <v>-95.26000000000001</v>
+        <v>-72.22</v>
       </c>
       <c r="L18" t="n">
-        <v>165.09</v>
+        <v>125.16</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>257.71</v>
+        <v>172.17</v>
       </c>
       <c r="K19" t="n">
-        <v>214.98</v>
+        <v>143.63</v>
       </c>
       <c r="L19" t="n">
-        <v>335.6</v>
+        <v>224.21</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-162.84</v>
+        <v>-105.02</v>
       </c>
       <c r="K20" t="n">
-        <v>-311.78</v>
+        <v>-201.08</v>
       </c>
       <c r="L20" t="n">
-        <v>351.74</v>
+        <v>226.85</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-379.8</v>
+        <v>-219.78</v>
       </c>
       <c r="K21" t="n">
-        <v>394.41</v>
+        <v>228.24</v>
       </c>
       <c r="L21" t="n">
-        <v>547.54</v>
+        <v>316.86</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-159.82</v>
+        <v>-100.13</v>
       </c>
       <c r="K22" t="n">
-        <v>326.37</v>
+        <v>204.47</v>
       </c>
       <c r="L22" t="n">
-        <v>363.41</v>
+        <v>227.66</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-511.43</v>
+        <v>-282.75</v>
       </c>
       <c r="K23" t="n">
-        <v>418.8</v>
+        <v>231.54</v>
       </c>
       <c r="L23" t="n">
-        <v>661.02</v>
+        <v>365.46</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>417.24</v>
+        <v>215.92</v>
       </c>
       <c r="K24" t="n">
-        <v>255.01</v>
+        <v>131.97</v>
       </c>
       <c r="L24" t="n">
-        <v>489</v>
+        <v>253.06</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-140.24</v>
+        <v>-75.55</v>
       </c>
       <c r="K25" t="n">
-        <v>400.95</v>
+        <v>215.99</v>
       </c>
       <c r="L25" t="n">
-        <v>424.77</v>
+        <v>228.82</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-649.75</v>
+        <v>-293.75</v>
       </c>
       <c r="K26" t="n">
-        <v>145.98</v>
+        <v>66</v>
       </c>
       <c r="L26" t="n">
-        <v>665.9400000000001</v>
+        <v>301.07</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-378.56</v>
+        <v>-182.76</v>
       </c>
       <c r="K27" t="n">
-        <v>-700.1799999999999</v>
+        <v>-338.04</v>
       </c>
       <c r="L27" t="n">
-        <v>795.97</v>
+        <v>384.28</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-880.61</v>
+        <v>-429.44</v>
       </c>
       <c r="K28" t="n">
-        <v>337.3</v>
+        <v>164.49</v>
       </c>
       <c r="L28" t="n">
-        <v>943</v>
+        <v>459.86</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-158.71</v>
+        <v>-107.73</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.92</v>
+        <v>-0.63</v>
       </c>
       <c r="L29" t="n">
-        <v>158.71</v>
+        <v>107.73</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>166.01</v>
+        <v>118.77</v>
       </c>
       <c r="K30" t="n">
-        <v>-23.58</v>
+        <v>-16.87</v>
       </c>
       <c r="L30" t="n">
-        <v>167.68</v>
+        <v>119.96</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>234.2</v>
+        <v>177.37</v>
       </c>
       <c r="K31" t="n">
-        <v>59.76</v>
+        <v>45.26</v>
       </c>
       <c r="L31" t="n">
-        <v>241.7</v>
+        <v>183.05</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>66.04000000000001</v>
+        <v>41.56</v>
       </c>
       <c r="K32" t="n">
-        <v>-243.63</v>
+        <v>-153.3</v>
       </c>
       <c r="L32" t="n">
-        <v>252.42</v>
+        <v>158.84</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.28</v>
+        <v>-1.44</v>
       </c>
       <c r="K33" t="n">
-        <v>224.22</v>
+        <v>141.43</v>
       </c>
       <c r="L33" t="n">
-        <v>224.23</v>
+        <v>141.44</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-236.17</v>
+        <v>-157.41</v>
       </c>
       <c r="K34" t="n">
-        <v>61.22</v>
+        <v>40.8</v>
       </c>
       <c r="L34" t="n">
-        <v>243.98</v>
+        <v>162.61</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-209.39</v>
+        <v>-122.79</v>
       </c>
       <c r="K35" t="n">
-        <v>297.02</v>
+        <v>174.19</v>
       </c>
       <c r="L35" t="n">
-        <v>363.41</v>
+        <v>213.12</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-181.71</v>
+        <v>-118.05</v>
       </c>
       <c r="K36" t="n">
-        <v>-230.38</v>
+        <v>-149.67</v>
       </c>
       <c r="L36" t="n">
-        <v>293.42</v>
+        <v>190.62</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-244.81</v>
+        <v>-138.61</v>
       </c>
       <c r="K37" t="n">
-        <v>457.95</v>
+        <v>259.29</v>
       </c>
       <c r="L37" t="n">
-        <v>519.28</v>
+        <v>294.02</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-333.32</v>
+        <v>-198.19</v>
       </c>
       <c r="K38" t="n">
-        <v>460.46</v>
+        <v>273.79</v>
       </c>
       <c r="L38" t="n">
-        <v>568.4400000000001</v>
+        <v>338</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-1043.56</v>
+        <v>-557.92</v>
       </c>
       <c r="K39" t="n">
-        <v>164.22</v>
+        <v>87.8</v>
       </c>
       <c r="L39" t="n">
-        <v>1056.4</v>
+        <v>564.79</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>692.4299999999999</v>
+        <v>355.89</v>
       </c>
       <c r="K40" t="n">
-        <v>590.6</v>
+        <v>303.55</v>
       </c>
       <c r="L40" t="n">
-        <v>910.09</v>
+        <v>467.76</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>442.07</v>
+        <v>218.02</v>
       </c>
       <c r="K41" t="n">
-        <v>676.38</v>
+        <v>333.58</v>
       </c>
       <c r="L41" t="n">
-        <v>808.03</v>
+        <v>398.51</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>1047.21</v>
+        <v>522.51</v>
       </c>
       <c r="K42" t="n">
-        <v>-524.27</v>
+        <v>-261.59</v>
       </c>
       <c r="L42" t="n">
-        <v>1171.11</v>
+        <v>584.33</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>856.8</v>
+        <v>440.92</v>
       </c>
       <c r="K43" t="n">
-        <v>74.28</v>
+        <v>38.23</v>
       </c>
       <c r="L43" t="n">
-        <v>860.01</v>
+        <v>442.57</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>80.28</v>
+        <v>56.25</v>
       </c>
       <c r="K44" t="n">
-        <v>241.72</v>
+        <v>169.39</v>
       </c>
       <c r="L44" t="n">
-        <v>254.7</v>
+        <v>178.48</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>134.37</v>
+        <v>107.3</v>
       </c>
       <c r="K45" t="n">
-        <v>76.69</v>
+        <v>61.24</v>
       </c>
       <c r="L45" t="n">
-        <v>154.71</v>
+        <v>123.54</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>224.95</v>
+        <v>156.88</v>
       </c>
       <c r="K46" t="n">
-        <v>-174.67</v>
+        <v>-121.82</v>
       </c>
       <c r="L46" t="n">
-        <v>284.8</v>
+        <v>198.62</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-379.97</v>
+        <v>-261.42</v>
       </c>
       <c r="K47" t="n">
-        <v>394.17</v>
+        <v>271.19</v>
       </c>
       <c r="L47" t="n">
-        <v>547.5</v>
+        <v>376.67</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>236.95</v>
+        <v>183.86</v>
       </c>
       <c r="K48" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="L48" t="n">
-        <v>236.95</v>
+        <v>183.86</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>9.17</v>
+        <v>6.63</v>
       </c>
       <c r="K49" t="n">
-        <v>191.15</v>
+        <v>138.13</v>
       </c>
       <c r="L49" t="n">
-        <v>191.37</v>
+        <v>138.29</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-283.3</v>
+        <v>-170.4</v>
       </c>
       <c r="K50" t="n">
-        <v>341.51</v>
+        <v>205.42</v>
       </c>
       <c r="L50" t="n">
-        <v>443.72</v>
+        <v>266.9</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>137.16</v>
+        <v>75.55</v>
       </c>
       <c r="K51" t="n">
-        <v>-278.44</v>
+        <v>-153.36</v>
       </c>
       <c r="L51" t="n">
-        <v>310.39</v>
+        <v>170.96</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-415.03</v>
+        <v>-277.67</v>
       </c>
       <c r="K52" t="n">
-        <v>-21.53</v>
+        <v>-14.41</v>
       </c>
       <c r="L52" t="n">
-        <v>415.58</v>
+        <v>278.05</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-181.74</v>
+        <v>-90.73999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>-334.22</v>
+        <v>-166.87</v>
       </c>
       <c r="L53" t="n">
-        <v>380.44</v>
+        <v>189.95</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-712.45</v>
+        <v>-360.07</v>
       </c>
       <c r="K54" t="n">
-        <v>-210.4</v>
+        <v>-106.34</v>
       </c>
       <c r="L54" t="n">
-        <v>742.87</v>
+        <v>375.44</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>624.77</v>
+        <v>341.58</v>
       </c>
       <c r="K55" t="n">
-        <v>456.31</v>
+        <v>249.48</v>
       </c>
       <c r="L55" t="n">
-        <v>773.67</v>
+        <v>422.99</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-160.21</v>
+        <v>-84.97</v>
       </c>
       <c r="K56" t="n">
-        <v>-388.17</v>
+        <v>-205.87</v>
       </c>
       <c r="L56" t="n">
-        <v>419.93</v>
+        <v>222.71</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-1181.72</v>
+        <v>-545.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-61.02</v>
+        <v>-28.17</v>
       </c>
       <c r="L57" t="n">
-        <v>1183.29</v>
+        <v>546.37</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-16.93</v>
+        <v>-8.09</v>
       </c>
       <c r="K58" t="n">
-        <v>-1578.54</v>
+        <v>-754.85</v>
       </c>
       <c r="L58" t="n">
-        <v>1578.63</v>
+        <v>754.89</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>116.19</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>-176.48</v>
+        <v>-120.77</v>
       </c>
       <c r="L59" t="n">
-        <v>211.3</v>
+        <v>144.59</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>245.32</v>
+        <v>185.68</v>
       </c>
       <c r="K60" t="n">
-        <v>65.59999999999999</v>
+        <v>49.65</v>
       </c>
       <c r="L60" t="n">
-        <v>253.94</v>
+        <v>192.21</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>193.69</v>
+        <v>129.71</v>
       </c>
       <c r="K61" t="n">
-        <v>-104.18</v>
+        <v>-69.77</v>
       </c>
       <c r="L61" t="n">
-        <v>219.92</v>
+        <v>147.29</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-179.99</v>
+        <v>-139.54</v>
       </c>
       <c r="K62" t="n">
-        <v>-128.54</v>
+        <v>-99.65000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>221.18</v>
+        <v>171.47</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>122.48</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>297.59</v>
+        <v>194.88</v>
       </c>
       <c r="L63" t="n">
-        <v>321.81</v>
+        <v>210.74</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>23.4</v>
+        <v>17.95</v>
       </c>
       <c r="K64" t="n">
-        <v>223.38</v>
+        <v>171.36</v>
       </c>
       <c r="L64" t="n">
-        <v>224.61</v>
+        <v>172.29</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>546.12</v>
+        <v>344.72</v>
       </c>
       <c r="K65" t="n">
-        <v>-174.71</v>
+        <v>-110.28</v>
       </c>
       <c r="L65" t="n">
-        <v>573.39</v>
+        <v>361.93</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-93.06</v>
+        <v>-55.09</v>
       </c>
       <c r="K66" t="n">
-        <v>-447.24</v>
+        <v>-264.77</v>
       </c>
       <c r="L66" t="n">
-        <v>456.82</v>
+        <v>270.44</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-208.49</v>
+        <v>-125.62</v>
       </c>
       <c r="K67" t="n">
-        <v>99.42</v>
+        <v>59.9</v>
       </c>
       <c r="L67" t="n">
-        <v>230.98</v>
+        <v>139.17</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-207.48</v>
+        <v>-111.96</v>
       </c>
       <c r="K68" t="n">
-        <v>417.66</v>
+        <v>225.38</v>
       </c>
       <c r="L68" t="n">
-        <v>466.35</v>
+        <v>251.65</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>430.56</v>
+        <v>228.69</v>
       </c>
       <c r="K69" t="n">
-        <v>-428.69</v>
+        <v>-227.7</v>
       </c>
       <c r="L69" t="n">
-        <v>607.59</v>
+        <v>322.72</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>34.79</v>
+        <v>20.92</v>
       </c>
       <c r="K70" t="n">
-        <v>363.35</v>
+        <v>218.5</v>
       </c>
       <c r="L70" t="n">
-        <v>365.02</v>
+        <v>219.5</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>51.73</v>
+        <v>27.46</v>
       </c>
       <c r="K71" t="n">
-        <v>-405.35</v>
+        <v>-215.17</v>
       </c>
       <c r="L71" t="n">
-        <v>408.64</v>
+        <v>216.91</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="K72" t="n">
-        <v>669.92</v>
+        <v>313.32</v>
       </c>
       <c r="L72" t="n">
-        <v>669.9299999999999</v>
+        <v>313.32</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-806.91</v>
+        <v>-359.61</v>
       </c>
       <c r="K73" t="n">
-        <v>600.65</v>
+        <v>267.69</v>
       </c>
       <c r="L73" t="n">
-        <v>1005.93</v>
+        <v>448.3</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-170.96</v>
+        <v>-128.22</v>
       </c>
       <c r="K74" t="n">
-        <v>-32.97</v>
+        <v>-24.73</v>
       </c>
       <c r="L74" t="n">
-        <v>174.11</v>
+        <v>130.58</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>292.42</v>
+        <v>191.87</v>
       </c>
       <c r="K75" t="n">
-        <v>137.76</v>
+        <v>90.39</v>
       </c>
       <c r="L75" t="n">
-        <v>323.24</v>
+        <v>212.09</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-273.75</v>
+        <v>-184.96</v>
       </c>
       <c r="K76" t="n">
-        <v>215.14</v>
+        <v>145.36</v>
       </c>
       <c r="L76" t="n">
-        <v>348.18</v>
+        <v>235.24</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>259.79</v>
+        <v>161.57</v>
       </c>
       <c r="K77" t="n">
-        <v>-184.66</v>
+        <v>-114.84</v>
       </c>
       <c r="L77" t="n">
-        <v>318.73</v>
+        <v>198.22</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-269.06</v>
+        <v>-204.5</v>
       </c>
       <c r="K78" t="n">
-        <v>122.65</v>
+        <v>93.22</v>
       </c>
       <c r="L78" t="n">
-        <v>295.69</v>
+        <v>224.74</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-38.16</v>
+        <v>-27.87</v>
       </c>
       <c r="K79" t="n">
-        <v>-142.37</v>
+        <v>-103.98</v>
       </c>
       <c r="L79" t="n">
-        <v>147.39</v>
+        <v>107.65</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>661.61</v>
+        <v>352.42</v>
       </c>
       <c r="K80" t="n">
-        <v>-7.66</v>
+        <v>-4.08</v>
       </c>
       <c r="L80" t="n">
-        <v>661.66</v>
+        <v>352.45</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>495.09</v>
+        <v>262.88</v>
       </c>
       <c r="K81" t="n">
-        <v>-136.26</v>
+        <v>-72.34999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>513.5</v>
+        <v>272.65</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>2.46</v>
+        <v>1.57</v>
       </c>
       <c r="K82" t="n">
-        <v>-398.37</v>
+        <v>-253.97</v>
       </c>
       <c r="L82" t="n">
-        <v>398.37</v>
+        <v>253.97</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>511.81</v>
+        <v>255.65</v>
       </c>
       <c r="K83" t="n">
-        <v>-22.34</v>
+        <v>-11.16</v>
       </c>
       <c r="L83" t="n">
-        <v>512.3</v>
+        <v>255.89</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>605.58</v>
+        <v>291.91</v>
       </c>
       <c r="K84" t="n">
-        <v>-102.5</v>
+        <v>-49.41</v>
       </c>
       <c r="L84" t="n">
-        <v>614.2</v>
+        <v>296.06</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>540.15</v>
+        <v>278.66</v>
       </c>
       <c r="K85" t="n">
-        <v>-658.3200000000001</v>
+        <v>-339.62</v>
       </c>
       <c r="L85" t="n">
-        <v>851.5599999999999</v>
+        <v>439.31</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-648.21</v>
+        <v>-284.03</v>
       </c>
       <c r="K86" t="n">
-        <v>-383.31</v>
+        <v>-167.96</v>
       </c>
       <c r="L86" t="n">
-        <v>753.0599999999999</v>
+        <v>329.97</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>732.11</v>
+        <v>376.33</v>
       </c>
       <c r="K87" t="n">
-        <v>988.03</v>
+        <v>507.88</v>
       </c>
       <c r="L87" t="n">
-        <v>1229.71</v>
+        <v>632.11</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>598.24</v>
+        <v>318.78</v>
       </c>
       <c r="K88" t="n">
-        <v>707.6799999999999</v>
+        <v>377.1</v>
       </c>
       <c r="L88" t="n">
-        <v>926.66</v>
+        <v>493.79</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>93.36</v>
+        <v>101.54</v>
       </c>
       <c r="K14" t="n">
-        <v>23.6</v>
+        <v>25.66</v>
       </c>
       <c r="L14" t="n">
-        <v>96.29000000000001</v>
+        <v>104.73</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>181.2</v>
+        <v>194.32</v>
       </c>
       <c r="K15" t="n">
-        <v>-31.72</v>
+        <v>-34.01</v>
       </c>
       <c r="L15" t="n">
-        <v>183.96</v>
+        <v>197.27</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-123.06</v>
+        <v>-129.34</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.4</v>
+        <v>-8.82</v>
       </c>
       <c r="L16" t="n">
-        <v>123.35</v>
+        <v>129.64</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>48.55</v>
+        <v>53.65</v>
       </c>
       <c r="K17" t="n">
-        <v>-118.63</v>
+        <v>-131.09</v>
       </c>
       <c r="L17" t="n">
-        <v>128.18</v>
+        <v>141.65</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-102.22</v>
+        <v>-111.35</v>
       </c>
       <c r="K18" t="n">
-        <v>-72.22</v>
+        <v>-78.67</v>
       </c>
       <c r="L18" t="n">
-        <v>125.16</v>
+        <v>136.34</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>172.17</v>
+        <v>188.07</v>
       </c>
       <c r="K19" t="n">
-        <v>143.63</v>
+        <v>156.89</v>
       </c>
       <c r="L19" t="n">
-        <v>224.21</v>
+        <v>244.91</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-105.02</v>
+        <v>-117.86</v>
       </c>
       <c r="K20" t="n">
-        <v>-201.08</v>
+        <v>-225.66</v>
       </c>
       <c r="L20" t="n">
-        <v>226.85</v>
+        <v>254.59</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-219.78</v>
+        <v>-251.69</v>
       </c>
       <c r="K21" t="n">
-        <v>228.24</v>
+        <v>261.38</v>
       </c>
       <c r="L21" t="n">
-        <v>316.86</v>
+        <v>362.86</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-100.13</v>
+        <v>-114.12</v>
       </c>
       <c r="K22" t="n">
-        <v>204.47</v>
+        <v>233.04</v>
       </c>
       <c r="L22" t="n">
-        <v>227.66</v>
+        <v>259.48</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-282.75</v>
+        <v>-329.59</v>
       </c>
       <c r="K23" t="n">
-        <v>231.54</v>
+        <v>269.9</v>
       </c>
       <c r="L23" t="n">
-        <v>365.46</v>
+        <v>426</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>215.92</v>
+        <v>254.52</v>
       </c>
       <c r="K24" t="n">
-        <v>131.97</v>
+        <v>155.56</v>
       </c>
       <c r="L24" t="n">
-        <v>253.06</v>
+        <v>298.29</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-75.55</v>
+        <v>-88.5</v>
       </c>
       <c r="K25" t="n">
-        <v>215.99</v>
+        <v>253.02</v>
       </c>
       <c r="L25" t="n">
-        <v>228.82</v>
+        <v>268.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-293.75</v>
+        <v>-357.97</v>
       </c>
       <c r="K26" t="n">
-        <v>66</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>301.07</v>
+        <v>366.9</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-182.76</v>
+        <v>-219.87</v>
       </c>
       <c r="K27" t="n">
-        <v>-338.04</v>
+        <v>-406.66</v>
       </c>
       <c r="L27" t="n">
-        <v>384.28</v>
+        <v>462.29</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-429.44</v>
+        <v>-517.95</v>
       </c>
       <c r="K28" t="n">
-        <v>164.49</v>
+        <v>198.39</v>
       </c>
       <c r="L28" t="n">
-        <v>459.86</v>
+        <v>554.65</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-107.73</v>
+        <v>-117.16</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.63</v>
+        <v>-0.68</v>
       </c>
       <c r="L29" t="n">
-        <v>107.73</v>
+        <v>117.16</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>118.77</v>
+        <v>129.28</v>
       </c>
       <c r="K30" t="n">
-        <v>-16.87</v>
+        <v>-18.36</v>
       </c>
       <c r="L30" t="n">
-        <v>119.96</v>
+        <v>130.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>177.37</v>
+        <v>190.87</v>
       </c>
       <c r="K31" t="n">
-        <v>45.26</v>
+        <v>48.71</v>
       </c>
       <c r="L31" t="n">
-        <v>183.05</v>
+        <v>196.99</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>41.56</v>
+        <v>46.18</v>
       </c>
       <c r="K32" t="n">
-        <v>-153.3</v>
+        <v>-170.35</v>
       </c>
       <c r="L32" t="n">
-        <v>158.84</v>
+        <v>176.5</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.44</v>
+        <v>-1.6</v>
       </c>
       <c r="K33" t="n">
-        <v>141.43</v>
+        <v>157.18</v>
       </c>
       <c r="L33" t="n">
-        <v>141.44</v>
+        <v>157.18</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-157.41</v>
+        <v>-172.35</v>
       </c>
       <c r="K34" t="n">
-        <v>40.8</v>
+        <v>44.67</v>
       </c>
       <c r="L34" t="n">
-        <v>162.61</v>
+        <v>178.05</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-122.79</v>
+        <v>-139.96</v>
       </c>
       <c r="K35" t="n">
-        <v>174.19</v>
+        <v>198.53</v>
       </c>
       <c r="L35" t="n">
-        <v>213.12</v>
+        <v>242.91</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-118.05</v>
+        <v>-133.21</v>
       </c>
       <c r="K36" t="n">
-        <v>-149.67</v>
+        <v>-168.89</v>
       </c>
       <c r="L36" t="n">
-        <v>190.62</v>
+        <v>215.1</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-138.61</v>
+        <v>-159.47</v>
       </c>
       <c r="K37" t="n">
-        <v>259.29</v>
+        <v>298.3</v>
       </c>
       <c r="L37" t="n">
-        <v>294.02</v>
+        <v>338.25</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-198.19</v>
+        <v>-227.98</v>
       </c>
       <c r="K38" t="n">
-        <v>273.79</v>
+        <v>314.95</v>
       </c>
       <c r="L38" t="n">
-        <v>338</v>
+        <v>388.81</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-557.92</v>
+        <v>-650.7</v>
       </c>
       <c r="K39" t="n">
-        <v>87.8</v>
+        <v>102.4</v>
       </c>
       <c r="L39" t="n">
-        <v>564.79</v>
+        <v>658.71</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>355.89</v>
+        <v>418.73</v>
       </c>
       <c r="K40" t="n">
-        <v>303.55</v>
+        <v>357.15</v>
       </c>
       <c r="L40" t="n">
-        <v>467.76</v>
+        <v>550.36</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>218.02</v>
+        <v>260.57</v>
       </c>
       <c r="K41" t="n">
-        <v>333.58</v>
+        <v>398.69</v>
       </c>
       <c r="L41" t="n">
-        <v>398.51</v>
+        <v>476.29</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>522.51</v>
+        <v>628.27</v>
       </c>
       <c r="K42" t="n">
-        <v>-261.59</v>
+        <v>-314.54</v>
       </c>
       <c r="L42" t="n">
-        <v>584.33</v>
+        <v>702.61</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>440.92</v>
+        <v>526.1900000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>38.23</v>
+        <v>45.62</v>
       </c>
       <c r="L43" t="n">
-        <v>442.57</v>
+        <v>528.16</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>56.25</v>
+        <v>61.3</v>
       </c>
       <c r="K44" t="n">
-        <v>169.39</v>
+        <v>184.58</v>
       </c>
       <c r="L44" t="n">
-        <v>178.48</v>
+        <v>194.49</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>107.3</v>
+        <v>115.23</v>
       </c>
       <c r="K45" t="n">
-        <v>61.24</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>123.54</v>
+        <v>132.68</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>156.88</v>
+        <v>171</v>
       </c>
       <c r="K46" t="n">
-        <v>-121.82</v>
+        <v>-132.78</v>
       </c>
       <c r="L46" t="n">
-        <v>198.62</v>
+        <v>216.5</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-261.42</v>
+        <v>-282.43</v>
       </c>
       <c r="K47" t="n">
-        <v>271.19</v>
+        <v>292.99</v>
       </c>
       <c r="L47" t="n">
-        <v>376.67</v>
+        <v>406.95</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>183.86</v>
+        <v>198.77</v>
       </c>
       <c r="K48" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="L48" t="n">
-        <v>183.86</v>
+        <v>198.77</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>6.63</v>
+        <v>7.24</v>
       </c>
       <c r="K49" t="n">
-        <v>138.13</v>
+        <v>150.98</v>
       </c>
       <c r="L49" t="n">
-        <v>138.29</v>
+        <v>151.15</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-170.4</v>
+        <v>-191.24</v>
       </c>
       <c r="K50" t="n">
-        <v>205.42</v>
+        <v>230.54</v>
       </c>
       <c r="L50" t="n">
-        <v>266.9</v>
+        <v>299.53</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>75.55</v>
+        <v>87.3</v>
       </c>
       <c r="K51" t="n">
-        <v>-153.36</v>
+        <v>-177.22</v>
       </c>
       <c r="L51" t="n">
-        <v>170.96</v>
+        <v>197.56</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-277.67</v>
+        <v>-311.68</v>
       </c>
       <c r="K52" t="n">
-        <v>-14.41</v>
+        <v>-16.17</v>
       </c>
       <c r="L52" t="n">
-        <v>278.05</v>
+        <v>312.1</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-90.73999999999999</v>
+        <v>-107.09</v>
       </c>
       <c r="K53" t="n">
-        <v>-166.87</v>
+        <v>-196.94</v>
       </c>
       <c r="L53" t="n">
-        <v>189.95</v>
+        <v>224.17</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-360.07</v>
+        <v>-423.44</v>
       </c>
       <c r="K54" t="n">
-        <v>-106.34</v>
+        <v>-125.05</v>
       </c>
       <c r="L54" t="n">
-        <v>375.44</v>
+        <v>441.52</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>341.58</v>
+        <v>398.53</v>
       </c>
       <c r="K55" t="n">
-        <v>249.48</v>
+        <v>291.07</v>
       </c>
       <c r="L55" t="n">
-        <v>422.99</v>
+        <v>493.51</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-84.97</v>
+        <v>-101.15</v>
       </c>
       <c r="K56" t="n">
-        <v>-205.87</v>
+        <v>-245.06</v>
       </c>
       <c r="L56" t="n">
-        <v>222.71</v>
+        <v>265.11</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-545.65</v>
+        <v>-656.62</v>
       </c>
       <c r="K57" t="n">
-        <v>-28.17</v>
+        <v>-33.9</v>
       </c>
       <c r="L57" t="n">
-        <v>546.37</v>
+        <v>657.49</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-8.09</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>-754.85</v>
+        <v>-905.05</v>
       </c>
       <c r="L58" t="n">
-        <v>754.89</v>
+        <v>905.1</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>79.51000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-120.77</v>
+        <v>-133.05</v>
       </c>
       <c r="L59" t="n">
-        <v>144.59</v>
+        <v>159.29</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>185.68</v>
+        <v>201</v>
       </c>
       <c r="K60" t="n">
-        <v>49.65</v>
+        <v>53.75</v>
       </c>
       <c r="L60" t="n">
-        <v>192.21</v>
+        <v>208.06</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>129.71</v>
+        <v>143.07</v>
       </c>
       <c r="K61" t="n">
-        <v>-69.77</v>
+        <v>-76.95</v>
       </c>
       <c r="L61" t="n">
-        <v>147.29</v>
+        <v>162.46</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-139.54</v>
+        <v>-150.09</v>
       </c>
       <c r="K62" t="n">
-        <v>-99.65000000000001</v>
+        <v>-107.19</v>
       </c>
       <c r="L62" t="n">
-        <v>171.47</v>
+        <v>184.43</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>80.20999999999999</v>
+        <v>88.69</v>
       </c>
       <c r="K63" t="n">
-        <v>194.88</v>
+        <v>215.5</v>
       </c>
       <c r="L63" t="n">
-        <v>210.74</v>
+        <v>233.04</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>17.95</v>
+        <v>19.32</v>
       </c>
       <c r="K64" t="n">
-        <v>171.36</v>
+        <v>184.47</v>
       </c>
       <c r="L64" t="n">
-        <v>172.29</v>
+        <v>185.48</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>344.72</v>
+        <v>386.91</v>
       </c>
       <c r="K65" t="n">
-        <v>-110.28</v>
+        <v>-123.77</v>
       </c>
       <c r="L65" t="n">
-        <v>361.93</v>
+        <v>406.23</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-55.09</v>
+        <v>-62.78</v>
       </c>
       <c r="K66" t="n">
-        <v>-264.77</v>
+        <v>-301.69</v>
       </c>
       <c r="L66" t="n">
-        <v>270.44</v>
+        <v>308.16</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-125.62</v>
+        <v>-143.18</v>
       </c>
       <c r="K67" t="n">
-        <v>59.9</v>
+        <v>68.28</v>
       </c>
       <c r="L67" t="n">
-        <v>139.17</v>
+        <v>158.62</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-111.96</v>
+        <v>-130.39</v>
       </c>
       <c r="K68" t="n">
-        <v>225.38</v>
+        <v>262.48</v>
       </c>
       <c r="L68" t="n">
-        <v>251.65</v>
+        <v>293.08</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>228.69</v>
+        <v>268.75</v>
       </c>
       <c r="K69" t="n">
-        <v>-227.7</v>
+        <v>-267.58</v>
       </c>
       <c r="L69" t="n">
-        <v>322.72</v>
+        <v>379.25</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>20.92</v>
+        <v>24.13</v>
       </c>
       <c r="K70" t="n">
-        <v>218.5</v>
+        <v>252.02</v>
       </c>
       <c r="L70" t="n">
-        <v>219.5</v>
+        <v>253.17</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>27.46</v>
+        <v>32.44</v>
       </c>
       <c r="K71" t="n">
-        <v>-215.17</v>
+        <v>-254.18</v>
       </c>
       <c r="L71" t="n">
-        <v>216.91</v>
+        <v>256.24</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="K72" t="n">
-        <v>313.32</v>
+        <v>380.4</v>
       </c>
       <c r="L72" t="n">
-        <v>313.32</v>
+        <v>380.4</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-359.61</v>
+        <v>-432.26</v>
       </c>
       <c r="K73" t="n">
-        <v>267.69</v>
+        <v>321.77</v>
       </c>
       <c r="L73" t="n">
-        <v>448.3</v>
+        <v>538.87</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-128.22</v>
+        <v>-139.76</v>
       </c>
       <c r="K74" t="n">
-        <v>-24.73</v>
+        <v>-26.96</v>
       </c>
       <c r="L74" t="n">
-        <v>130.58</v>
+        <v>142.34</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>191.87</v>
+        <v>211.93</v>
       </c>
       <c r="K75" t="n">
-        <v>90.39</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>212.09</v>
+        <v>234.27</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-184.96</v>
+        <v>-204.82</v>
       </c>
       <c r="K76" t="n">
-        <v>145.36</v>
+        <v>160.96</v>
       </c>
       <c r="L76" t="n">
-        <v>235.24</v>
+        <v>260.5</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>161.57</v>
+        <v>178.42</v>
       </c>
       <c r="K77" t="n">
-        <v>-114.84</v>
+        <v>-126.83</v>
       </c>
       <c r="L77" t="n">
-        <v>198.22</v>
+        <v>218.9</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-204.5</v>
+        <v>-221.02</v>
       </c>
       <c r="K78" t="n">
-        <v>93.22</v>
+        <v>100.76</v>
       </c>
       <c r="L78" t="n">
-        <v>224.74</v>
+        <v>242.91</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-27.87</v>
+        <v>-30.29</v>
       </c>
       <c r="K79" t="n">
-        <v>-103.98</v>
+        <v>-113.02</v>
       </c>
       <c r="L79" t="n">
-        <v>107.65</v>
+        <v>117.01</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>352.42</v>
+        <v>407.25</v>
       </c>
       <c r="K80" t="n">
-        <v>-4.08</v>
+        <v>-4.72</v>
       </c>
       <c r="L80" t="n">
-        <v>352.45</v>
+        <v>407.28</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>262.88</v>
+        <v>303.46</v>
       </c>
       <c r="K81" t="n">
-        <v>-72.34999999999999</v>
+        <v>-83.52</v>
       </c>
       <c r="L81" t="n">
-        <v>272.65</v>
+        <v>314.75</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="K82" t="n">
-        <v>-253.97</v>
+        <v>-286.58</v>
       </c>
       <c r="L82" t="n">
-        <v>253.97</v>
+        <v>286.59</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>255.65</v>
+        <v>302.05</v>
       </c>
       <c r="K83" t="n">
-        <v>-11.16</v>
+        <v>-13.18</v>
       </c>
       <c r="L83" t="n">
-        <v>255.89</v>
+        <v>302.34</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>291.91</v>
+        <v>345.26</v>
       </c>
       <c r="K84" t="n">
-        <v>-49.41</v>
+        <v>-58.44</v>
       </c>
       <c r="L84" t="n">
-        <v>296.06</v>
+        <v>350.17</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>278.66</v>
+        <v>327.98</v>
       </c>
       <c r="K85" t="n">
-        <v>-339.62</v>
+        <v>-399.73</v>
       </c>
       <c r="L85" t="n">
-        <v>439.31</v>
+        <v>517.0700000000001</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-284.03</v>
+        <v>-347.02</v>
       </c>
       <c r="K86" t="n">
-        <v>-167.96</v>
+        <v>-205.21</v>
       </c>
       <c r="L86" t="n">
-        <v>329.97</v>
+        <v>403.16</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>376.33</v>
+        <v>448.87</v>
       </c>
       <c r="K87" t="n">
-        <v>507.88</v>
+        <v>605.78</v>
       </c>
       <c r="L87" t="n">
-        <v>632.11</v>
+        <v>753.96</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>318.78</v>
+        <v>376.43</v>
       </c>
       <c r="K88" t="n">
-        <v>377.1</v>
+        <v>445.29</v>
       </c>
       <c r="L88" t="n">
-        <v>493.79</v>
+        <v>583.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>101.54</v>
+        <v>44.17</v>
       </c>
       <c r="K14" t="n">
-        <v>25.66</v>
+        <v>11.16</v>
       </c>
       <c r="L14" t="n">
-        <v>104.73</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>194.32</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-34.01</v>
+        <v>-14.85</v>
       </c>
       <c r="L15" t="n">
-        <v>197.27</v>
+        <v>86.14</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-129.34</v>
+        <v>-60.03</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.82</v>
+        <v>-4.09</v>
       </c>
       <c r="L16" t="n">
-        <v>129.64</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>53.65</v>
+        <v>24.95</v>
       </c>
       <c r="K17" t="n">
-        <v>-131.09</v>
+        <v>-60.97</v>
       </c>
       <c r="L17" t="n">
-        <v>141.65</v>
+        <v>65.88</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-111.35</v>
+        <v>-52.81</v>
       </c>
       <c r="K18" t="n">
-        <v>-78.67</v>
+        <v>-37.31</v>
       </c>
       <c r="L18" t="n">
-        <v>136.34</v>
+        <v>64.66</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>188.07</v>
+        <v>81.89</v>
       </c>
       <c r="K19" t="n">
-        <v>156.89</v>
+        <v>68.31</v>
       </c>
       <c r="L19" t="n">
-        <v>244.91</v>
+        <v>106.64</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-117.86</v>
+        <v>-56.59</v>
       </c>
       <c r="K20" t="n">
-        <v>-225.66</v>
+        <v>-108.35</v>
       </c>
       <c r="L20" t="n">
-        <v>254.59</v>
+        <v>122.24</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-251.69</v>
+        <v>-120.15</v>
       </c>
       <c r="K21" t="n">
-        <v>261.38</v>
+        <v>124.77</v>
       </c>
       <c r="L21" t="n">
-        <v>362.86</v>
+        <v>173.21</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-114.12</v>
+        <v>-57.62</v>
       </c>
       <c r="K22" t="n">
-        <v>233.04</v>
+        <v>117.67</v>
       </c>
       <c r="L22" t="n">
-        <v>259.48</v>
+        <v>131.02</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-329.59</v>
+        <v>-151.68</v>
       </c>
       <c r="K23" t="n">
-        <v>269.9</v>
+        <v>124.21</v>
       </c>
       <c r="L23" t="n">
-        <v>426</v>
+        <v>196.05</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>254.52</v>
+        <v>116.94</v>
       </c>
       <c r="K24" t="n">
-        <v>155.56</v>
+        <v>71.47</v>
       </c>
       <c r="L24" t="n">
-        <v>298.29</v>
+        <v>137.05</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-88.5</v>
+        <v>-42.23</v>
       </c>
       <c r="K25" t="n">
-        <v>253.02</v>
+        <v>120.75</v>
       </c>
       <c r="L25" t="n">
-        <v>268.05</v>
+        <v>127.93</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-357.97</v>
+        <v>-191.73</v>
       </c>
       <c r="K26" t="n">
-        <v>80.43000000000001</v>
+        <v>43.08</v>
       </c>
       <c r="L26" t="n">
-        <v>366.9</v>
+        <v>196.51</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-219.87</v>
+        <v>-119</v>
       </c>
       <c r="K27" t="n">
-        <v>-406.66</v>
+        <v>-220.1</v>
       </c>
       <c r="L27" t="n">
-        <v>462.29</v>
+        <v>250.21</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-517.95</v>
+        <v>-274.84</v>
       </c>
       <c r="K28" t="n">
-        <v>198.39</v>
+        <v>105.27</v>
       </c>
       <c r="L28" t="n">
-        <v>554.65</v>
+        <v>294.31</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-117.16</v>
+        <v>-54.84</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.68</v>
+        <v>-0.32</v>
       </c>
       <c r="L29" t="n">
-        <v>117.16</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>129.28</v>
+        <v>51.33</v>
       </c>
       <c r="K30" t="n">
-        <v>-18.36</v>
+        <v>-7.29</v>
       </c>
       <c r="L30" t="n">
-        <v>130.58</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>190.87</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>48.71</v>
+        <v>21.43</v>
       </c>
       <c r="L31" t="n">
-        <v>196.99</v>
+        <v>86.68000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>46.18</v>
+        <v>19.99</v>
       </c>
       <c r="K32" t="n">
-        <v>-170.35</v>
+        <v>-73.73</v>
       </c>
       <c r="L32" t="n">
-        <v>176.5</v>
+        <v>76.39</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.6</v>
+        <v>-0.7</v>
       </c>
       <c r="K33" t="n">
-        <v>157.18</v>
+        <v>68.64</v>
       </c>
       <c r="L33" t="n">
-        <v>157.18</v>
+        <v>68.65000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-172.35</v>
+        <v>-74.17</v>
       </c>
       <c r="K34" t="n">
-        <v>44.67</v>
+        <v>19.22</v>
       </c>
       <c r="L34" t="n">
-        <v>178.05</v>
+        <v>76.62</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-139.96</v>
+        <v>-66.94</v>
       </c>
       <c r="K35" t="n">
-        <v>198.53</v>
+        <v>94.95</v>
       </c>
       <c r="L35" t="n">
-        <v>242.91</v>
+        <v>116.17</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-133.21</v>
+        <v>-64.53</v>
       </c>
       <c r="K36" t="n">
-        <v>-168.89</v>
+        <v>-81.81999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>215.1</v>
+        <v>104.2</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-159.47</v>
+        <v>-76.73</v>
       </c>
       <c r="K37" t="n">
-        <v>298.3</v>
+        <v>143.52</v>
       </c>
       <c r="L37" t="n">
-        <v>338.25</v>
+        <v>162.75</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-227.98</v>
+        <v>-103.88</v>
       </c>
       <c r="K38" t="n">
-        <v>314.95</v>
+        <v>143.5</v>
       </c>
       <c r="L38" t="n">
-        <v>388.81</v>
+        <v>177.15</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-650.7</v>
+        <v>-299.97</v>
       </c>
       <c r="K39" t="n">
-        <v>102.4</v>
+        <v>47.2</v>
       </c>
       <c r="L39" t="n">
-        <v>658.71</v>
+        <v>303.66</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>418.73</v>
+        <v>182.51</v>
       </c>
       <c r="K40" t="n">
-        <v>357.15</v>
+        <v>155.67</v>
       </c>
       <c r="L40" t="n">
-        <v>550.36</v>
+        <v>239.88</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>260.57</v>
+        <v>139.04</v>
       </c>
       <c r="K41" t="n">
-        <v>398.69</v>
+        <v>212.74</v>
       </c>
       <c r="L41" t="n">
-        <v>476.29</v>
+        <v>254.15</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>628.27</v>
+        <v>331.71</v>
       </c>
       <c r="K42" t="n">
-        <v>-314.54</v>
+        <v>-166.07</v>
       </c>
       <c r="L42" t="n">
-        <v>702.61</v>
+        <v>370.96</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>526.1900000000001</v>
+        <v>279.58</v>
       </c>
       <c r="K43" t="n">
-        <v>45.62</v>
+        <v>24.24</v>
       </c>
       <c r="L43" t="n">
-        <v>528.16</v>
+        <v>280.63</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>61.3</v>
+        <v>25.56</v>
       </c>
       <c r="K44" t="n">
-        <v>184.58</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>194.49</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>115.23</v>
+        <v>45.98</v>
       </c>
       <c r="K45" t="n">
-        <v>65.76000000000001</v>
+        <v>26.24</v>
       </c>
       <c r="L45" t="n">
-        <v>132.68</v>
+        <v>52.94</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>171</v>
+        <v>69.83</v>
       </c>
       <c r="K46" t="n">
-        <v>-132.78</v>
+        <v>-54.23</v>
       </c>
       <c r="L46" t="n">
-        <v>216.5</v>
+        <v>88.42</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-282.43</v>
+        <v>-118.17</v>
       </c>
       <c r="K47" t="n">
-        <v>292.99</v>
+        <v>122.58</v>
       </c>
       <c r="L47" t="n">
-        <v>406.95</v>
+        <v>170.27</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>198.77</v>
+        <v>89.41</v>
       </c>
       <c r="K48" t="n">
-        <v>1.19</v>
+        <v>0.54</v>
       </c>
       <c r="L48" t="n">
-        <v>198.77</v>
+        <v>89.41</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>7.24</v>
+        <v>3.3</v>
       </c>
       <c r="K49" t="n">
-        <v>150.98</v>
+        <v>68.81</v>
       </c>
       <c r="L49" t="n">
-        <v>151.15</v>
+        <v>68.89</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-191.24</v>
+        <v>-91.86</v>
       </c>
       <c r="K50" t="n">
-        <v>230.54</v>
+        <v>110.74</v>
       </c>
       <c r="L50" t="n">
-        <v>299.53</v>
+        <v>143.88</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>87.3</v>
+        <v>42.04</v>
       </c>
       <c r="K51" t="n">
-        <v>-177.22</v>
+        <v>-85.34</v>
       </c>
       <c r="L51" t="n">
-        <v>197.56</v>
+        <v>95.13</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-311.68</v>
+        <v>-149.29</v>
       </c>
       <c r="K52" t="n">
-        <v>-16.17</v>
+        <v>-7.75</v>
       </c>
       <c r="L52" t="n">
-        <v>312.1</v>
+        <v>149.49</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-107.09</v>
+        <v>-38.8</v>
       </c>
       <c r="K53" t="n">
-        <v>-196.94</v>
+        <v>-71.36</v>
       </c>
       <c r="L53" t="n">
-        <v>224.17</v>
+        <v>81.23</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-423.44</v>
+        <v>-191.68</v>
       </c>
       <c r="K54" t="n">
-        <v>-125.05</v>
+        <v>-56.61</v>
       </c>
       <c r="L54" t="n">
-        <v>441.52</v>
+        <v>199.86</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>398.53</v>
+        <v>175.27</v>
       </c>
       <c r="K55" t="n">
-        <v>291.07</v>
+        <v>128.01</v>
       </c>
       <c r="L55" t="n">
-        <v>493.51</v>
+        <v>217.04</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-101.15</v>
+        <v>-54.13</v>
       </c>
       <c r="K56" t="n">
-        <v>-245.06</v>
+        <v>-131.14</v>
       </c>
       <c r="L56" t="n">
-        <v>265.11</v>
+        <v>141.88</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-656.62</v>
+        <v>-351.63</v>
       </c>
       <c r="K57" t="n">
-        <v>-33.9</v>
+        <v>-18.16</v>
       </c>
       <c r="L57" t="n">
-        <v>657.49</v>
+        <v>352.09</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-9.710000000000001</v>
+        <v>-5.18</v>
       </c>
       <c r="K58" t="n">
-        <v>-905.05</v>
+        <v>-482.81</v>
       </c>
       <c r="L58" t="n">
-        <v>905.1</v>
+        <v>482.84</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>87.59999999999999</v>
+        <v>35.13</v>
       </c>
       <c r="K59" t="n">
-        <v>-133.05</v>
+        <v>-53.36</v>
       </c>
       <c r="L59" t="n">
-        <v>159.29</v>
+        <v>63.89</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>201</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>53.75</v>
+        <v>21.58</v>
       </c>
       <c r="L60" t="n">
-        <v>208.06</v>
+        <v>83.52</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>143.07</v>
+        <v>57</v>
       </c>
       <c r="K61" t="n">
-        <v>-76.95</v>
+        <v>-30.66</v>
       </c>
       <c r="L61" t="n">
-        <v>162.46</v>
+        <v>64.72</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-150.09</v>
+        <v>-67.3</v>
       </c>
       <c r="K62" t="n">
-        <v>-107.19</v>
+        <v>-48.06</v>
       </c>
       <c r="L62" t="n">
-        <v>184.43</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>88.69</v>
+        <v>37.74</v>
       </c>
       <c r="K63" t="n">
-        <v>215.5</v>
+        <v>91.69</v>
       </c>
       <c r="L63" t="n">
-        <v>233.04</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>19.32</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>184.47</v>
+        <v>77.5</v>
       </c>
       <c r="L64" t="n">
-        <v>185.48</v>
+        <v>77.92</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>386.91</v>
+        <v>184.98</v>
       </c>
       <c r="K65" t="n">
-        <v>-123.77</v>
+        <v>-59.18</v>
       </c>
       <c r="L65" t="n">
-        <v>406.23</v>
+        <v>194.22</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-62.78</v>
+        <v>-29.99</v>
       </c>
       <c r="K66" t="n">
-        <v>-301.69</v>
+        <v>-144.15</v>
       </c>
       <c r="L66" t="n">
-        <v>308.16</v>
+        <v>147.24</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-143.18</v>
+        <v>-68.92</v>
       </c>
       <c r="K67" t="n">
-        <v>68.28</v>
+        <v>32.86</v>
       </c>
       <c r="L67" t="n">
-        <v>158.62</v>
+        <v>76.34999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-130.39</v>
+        <v>-59.05</v>
       </c>
       <c r="K68" t="n">
-        <v>262.48</v>
+        <v>118.88</v>
       </c>
       <c r="L68" t="n">
-        <v>293.08</v>
+        <v>132.74</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>268.75</v>
+        <v>117.09</v>
       </c>
       <c r="K69" t="n">
-        <v>-267.58</v>
+        <v>-116.58</v>
       </c>
       <c r="L69" t="n">
-        <v>379.25</v>
+        <v>165.23</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>24.13</v>
+        <v>11.58</v>
       </c>
       <c r="K70" t="n">
-        <v>252.02</v>
+        <v>120.92</v>
       </c>
       <c r="L70" t="n">
-        <v>253.17</v>
+        <v>121.48</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>32.44</v>
+        <v>17.38</v>
       </c>
       <c r="K71" t="n">
-        <v>-254.18</v>
+        <v>-136.2</v>
       </c>
       <c r="L71" t="n">
-        <v>256.24</v>
+        <v>137.3</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="K72" t="n">
-        <v>380.4</v>
+        <v>200.84</v>
       </c>
       <c r="L72" t="n">
-        <v>380.4</v>
+        <v>200.84</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-432.26</v>
+        <v>-233.02</v>
       </c>
       <c r="K73" t="n">
-        <v>321.77</v>
+        <v>173.45</v>
       </c>
       <c r="L73" t="n">
-        <v>538.87</v>
+        <v>290.49</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-139.76</v>
+        <v>-56.51</v>
       </c>
       <c r="K74" t="n">
-        <v>-26.96</v>
+        <v>-10.9</v>
       </c>
       <c r="L74" t="n">
-        <v>142.34</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>211.93</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>99.84999999999999</v>
+        <v>40.3</v>
       </c>
       <c r="L75" t="n">
-        <v>234.27</v>
+        <v>94.56</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-204.82</v>
+        <v>-82.98</v>
       </c>
       <c r="K76" t="n">
-        <v>160.96</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>260.5</v>
+        <v>105.53</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>178.42</v>
+        <v>75.16</v>
       </c>
       <c r="K77" t="n">
-        <v>-126.83</v>
+        <v>-53.43</v>
       </c>
       <c r="L77" t="n">
-        <v>218.9</v>
+        <v>92.22</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-221.02</v>
+        <v>-92.88</v>
       </c>
       <c r="K78" t="n">
-        <v>100.76</v>
+        <v>42.34</v>
       </c>
       <c r="L78" t="n">
-        <v>242.91</v>
+        <v>102.08</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-30.29</v>
+        <v>-5.75</v>
       </c>
       <c r="K79" t="n">
-        <v>-113.02</v>
+        <v>-21.47</v>
       </c>
       <c r="L79" t="n">
-        <v>117.01</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>407.25</v>
+        <v>194.9</v>
       </c>
       <c r="K80" t="n">
-        <v>-4.72</v>
+        <v>-2.26</v>
       </c>
       <c r="L80" t="n">
-        <v>407.28</v>
+        <v>194.91</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>303.46</v>
+        <v>145.28</v>
       </c>
       <c r="K81" t="n">
-        <v>-83.52</v>
+        <v>-39.98</v>
       </c>
       <c r="L81" t="n">
-        <v>314.75</v>
+        <v>150.68</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>1.77</v>
+        <v>0.85</v>
       </c>
       <c r="K82" t="n">
-        <v>-286.58</v>
+        <v>-136.87</v>
       </c>
       <c r="L82" t="n">
-        <v>286.59</v>
+        <v>136.87</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>302.05</v>
+        <v>132.21</v>
       </c>
       <c r="K83" t="n">
-        <v>-13.18</v>
+        <v>-5.77</v>
       </c>
       <c r="L83" t="n">
-        <v>302.34</v>
+        <v>132.34</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>345.26</v>
+        <v>152.49</v>
       </c>
       <c r="K84" t="n">
-        <v>-58.44</v>
+        <v>-25.81</v>
       </c>
       <c r="L84" t="n">
-        <v>350.17</v>
+        <v>154.66</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>327.98</v>
+        <v>147.25</v>
       </c>
       <c r="K85" t="n">
-        <v>-399.73</v>
+        <v>-179.46</v>
       </c>
       <c r="L85" t="n">
-        <v>517.0700000000001</v>
+        <v>232.14</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-347.02</v>
+        <v>-184.51</v>
       </c>
       <c r="K86" t="n">
-        <v>-205.21</v>
+        <v>-109.11</v>
       </c>
       <c r="L86" t="n">
-        <v>403.16</v>
+        <v>214.36</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>448.87</v>
+        <v>238.82</v>
       </c>
       <c r="K87" t="n">
-        <v>605.78</v>
+        <v>322.31</v>
       </c>
       <c r="L87" t="n">
-        <v>753.96</v>
+        <v>401.15</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>376.43</v>
+        <v>200.94</v>
       </c>
       <c r="K88" t="n">
-        <v>445.29</v>
+        <v>237.7</v>
       </c>
       <c r="L88" t="n">
-        <v>583.08</v>
+        <v>311.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>44.17</v>
+        <v>46.05</v>
       </c>
       <c r="K14" t="n">
-        <v>11.16</v>
+        <v>11.64</v>
       </c>
       <c r="L14" t="n">
-        <v>45.56</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>84.84999999999999</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.85</v>
+        <v>-14.08</v>
       </c>
       <c r="L15" t="n">
-        <v>86.14</v>
+        <v>81.68000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-60.03</v>
+        <v>-59.42</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.09</v>
+        <v>-4.05</v>
       </c>
       <c r="L16" t="n">
-        <v>60.16</v>
+        <v>59.55</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>24.95</v>
+        <v>25.32</v>
       </c>
       <c r="K17" t="n">
-        <v>-60.97</v>
+        <v>-61.86</v>
       </c>
       <c r="L17" t="n">
-        <v>65.88</v>
+        <v>66.84</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-52.81</v>
+        <v>-53.22</v>
       </c>
       <c r="K18" t="n">
-        <v>-37.31</v>
+        <v>-37.6</v>
       </c>
       <c r="L18" t="n">
-        <v>64.66</v>
+        <v>65.16</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>81.89</v>
+        <v>77.38</v>
       </c>
       <c r="K19" t="n">
-        <v>68.31</v>
+        <v>64.55</v>
       </c>
       <c r="L19" t="n">
-        <v>106.64</v>
+        <v>100.76</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-56.59</v>
+        <v>-56.11</v>
       </c>
       <c r="K20" t="n">
-        <v>-108.35</v>
+        <v>-107.44</v>
       </c>
       <c r="L20" t="n">
-        <v>122.24</v>
+        <v>121.21</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-120.15</v>
+        <v>-115.3</v>
       </c>
       <c r="K21" t="n">
-        <v>124.77</v>
+        <v>119.73</v>
       </c>
       <c r="L21" t="n">
-        <v>173.21</v>
+        <v>166.22</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-57.62</v>
+        <v>-56.46</v>
       </c>
       <c r="K22" t="n">
-        <v>117.67</v>
+        <v>115.3</v>
       </c>
       <c r="L22" t="n">
-        <v>131.02</v>
+        <v>128.39</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-151.68</v>
+        <v>-149.64</v>
       </c>
       <c r="K23" t="n">
-        <v>124.21</v>
+        <v>122.54</v>
       </c>
       <c r="L23" t="n">
-        <v>196.05</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>116.94</v>
+        <v>121.2</v>
       </c>
       <c r="K24" t="n">
-        <v>71.47</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>137.05</v>
+        <v>142.04</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-42.23</v>
+        <v>-43.93</v>
       </c>
       <c r="K25" t="n">
-        <v>120.75</v>
+        <v>125.59</v>
       </c>
       <c r="L25" t="n">
-        <v>127.93</v>
+        <v>133.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-191.73</v>
+        <v>-211.66</v>
       </c>
       <c r="K26" t="n">
-        <v>43.08</v>
+        <v>47.56</v>
       </c>
       <c r="L26" t="n">
-        <v>196.51</v>
+        <v>216.94</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-119</v>
+        <v>-123.72</v>
       </c>
       <c r="K27" t="n">
-        <v>-220.1</v>
+        <v>-228.84</v>
       </c>
       <c r="L27" t="n">
-        <v>250.21</v>
+        <v>260.14</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-274.84</v>
+        <v>-297.83</v>
       </c>
       <c r="K28" t="n">
-        <v>105.27</v>
+        <v>114.08</v>
       </c>
       <c r="L28" t="n">
-        <v>294.31</v>
+        <v>318.93</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-54.84</v>
+        <v>-56.42</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="L29" t="n">
-        <v>54.84</v>
+        <v>56.42</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>51.33</v>
+        <v>52.06</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.29</v>
+        <v>-7.39</v>
       </c>
       <c r="L30" t="n">
-        <v>51.85</v>
+        <v>52.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>83.98999999999999</v>
+        <v>80.03</v>
       </c>
       <c r="K31" t="n">
-        <v>21.43</v>
+        <v>20.42</v>
       </c>
       <c r="L31" t="n">
-        <v>86.68000000000001</v>
+        <v>82.59</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>19.99</v>
+        <v>19.9</v>
       </c>
       <c r="K32" t="n">
-        <v>-73.73</v>
+        <v>-73.41</v>
       </c>
       <c r="L32" t="n">
-        <v>76.39</v>
+        <v>76.05</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="K33" t="n">
-        <v>68.64</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>68.65000000000001</v>
+        <v>69.54000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-74.17</v>
+        <v>-73.3</v>
       </c>
       <c r="K34" t="n">
-        <v>19.22</v>
+        <v>19</v>
       </c>
       <c r="L34" t="n">
-        <v>76.62</v>
+        <v>75.72</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-66.94</v>
+        <v>-68.39</v>
       </c>
       <c r="K35" t="n">
-        <v>94.95</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>116.17</v>
+        <v>118.69</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-64.53</v>
+        <v>-65.66</v>
       </c>
       <c r="K36" t="n">
-        <v>-81.81999999999999</v>
+        <v>-83.25</v>
       </c>
       <c r="L36" t="n">
-        <v>104.2</v>
+        <v>106.02</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-76.73</v>
+        <v>-74.59</v>
       </c>
       <c r="K37" t="n">
-        <v>143.52</v>
+        <v>139.54</v>
       </c>
       <c r="L37" t="n">
-        <v>162.75</v>
+        <v>158.22</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-103.88</v>
+        <v>-103.64</v>
       </c>
       <c r="K38" t="n">
-        <v>143.5</v>
+        <v>143.18</v>
       </c>
       <c r="L38" t="n">
-        <v>177.15</v>
+        <v>176.75</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-299.97</v>
+        <v>-286.21</v>
       </c>
       <c r="K39" t="n">
-        <v>47.2</v>
+        <v>45.04</v>
       </c>
       <c r="L39" t="n">
-        <v>303.66</v>
+        <v>289.73</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>182.51</v>
+        <v>187.36</v>
       </c>
       <c r="K40" t="n">
-        <v>155.67</v>
+        <v>159.81</v>
       </c>
       <c r="L40" t="n">
-        <v>239.88</v>
+        <v>246.26</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>139.04</v>
+        <v>150.14</v>
       </c>
       <c r="K41" t="n">
-        <v>212.74</v>
+        <v>229.72</v>
       </c>
       <c r="L41" t="n">
-        <v>254.15</v>
+        <v>274.43</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>331.71</v>
+        <v>360.39</v>
       </c>
       <c r="K42" t="n">
-        <v>-166.07</v>
+        <v>-180.42</v>
       </c>
       <c r="L42" t="n">
-        <v>370.96</v>
+        <v>403.03</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>279.58</v>
+        <v>315.99</v>
       </c>
       <c r="K43" t="n">
-        <v>24.24</v>
+        <v>27.4</v>
       </c>
       <c r="L43" t="n">
-        <v>280.63</v>
+        <v>317.17</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>25.56</v>
+        <v>24.56</v>
       </c>
       <c r="K44" t="n">
-        <v>76.95999999999999</v>
+        <v>73.94</v>
       </c>
       <c r="L44" t="n">
-        <v>81.09999999999999</v>
+        <v>77.92</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>45.98</v>
+        <v>46.2</v>
       </c>
       <c r="K45" t="n">
-        <v>26.24</v>
+        <v>26.37</v>
       </c>
       <c r="L45" t="n">
-        <v>52.94</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>69.83</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-54.23</v>
+        <v>-51.45</v>
       </c>
       <c r="L46" t="n">
-        <v>88.42</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-118.17</v>
+        <v>-107</v>
       </c>
       <c r="K47" t="n">
-        <v>122.58</v>
+        <v>111</v>
       </c>
       <c r="L47" t="n">
-        <v>170.27</v>
+        <v>154.18</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>89.41</v>
+        <v>86.37</v>
       </c>
       <c r="K48" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="L48" t="n">
-        <v>89.41</v>
+        <v>86.37</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="K49" t="n">
-        <v>68.81</v>
+        <v>69.31</v>
       </c>
       <c r="L49" t="n">
-        <v>68.89</v>
+        <v>69.39</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-91.86</v>
+        <v>-90.28</v>
       </c>
       <c r="K50" t="n">
-        <v>110.74</v>
+        <v>108.83</v>
       </c>
       <c r="L50" t="n">
-        <v>143.88</v>
+        <v>141.4</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>42.04</v>
+        <v>44.37</v>
       </c>
       <c r="K51" t="n">
-        <v>-85.34</v>
+        <v>-90.06999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>95.13</v>
+        <v>100.4</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-149.29</v>
+        <v>-145.4</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.75</v>
+        <v>-7.54</v>
       </c>
       <c r="L52" t="n">
-        <v>149.49</v>
+        <v>145.59</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-38.8</v>
+        <v>-40.03</v>
       </c>
       <c r="K53" t="n">
-        <v>-71.36</v>
+        <v>-73.61</v>
       </c>
       <c r="L53" t="n">
-        <v>81.23</v>
+        <v>83.79000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-191.68</v>
+        <v>-207.68</v>
       </c>
       <c r="K54" t="n">
-        <v>-56.61</v>
+        <v>-61.33</v>
       </c>
       <c r="L54" t="n">
-        <v>199.86</v>
+        <v>216.55</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>175.27</v>
+        <v>182.69</v>
       </c>
       <c r="K55" t="n">
-        <v>128.01</v>
+        <v>133.43</v>
       </c>
       <c r="L55" t="n">
-        <v>217.04</v>
+        <v>226.23</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-54.13</v>
+        <v>-63.08</v>
       </c>
       <c r="K56" t="n">
-        <v>-131.14</v>
+        <v>-152.84</v>
       </c>
       <c r="L56" t="n">
-        <v>141.88</v>
+        <v>165.35</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-351.63</v>
+        <v>-397.42</v>
       </c>
       <c r="K57" t="n">
-        <v>-18.16</v>
+        <v>-20.52</v>
       </c>
       <c r="L57" t="n">
-        <v>352.09</v>
+        <v>397.95</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.18</v>
+        <v>-5.63</v>
       </c>
       <c r="K58" t="n">
-        <v>-482.81</v>
+        <v>-525.23</v>
       </c>
       <c r="L58" t="n">
-        <v>482.84</v>
+        <v>525.26</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>35.13</v>
+        <v>32.16</v>
       </c>
       <c r="K59" t="n">
-        <v>-53.36</v>
+        <v>-48.85</v>
       </c>
       <c r="L59" t="n">
-        <v>63.89</v>
+        <v>58.49</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>80.68000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="K60" t="n">
-        <v>21.58</v>
+        <v>18.74</v>
       </c>
       <c r="L60" t="n">
-        <v>83.52</v>
+        <v>72.55</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>57</v>
+        <v>54.75</v>
       </c>
       <c r="K61" t="n">
-        <v>-30.66</v>
+        <v>-29.45</v>
       </c>
       <c r="L61" t="n">
-        <v>64.72</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-67.3</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-48.06</v>
+        <v>-46.61</v>
       </c>
       <c r="L62" t="n">
-        <v>82.7</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>37.74</v>
+        <v>32.77</v>
       </c>
       <c r="K63" t="n">
-        <v>91.69</v>
+        <v>79.62</v>
       </c>
       <c r="L63" t="n">
-        <v>99.15000000000001</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>8.119999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="K64" t="n">
-        <v>77.5</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>77.92</v>
+        <v>75.67</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>184.98</v>
+        <v>175.22</v>
       </c>
       <c r="K65" t="n">
-        <v>-59.18</v>
+        <v>-56.05</v>
       </c>
       <c r="L65" t="n">
-        <v>194.22</v>
+        <v>183.96</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-29.99</v>
+        <v>-29.36</v>
       </c>
       <c r="K66" t="n">
-        <v>-144.15</v>
+        <v>-141.12</v>
       </c>
       <c r="L66" t="n">
-        <v>147.24</v>
+        <v>144.14</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-68.92</v>
+        <v>-74.48999999999999</v>
       </c>
       <c r="K67" t="n">
-        <v>32.86</v>
+        <v>35.52</v>
       </c>
       <c r="L67" t="n">
-        <v>76.34999999999999</v>
+        <v>82.52</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-59.05</v>
+        <v>-67.31999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>118.88</v>
+        <v>135.51</v>
       </c>
       <c r="L68" t="n">
-        <v>132.74</v>
+        <v>151.31</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>117.09</v>
+        <v>124.33</v>
       </c>
       <c r="K69" t="n">
-        <v>-116.58</v>
+        <v>-123.79</v>
       </c>
       <c r="L69" t="n">
-        <v>165.23</v>
+        <v>175.45</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>11.58</v>
+        <v>12.06</v>
       </c>
       <c r="K70" t="n">
-        <v>120.92</v>
+        <v>125.99</v>
       </c>
       <c r="L70" t="n">
-        <v>121.48</v>
+        <v>126.57</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>17.38</v>
+        <v>20.09</v>
       </c>
       <c r="K71" t="n">
-        <v>-136.2</v>
+        <v>-157.43</v>
       </c>
       <c r="L71" t="n">
-        <v>137.3</v>
+        <v>158.71</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="K72" t="n">
-        <v>200.84</v>
+        <v>234.89</v>
       </c>
       <c r="L72" t="n">
-        <v>200.84</v>
+        <v>234.9</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-233.02</v>
+        <v>-272.59</v>
       </c>
       <c r="K73" t="n">
-        <v>173.45</v>
+        <v>202.91</v>
       </c>
       <c r="L73" t="n">
-        <v>290.49</v>
+        <v>339.83</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-56.51</v>
+        <v>-49.44</v>
       </c>
       <c r="K74" t="n">
-        <v>-10.9</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>57.55</v>
+        <v>50.35</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>85.54000000000001</v>
+        <v>80.75</v>
       </c>
       <c r="K75" t="n">
-        <v>40.3</v>
+        <v>38.04</v>
       </c>
       <c r="L75" t="n">
-        <v>94.56</v>
+        <v>89.27</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-82.98</v>
+        <v>-65.91</v>
       </c>
       <c r="K76" t="n">
-        <v>65.20999999999999</v>
+        <v>51.8</v>
       </c>
       <c r="L76" t="n">
-        <v>105.53</v>
+        <v>83.81999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>75.16</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-53.43</v>
+        <v>-48.92</v>
       </c>
       <c r="L77" t="n">
-        <v>92.22</v>
+        <v>84.43000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-92.88</v>
+        <v>-83.44</v>
       </c>
       <c r="K78" t="n">
-        <v>42.34</v>
+        <v>38.04</v>
       </c>
       <c r="L78" t="n">
-        <v>102.08</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.75</v>
+        <v>-5.06</v>
       </c>
       <c r="K79" t="n">
-        <v>-21.47</v>
+        <v>-18.88</v>
       </c>
       <c r="L79" t="n">
-        <v>22.22</v>
+        <v>19.55</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>194.9</v>
+        <v>188</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.26</v>
+        <v>-2.18</v>
       </c>
       <c r="L80" t="n">
-        <v>194.91</v>
+        <v>188.01</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>145.28</v>
+        <v>145.26</v>
       </c>
       <c r="K81" t="n">
         <v>-39.98</v>
       </c>
       <c r="L81" t="n">
-        <v>150.68</v>
+        <v>150.66</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="K82" t="n">
-        <v>-136.87</v>
+        <v>-134.82</v>
       </c>
       <c r="L82" t="n">
-        <v>136.87</v>
+        <v>134.83</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>132.21</v>
+        <v>145.36</v>
       </c>
       <c r="K83" t="n">
-        <v>-5.77</v>
+        <v>-6.34</v>
       </c>
       <c r="L83" t="n">
-        <v>132.34</v>
+        <v>145.5</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>152.49</v>
+        <v>168.02</v>
       </c>
       <c r="K84" t="n">
-        <v>-25.81</v>
+        <v>-28.44</v>
       </c>
       <c r="L84" t="n">
-        <v>154.66</v>
+        <v>170.41</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>147.25</v>
+        <v>144.87</v>
       </c>
       <c r="K85" t="n">
-        <v>-179.46</v>
+        <v>-176.57</v>
       </c>
       <c r="L85" t="n">
-        <v>232.14</v>
+        <v>228.4</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-184.51</v>
+        <v>-220.22</v>
       </c>
       <c r="K86" t="n">
-        <v>-109.11</v>
+        <v>-130.22</v>
       </c>
       <c r="L86" t="n">
-        <v>214.36</v>
+        <v>255.84</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>238.82</v>
+        <v>261.52</v>
       </c>
       <c r="K87" t="n">
-        <v>322.31</v>
+        <v>352.94</v>
       </c>
       <c r="L87" t="n">
-        <v>401.15</v>
+        <v>439.27</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>200.94</v>
+        <v>226.5</v>
       </c>
       <c r="K88" t="n">
-        <v>237.7</v>
+        <v>267.93</v>
       </c>
       <c r="L88" t="n">
-        <v>311.25</v>
+        <v>350.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>46.05</v>
+        <v>49.56</v>
       </c>
       <c r="K14" t="n">
-        <v>11.64</v>
+        <v>12.53</v>
       </c>
       <c r="L14" t="n">
-        <v>47.5</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>80.45999999999999</v>
+        <v>78.08</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.08</v>
+        <v>-13.67</v>
       </c>
       <c r="L15" t="n">
-        <v>81.68000000000001</v>
+        <v>79.26000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-59.42</v>
+        <v>-60.02</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.05</v>
+        <v>-4.09</v>
       </c>
       <c r="L16" t="n">
-        <v>59.55</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>25.32</v>
+        <v>26.34</v>
       </c>
       <c r="K17" t="n">
-        <v>-61.86</v>
+        <v>-64.34999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>66.84</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-53.22</v>
+        <v>-54.78</v>
       </c>
       <c r="K18" t="n">
-        <v>-37.6</v>
+        <v>-38.7</v>
       </c>
       <c r="L18" t="n">
-        <v>65.16</v>
+        <v>67.06999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>77.38</v>
+        <v>75.19</v>
       </c>
       <c r="K19" t="n">
-        <v>64.55</v>
+        <v>62.73</v>
       </c>
       <c r="L19" t="n">
-        <v>100.76</v>
+        <v>97.92</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-56.11</v>
+        <v>-56.39</v>
       </c>
       <c r="K20" t="n">
-        <v>-107.44</v>
+        <v>-107.96</v>
       </c>
       <c r="L20" t="n">
-        <v>121.21</v>
+        <v>121.8</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-115.3</v>
+        <v>-112</v>
       </c>
       <c r="K21" t="n">
-        <v>119.73</v>
+        <v>116.31</v>
       </c>
       <c r="L21" t="n">
-        <v>166.22</v>
+        <v>161.47</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-56.46</v>
+        <v>-55.38</v>
       </c>
       <c r="K22" t="n">
-        <v>115.3</v>
+        <v>113.1</v>
       </c>
       <c r="L22" t="n">
-        <v>128.39</v>
+        <v>125.93</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-149.64</v>
+        <v>-145.89</v>
       </c>
       <c r="K23" t="n">
-        <v>122.54</v>
+        <v>119.47</v>
       </c>
       <c r="L23" t="n">
-        <v>193.41</v>
+        <v>188.57</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>121.2</v>
+        <v>124.99</v>
       </c>
       <c r="K24" t="n">
-        <v>74.06999999999999</v>
+        <v>76.39</v>
       </c>
       <c r="L24" t="n">
-        <v>142.04</v>
+        <v>146.48</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-43.93</v>
+        <v>-45.54</v>
       </c>
       <c r="K25" t="n">
-        <v>125.59</v>
+        <v>130.21</v>
       </c>
       <c r="L25" t="n">
-        <v>133.05</v>
+        <v>137.95</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-211.66</v>
+        <v>-222.09</v>
       </c>
       <c r="K26" t="n">
-        <v>47.56</v>
+        <v>49.9</v>
       </c>
       <c r="L26" t="n">
-        <v>216.94</v>
+        <v>227.62</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-123.72</v>
+        <v>-123.25</v>
       </c>
       <c r="K27" t="n">
-        <v>-228.84</v>
+        <v>-227.96</v>
       </c>
       <c r="L27" t="n">
-        <v>260.14</v>
+        <v>259.14</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-297.83</v>
+        <v>-294.2</v>
       </c>
       <c r="K28" t="n">
-        <v>114.08</v>
+        <v>112.69</v>
       </c>
       <c r="L28" t="n">
-        <v>318.93</v>
+        <v>315.05</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-56.42</v>
+        <v>-59.34</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
       <c r="L29" t="n">
-        <v>56.42</v>
+        <v>59.34</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>52.06</v>
+        <v>55.24</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.39</v>
+        <v>-7.85</v>
       </c>
       <c r="L30" t="n">
-        <v>52.58</v>
+        <v>55.79</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>80.03</v>
+        <v>78</v>
       </c>
       <c r="K31" t="n">
-        <v>20.42</v>
+        <v>19.9</v>
       </c>
       <c r="L31" t="n">
-        <v>82.59</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>19.9</v>
+        <v>20.54</v>
       </c>
       <c r="K32" t="n">
-        <v>-73.41</v>
+        <v>-75.76000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>76.05</v>
+        <v>78.48999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.71</v>
+        <v>-0.74</v>
       </c>
       <c r="K33" t="n">
-        <v>69.54000000000001</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>69.54000000000001</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-73.3</v>
+        <v>-75.13</v>
       </c>
       <c r="K34" t="n">
-        <v>19</v>
+        <v>19.47</v>
       </c>
       <c r="L34" t="n">
-        <v>75.72</v>
+        <v>77.61</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-68.39</v>
+        <v>-71.86</v>
       </c>
       <c r="K35" t="n">
-        <v>97.01000000000001</v>
+        <v>101.93</v>
       </c>
       <c r="L35" t="n">
-        <v>118.69</v>
+        <v>124.71</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-65.66</v>
+        <v>-67.75</v>
       </c>
       <c r="K36" t="n">
-        <v>-83.25</v>
+        <v>-85.91</v>
       </c>
       <c r="L36" t="n">
-        <v>106.02</v>
+        <v>109.41</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-74.59</v>
+        <v>-73.23999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>139.54</v>
+        <v>137.01</v>
       </c>
       <c r="L37" t="n">
-        <v>158.22</v>
+        <v>155.36</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-103.64</v>
+        <v>-102.37</v>
       </c>
       <c r="K38" t="n">
-        <v>143.18</v>
+        <v>141.42</v>
       </c>
       <c r="L38" t="n">
-        <v>176.75</v>
+        <v>174.58</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-286.21</v>
+        <v>-267.71</v>
       </c>
       <c r="K39" t="n">
-        <v>45.04</v>
+        <v>42.13</v>
       </c>
       <c r="L39" t="n">
-        <v>289.73</v>
+        <v>271.01</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>187.36</v>
+        <v>181.5</v>
       </c>
       <c r="K40" t="n">
-        <v>159.81</v>
+        <v>154.81</v>
       </c>
       <c r="L40" t="n">
-        <v>246.26</v>
+        <v>238.55</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>150.14</v>
+        <v>151.36</v>
       </c>
       <c r="K41" t="n">
-        <v>229.72</v>
+        <v>231.59</v>
       </c>
       <c r="L41" t="n">
-        <v>274.43</v>
+        <v>276.66</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>360.39</v>
+        <v>348.4</v>
       </c>
       <c r="K42" t="n">
-        <v>-180.42</v>
+        <v>-174.42</v>
       </c>
       <c r="L42" t="n">
-        <v>403.03</v>
+        <v>389.63</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>315.99</v>
+        <v>317.18</v>
       </c>
       <c r="K43" t="n">
-        <v>27.4</v>
+        <v>27.5</v>
       </c>
       <c r="L43" t="n">
-        <v>317.17</v>
+        <v>318.37</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>24.56</v>
+        <v>24.39</v>
       </c>
       <c r="K44" t="n">
-        <v>73.94</v>
+        <v>73.44</v>
       </c>
       <c r="L44" t="n">
-        <v>77.92</v>
+        <v>77.38</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>46.2</v>
+        <v>48.52</v>
       </c>
       <c r="K45" t="n">
-        <v>26.37</v>
+        <v>27.69</v>
       </c>
       <c r="L45" t="n">
-        <v>53.19</v>
+        <v>55.87</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>66.26000000000001</v>
+        <v>65.08</v>
       </c>
       <c r="K46" t="n">
-        <v>-51.45</v>
+        <v>-50.54</v>
       </c>
       <c r="L46" t="n">
-        <v>83.89</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-107</v>
+        <v>-99.47</v>
       </c>
       <c r="K47" t="n">
-        <v>111</v>
+        <v>103.18</v>
       </c>
       <c r="L47" t="n">
-        <v>154.18</v>
+        <v>143.32</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>86.37</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="L48" t="n">
-        <v>86.37</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>3.32</v>
+        <v>3.44</v>
       </c>
       <c r="K49" t="n">
-        <v>69.31</v>
+        <v>71.78</v>
       </c>
       <c r="L49" t="n">
-        <v>69.39</v>
+        <v>71.86</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-90.28</v>
+        <v>-89.8</v>
       </c>
       <c r="K50" t="n">
-        <v>108.83</v>
+        <v>108.25</v>
       </c>
       <c r="L50" t="n">
-        <v>141.4</v>
+        <v>140.65</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>44.37</v>
+        <v>47.61</v>
       </c>
       <c r="K51" t="n">
-        <v>-90.06999999999999</v>
+        <v>-96.64</v>
       </c>
       <c r="L51" t="n">
-        <v>100.4</v>
+        <v>107.73</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-145.4</v>
+        <v>-143.19</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.54</v>
+        <v>-7.43</v>
       </c>
       <c r="L52" t="n">
-        <v>145.59</v>
+        <v>143.39</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-40.03</v>
+        <v>-44.09</v>
       </c>
       <c r="K53" t="n">
-        <v>-73.61</v>
+        <v>-81.08</v>
       </c>
       <c r="L53" t="n">
-        <v>83.79000000000001</v>
+        <v>92.3</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-207.68</v>
+        <v>-211.29</v>
       </c>
       <c r="K54" t="n">
-        <v>-61.33</v>
+        <v>-62.4</v>
       </c>
       <c r="L54" t="n">
-        <v>216.55</v>
+        <v>220.31</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>182.69</v>
+        <v>179.63</v>
       </c>
       <c r="K55" t="n">
-        <v>133.43</v>
+        <v>131.19</v>
       </c>
       <c r="L55" t="n">
-        <v>226.23</v>
+        <v>222.44</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-63.08</v>
+        <v>-69.68000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-152.84</v>
+        <v>-168.83</v>
       </c>
       <c r="L56" t="n">
-        <v>165.35</v>
+        <v>182.65</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-397.42</v>
+        <v>-394.31</v>
       </c>
       <c r="K57" t="n">
-        <v>-20.52</v>
+        <v>-20.36</v>
       </c>
       <c r="L57" t="n">
-        <v>397.95</v>
+        <v>394.83</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.63</v>
+        <v>-5.36</v>
       </c>
       <c r="K58" t="n">
-        <v>-525.23</v>
+        <v>-500.12</v>
       </c>
       <c r="L58" t="n">
-        <v>525.26</v>
+        <v>500.15</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>32.16</v>
+        <v>33.52</v>
       </c>
       <c r="K59" t="n">
-        <v>-48.85</v>
+        <v>-50.91</v>
       </c>
       <c r="L59" t="n">
-        <v>58.49</v>
+        <v>60.96</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>70.08</v>
+        <v>69.53</v>
       </c>
       <c r="K60" t="n">
-        <v>18.74</v>
+        <v>18.59</v>
       </c>
       <c r="L60" t="n">
-        <v>72.55</v>
+        <v>71.97</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>54.75</v>
+        <v>56.5</v>
       </c>
       <c r="K61" t="n">
-        <v>-29.45</v>
+        <v>-30.39</v>
       </c>
       <c r="L61" t="n">
-        <v>62.17</v>
+        <v>64.15000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-65.26000000000001</v>
+        <v>-65</v>
       </c>
       <c r="K62" t="n">
-        <v>-46.61</v>
+        <v>-46.42</v>
       </c>
       <c r="L62" t="n">
-        <v>80.2</v>
+        <v>79.88</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>32.77</v>
+        <v>33.05</v>
       </c>
       <c r="K63" t="n">
-        <v>79.62</v>
+        <v>80.31</v>
       </c>
       <c r="L63" t="n">
-        <v>86.09999999999999</v>
+        <v>86.84</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>7.88</v>
+        <v>7.96</v>
       </c>
       <c r="K64" t="n">
-        <v>75.26000000000001</v>
+        <v>76.03</v>
       </c>
       <c r="L64" t="n">
-        <v>75.67</v>
+        <v>76.45</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>175.22</v>
+        <v>168.92</v>
       </c>
       <c r="K65" t="n">
-        <v>-56.05</v>
+        <v>-54.04</v>
       </c>
       <c r="L65" t="n">
-        <v>183.96</v>
+        <v>177.35</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-29.36</v>
+        <v>-29.37</v>
       </c>
       <c r="K66" t="n">
-        <v>-141.12</v>
+        <v>-141.13</v>
       </c>
       <c r="L66" t="n">
-        <v>144.14</v>
+        <v>144.16</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-74.48999999999999</v>
+        <v>-81.8</v>
       </c>
       <c r="K67" t="n">
-        <v>35.52</v>
+        <v>39.01</v>
       </c>
       <c r="L67" t="n">
-        <v>82.52</v>
+        <v>90.63</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-67.31999999999999</v>
+        <v>-72.28</v>
       </c>
       <c r="K68" t="n">
-        <v>135.51</v>
+        <v>145.5</v>
       </c>
       <c r="L68" t="n">
-        <v>151.31</v>
+        <v>162.46</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>124.33</v>
+        <v>125.73</v>
       </c>
       <c r="K69" t="n">
-        <v>-123.79</v>
+        <v>-125.19</v>
       </c>
       <c r="L69" t="n">
-        <v>175.45</v>
+        <v>177.43</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>12.06</v>
+        <v>12.53</v>
       </c>
       <c r="K70" t="n">
-        <v>125.99</v>
+        <v>130.9</v>
       </c>
       <c r="L70" t="n">
-        <v>126.57</v>
+        <v>131.49</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>20.09</v>
+        <v>22.12</v>
       </c>
       <c r="K71" t="n">
-        <v>-157.43</v>
+        <v>-173.33</v>
       </c>
       <c r="L71" t="n">
-        <v>158.71</v>
+        <v>174.73</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="K72" t="n">
-        <v>234.89</v>
+        <v>247.6</v>
       </c>
       <c r="L72" t="n">
-        <v>234.9</v>
+        <v>247.6</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-272.59</v>
+        <v>-278.78</v>
       </c>
       <c r="K73" t="n">
-        <v>202.91</v>
+        <v>207.52</v>
       </c>
       <c r="L73" t="n">
-        <v>339.83</v>
+        <v>347.54</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-49.44</v>
+        <v>-53.01</v>
       </c>
       <c r="K74" t="n">
-        <v>-9.539999999999999</v>
+        <v>-10.23</v>
       </c>
       <c r="L74" t="n">
-        <v>50.35</v>
+        <v>53.99</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>80.75</v>
+        <v>79.02</v>
       </c>
       <c r="K75" t="n">
-        <v>38.04</v>
+        <v>37.23</v>
       </c>
       <c r="L75" t="n">
-        <v>89.27</v>
+        <v>87.34999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-65.91</v>
+        <v>-65.01000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>51.8</v>
+        <v>51.09</v>
       </c>
       <c r="L76" t="n">
-        <v>83.81999999999999</v>
+        <v>82.69</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>68.81999999999999</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-48.92</v>
+        <v>-49.93</v>
       </c>
       <c r="L77" t="n">
-        <v>84.43000000000001</v>
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-83.44</v>
+        <v>-82.42</v>
       </c>
       <c r="K78" t="n">
-        <v>38.04</v>
+        <v>37.57</v>
       </c>
       <c r="L78" t="n">
-        <v>91.7</v>
+        <v>90.58</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.06</v>
+        <v>-5.44</v>
       </c>
       <c r="K79" t="n">
-        <v>-18.88</v>
+        <v>-20.28</v>
       </c>
       <c r="L79" t="n">
-        <v>19.55</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>188</v>
+        <v>185.84</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.18</v>
+        <v>-2.15</v>
       </c>
       <c r="L80" t="n">
-        <v>188.01</v>
+        <v>185.85</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>145.26</v>
+        <v>149.64</v>
       </c>
       <c r="K81" t="n">
-        <v>-39.98</v>
+        <v>-41.18</v>
       </c>
       <c r="L81" t="n">
-        <v>150.66</v>
+        <v>155.2</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="K82" t="n">
-        <v>-134.82</v>
+        <v>-135.61</v>
       </c>
       <c r="L82" t="n">
-        <v>134.83</v>
+        <v>135.61</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>145.36</v>
+        <v>153.72</v>
       </c>
       <c r="K83" t="n">
-        <v>-6.34</v>
+        <v>-6.71</v>
       </c>
       <c r="L83" t="n">
-        <v>145.5</v>
+        <v>153.86</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>168.02</v>
+        <v>175.57</v>
       </c>
       <c r="K84" t="n">
-        <v>-28.44</v>
+        <v>-29.72</v>
       </c>
       <c r="L84" t="n">
-        <v>170.41</v>
+        <v>178.07</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>144.87</v>
+        <v>140.74</v>
       </c>
       <c r="K85" t="n">
-        <v>-176.57</v>
+        <v>-171.53</v>
       </c>
       <c r="L85" t="n">
-        <v>228.4</v>
+        <v>221.87</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-220.22</v>
+        <v>-234.45</v>
       </c>
       <c r="K86" t="n">
-        <v>-130.22</v>
+        <v>-138.64</v>
       </c>
       <c r="L86" t="n">
-        <v>255.84</v>
+        <v>272.37</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>261.52</v>
+        <v>252.17</v>
       </c>
       <c r="K87" t="n">
-        <v>352.94</v>
+        <v>340.32</v>
       </c>
       <c r="L87" t="n">
-        <v>439.27</v>
+        <v>423.57</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>226.5</v>
+        <v>225.08</v>
       </c>
       <c r="K88" t="n">
-        <v>267.93</v>
+        <v>266.25</v>
       </c>
       <c r="L88" t="n">
-        <v>350.84</v>
+        <v>348.64</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -628,25 +628,25 @@
         <v>4.23</v>
       </c>
       <c r="F14" t="n">
-        <v>11.57</v>
+        <v>10.09</v>
       </c>
       <c r="G14" t="n">
-        <v>14.6</v>
+        <v>22.8</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I14" t="n">
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>49.56</v>
+        <v>56.09</v>
       </c>
       <c r="K14" t="n">
-        <v>12.53</v>
+        <v>16.39</v>
       </c>
       <c r="L14" t="n">
-        <v>51.12</v>
+        <v>58.44</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>4.21</v>
       </c>
       <c r="F15" t="n">
-        <v>11.67</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>27.8</v>
+        <v>25</v>
       </c>
       <c r="H15" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>78.08</v>
+        <v>88.92</v>
       </c>
       <c r="K15" t="n">
-        <v>-13.67</v>
+        <v>-14.38</v>
       </c>
       <c r="L15" t="n">
-        <v>79.26000000000001</v>
+        <v>90.08</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>3.91</v>
       </c>
       <c r="F16" t="n">
-        <v>11.65</v>
+        <v>6.82</v>
       </c>
       <c r="G16" t="n">
-        <v>7.3</v>
+        <v>24.5</v>
       </c>
       <c r="H16" t="n">
-        <v>93.59999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-60.02</v>
+        <v>-64.26000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.09</v>
+        <v>-3.41</v>
       </c>
       <c r="L16" t="n">
-        <v>60.16</v>
+        <v>64.34999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>3.99</v>
       </c>
       <c r="F17" t="n">
-        <v>11.69</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>27.3</v>
+        <v>25.3</v>
       </c>
       <c r="H17" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>26.34</v>
+        <v>31.03</v>
       </c>
       <c r="K17" t="n">
-        <v>-64.34999999999999</v>
+        <v>-65.75</v>
       </c>
       <c r="L17" t="n">
-        <v>69.53</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>3.88</v>
       </c>
       <c r="F18" t="n">
-        <v>11.43</v>
+        <v>9.4</v>
       </c>
       <c r="G18" t="n">
-        <v>17.8</v>
+        <v>20.2</v>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-54.78</v>
+        <v>-65.18000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-38.7</v>
+        <v>-42.91</v>
       </c>
       <c r="L18" t="n">
-        <v>67.06999999999999</v>
+        <v>78.04000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>4.4</v>
       </c>
       <c r="F19" t="n">
-        <v>10.76</v>
+        <v>11.96</v>
       </c>
       <c r="G19" t="n">
-        <v>17.5</v>
+        <v>6.7</v>
       </c>
       <c r="H19" t="n">
-        <v>93.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>75.19</v>
+        <v>80.88</v>
       </c>
       <c r="K19" t="n">
-        <v>62.73</v>
+        <v>71.2</v>
       </c>
       <c r="L19" t="n">
-        <v>97.92</v>
+        <v>107.75</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>4.6</v>
       </c>
       <c r="F20" t="n">
-        <v>11.69</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>22.2</v>
+        <v>25.2</v>
       </c>
       <c r="H20" t="n">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-56.39</v>
+        <v>-62.85</v>
       </c>
       <c r="K20" t="n">
-        <v>-107.96</v>
+        <v>-119.99</v>
       </c>
       <c r="L20" t="n">
-        <v>121.8</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>4.8</v>
       </c>
       <c r="F21" t="n">
-        <v>11.02</v>
+        <v>11.53</v>
       </c>
       <c r="G21" t="n">
-        <v>28.3</v>
+        <v>11.9</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-112</v>
+        <v>-110.45</v>
       </c>
       <c r="K21" t="n">
-        <v>116.31</v>
+        <v>131.94</v>
       </c>
       <c r="L21" t="n">
-        <v>161.47</v>
+        <v>172.07</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>3.58</v>
       </c>
       <c r="F22" t="n">
-        <v>11.57</v>
+        <v>11.03</v>
       </c>
       <c r="G22" t="n">
-        <v>25.1</v>
+        <v>22.9</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-55.38</v>
+        <v>-56</v>
       </c>
       <c r="K22" t="n">
-        <v>113.1</v>
+        <v>133.51</v>
       </c>
       <c r="L22" t="n">
-        <v>125.93</v>
+        <v>144.78</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>4.4</v>
       </c>
       <c r="F23" t="n">
-        <v>11.5</v>
+        <v>10.7</v>
       </c>
       <c r="G23" t="n">
-        <v>25.6</v>
+        <v>21.6</v>
       </c>
       <c r="H23" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-145.89</v>
+        <v>-155.25</v>
       </c>
       <c r="K23" t="n">
-        <v>119.47</v>
+        <v>162.49</v>
       </c>
       <c r="L23" t="n">
-        <v>188.57</v>
+        <v>224.73</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>4.41</v>
       </c>
       <c r="F24" t="n">
-        <v>11.51</v>
+        <v>12.41</v>
       </c>
       <c r="G24" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="H24" t="n">
         <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>124.99</v>
+        <v>136.83</v>
       </c>
       <c r="K24" t="n">
-        <v>76.39</v>
+        <v>111.61</v>
       </c>
       <c r="L24" t="n">
-        <v>146.48</v>
+        <v>176.58</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>4.19</v>
       </c>
       <c r="F25" t="n">
-        <v>11.58</v>
+        <v>9.02</v>
       </c>
       <c r="G25" t="n">
-        <v>18.8</v>
+        <v>23.1</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-45.54</v>
+        <v>-25.66</v>
       </c>
       <c r="K25" t="n">
-        <v>130.21</v>
+        <v>160.89</v>
       </c>
       <c r="L25" t="n">
-        <v>137.95</v>
+        <v>162.92</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>4.38</v>
       </c>
       <c r="F26" t="n">
-        <v>11.23</v>
+        <v>12.52</v>
       </c>
       <c r="G26" t="n">
-        <v>25.2</v>
+        <v>16</v>
       </c>
       <c r="H26" t="n">
         <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-222.09</v>
+        <v>-223.3</v>
       </c>
       <c r="K26" t="n">
-        <v>49.9</v>
+        <v>110.1</v>
       </c>
       <c r="L26" t="n">
-        <v>227.62</v>
+        <v>248.96</v>
       </c>
     </row>
     <row r="27">
@@ -1174,10 +1174,10 @@
         <v>4.14</v>
       </c>
       <c r="F27" t="n">
-        <v>11.25</v>
+        <v>9.33</v>
       </c>
       <c r="G27" t="n">
-        <v>24.3</v>
+        <v>16.5</v>
       </c>
       <c r="H27" t="n">
         <v>100</v>
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-123.25</v>
+        <v>-137.7</v>
       </c>
       <c r="K27" t="n">
-        <v>-227.96</v>
+        <v>-223.56</v>
       </c>
       <c r="L27" t="n">
-        <v>259.14</v>
+        <v>262.57</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>4.61</v>
       </c>
       <c r="F28" t="n">
-        <v>10.83</v>
+        <v>13.11</v>
       </c>
       <c r="G28" t="n">
-        <v>20.3</v>
+        <v>8.1</v>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>-294.2</v>
+        <v>-317.29</v>
       </c>
       <c r="K28" t="n">
-        <v>112.69</v>
+        <v>156.64</v>
       </c>
       <c r="L28" t="n">
-        <v>315.05</v>
+        <v>353.85</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>3.87</v>
       </c>
       <c r="F29" t="n">
-        <v>11.65</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="H29" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-59.34</v>
+        <v>-63.81</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.35</v>
+        <v>1.61</v>
       </c>
       <c r="L29" t="n">
-        <v>59.34</v>
+        <v>63.83</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>4.75</v>
       </c>
       <c r="F30" t="n">
-        <v>11.52</v>
+        <v>11.03</v>
       </c>
       <c r="G30" t="n">
-        <v>16.1</v>
+        <v>21.8</v>
       </c>
       <c r="H30" t="n">
         <v>98.3</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>55.24</v>
+        <v>66.36</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.85</v>
+        <v>-6.3</v>
       </c>
       <c r="L30" t="n">
-        <v>55.79</v>
+        <v>66.66</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>4.17</v>
       </c>
       <c r="F31" t="n">
-        <v>11.48</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>17.2</v>
+        <v>21.1</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>78</v>
+        <v>78.42</v>
       </c>
       <c r="K31" t="n">
-        <v>19.9</v>
+        <v>20.88</v>
       </c>
       <c r="L31" t="n">
-        <v>80.5</v>
+        <v>81.16</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>4.44</v>
       </c>
       <c r="F32" t="n">
-        <v>10.79</v>
+        <v>12.19</v>
       </c>
       <c r="G32" t="n">
-        <v>17.3</v>
+        <v>7.3</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>20.54</v>
+        <v>24.61</v>
       </c>
       <c r="K32" t="n">
-        <v>-75.76000000000001</v>
+        <v>-84.81999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>78.48999999999999</v>
+        <v>88.31999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>4.38</v>
       </c>
       <c r="F33" t="n">
-        <v>10.88</v>
+        <v>10.53</v>
       </c>
       <c r="G33" t="n">
-        <v>29.4</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.74</v>
+        <v>-1.77</v>
       </c>
       <c r="K33" t="n">
-        <v>72.98999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>72.98999999999999</v>
+        <v>77.73</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>4.48</v>
       </c>
       <c r="F34" t="n">
-        <v>11.8</v>
+        <v>9.52</v>
       </c>
       <c r="G34" t="n">
-        <v>15.3</v>
+        <v>27.4</v>
       </c>
       <c r="H34" t="n">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-75.13</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>19.47</v>
+        <v>27.07</v>
       </c>
       <c r="L34" t="n">
-        <v>77.61</v>
+        <v>86.73</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>5.52</v>
       </c>
       <c r="F35" t="n">
-        <v>11.26</v>
+        <v>11.34</v>
       </c>
       <c r="G35" t="n">
-        <v>31</v>
+        <v>16.7</v>
       </c>
       <c r="H35" t="n">
         <v>100</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>-71.86</v>
+        <v>-56.85</v>
       </c>
       <c r="K35" t="n">
-        <v>101.93</v>
+        <v>123.1</v>
       </c>
       <c r="L35" t="n">
-        <v>124.71</v>
+        <v>135.6</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>4.39</v>
       </c>
       <c r="F36" t="n">
-        <v>10.62</v>
+        <v>12.35</v>
       </c>
       <c r="G36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>100</v>
+      </c>
+      <c r="I36" t="n">
         <v>21</v>
       </c>
-      <c r="H36" t="n">
-        <v>100</v>
-      </c>
-      <c r="I36" t="n">
-        <v>25</v>
-      </c>
       <c r="J36" t="n">
-        <v>-67.75</v>
+        <v>-97.70999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-85.91</v>
+        <v>-88.02</v>
       </c>
       <c r="L36" t="n">
-        <v>109.41</v>
+        <v>131.51</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>4.55</v>
       </c>
       <c r="F37" t="n">
-        <v>11.54</v>
+        <v>8.84</v>
       </c>
       <c r="G37" t="n">
-        <v>19.6</v>
+        <v>22.4</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-73.23999999999999</v>
+        <v>-67.15000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>137.01</v>
+        <v>154.36</v>
       </c>
       <c r="L37" t="n">
-        <v>155.36</v>
+        <v>168.33</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>4.46</v>
       </c>
       <c r="F38" t="n">
-        <v>11.04</v>
+        <v>9.84</v>
       </c>
       <c r="G38" t="n">
-        <v>31</v>
+        <v>12.3</v>
       </c>
       <c r="H38" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-102.37</v>
+        <v>-103.29</v>
       </c>
       <c r="K38" t="n">
-        <v>141.42</v>
+        <v>172.51</v>
       </c>
       <c r="L38" t="n">
-        <v>174.58</v>
+        <v>201.07</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>4.39</v>
       </c>
       <c r="F39" t="n">
-        <v>12.4</v>
+        <v>10.97</v>
       </c>
       <c r="G39" t="n">
-        <v>357.1</v>
+        <v>39.6</v>
       </c>
       <c r="H39" t="n">
-        <v>95.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="I39" t="n">
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-267.71</v>
+        <v>-263.05</v>
       </c>
       <c r="K39" t="n">
-        <v>42.13</v>
+        <v>59.76</v>
       </c>
       <c r="L39" t="n">
-        <v>271.01</v>
+        <v>269.75</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>4.78</v>
       </c>
       <c r="F40" t="n">
-        <v>11.88</v>
+        <v>10.96</v>
       </c>
       <c r="G40" t="n">
-        <v>19.3</v>
+        <v>29.1</v>
       </c>
       <c r="H40" t="n">
-        <v>97.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>181.5</v>
+        <v>186.82</v>
       </c>
       <c r="K40" t="n">
-        <v>154.81</v>
+        <v>166.87</v>
       </c>
       <c r="L40" t="n">
-        <v>238.55</v>
+        <v>250.49</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>4.47</v>
       </c>
       <c r="F41" t="n">
-        <v>11.61</v>
+        <v>10.95</v>
       </c>
       <c r="G41" t="n">
-        <v>17.7</v>
+        <v>24.6</v>
       </c>
       <c r="H41" t="n">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>151.36</v>
+        <v>256.01</v>
       </c>
       <c r="K41" t="n">
-        <v>231.59</v>
+        <v>32.44</v>
       </c>
       <c r="L41" t="n">
-        <v>276.66</v>
+        <v>258.05</v>
       </c>
     </row>
     <row r="42">
@@ -1801,28 +1801,28 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.76</v>
+        <v>4.75</v>
       </c>
       <c r="F42" t="n">
-        <v>10.8</v>
+        <v>9.76</v>
       </c>
       <c r="G42" t="n">
-        <v>37.4</v>
+        <v>34.2</v>
       </c>
       <c r="H42" t="n">
         <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>348.4</v>
+        <v>257.05</v>
       </c>
       <c r="K42" t="n">
-        <v>-174.42</v>
+        <v>307.3</v>
       </c>
       <c r="L42" t="n">
-        <v>389.63</v>
+        <v>400.63</v>
       </c>
     </row>
     <row r="43">
@@ -1843,28 +1843,28 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.94</v>
+        <v>4.03</v>
       </c>
       <c r="F43" t="n">
-        <v>11.38</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>17.3</v>
+        <v>30</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="I43" t="n">
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>317.18</v>
+        <v>-172.83</v>
       </c>
       <c r="K43" t="n">
-        <v>27.5</v>
+        <v>-65.61</v>
       </c>
       <c r="L43" t="n">
-        <v>318.37</v>
+        <v>184.87</v>
       </c>
     </row>
     <row r="44">
@@ -1885,28 +1885,28 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
       <c r="F44" t="n">
-        <v>11.21</v>
+        <v>10.77</v>
       </c>
       <c r="G44" t="n">
-        <v>10.9</v>
+        <v>22.7</v>
       </c>
       <c r="H44" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>24.39</v>
+        <v>34.27</v>
       </c>
       <c r="K44" t="n">
-        <v>73.44</v>
+        <v>-54.79</v>
       </c>
       <c r="L44" t="n">
-        <v>77.38</v>
+        <v>64.63</v>
       </c>
     </row>
     <row r="45">
@@ -1927,28 +1927,28 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.72</v>
+        <v>4.27</v>
       </c>
       <c r="F45" t="n">
-        <v>11.37</v>
+        <v>10.73</v>
       </c>
       <c r="G45" t="n">
-        <v>18.6</v>
+        <v>23.7</v>
       </c>
       <c r="H45" t="n">
         <v>100</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>48.52</v>
+        <v>-13.56</v>
       </c>
       <c r="K45" t="n">
-        <v>27.69</v>
+        <v>-68.59</v>
       </c>
       <c r="L45" t="n">
-        <v>55.87</v>
+        <v>69.91</v>
       </c>
     </row>
     <row r="46">
@@ -1969,28 +1969,28 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.58</v>
+        <v>4.42</v>
       </c>
       <c r="F46" t="n">
-        <v>11.23</v>
+        <v>10.66</v>
       </c>
       <c r="G46" t="n">
-        <v>26.3</v>
+        <v>28.8</v>
       </c>
       <c r="H46" t="n">
-        <v>97.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>65.08</v>
+        <v>7.07</v>
       </c>
       <c r="K46" t="n">
-        <v>-50.54</v>
+        <v>61.05</v>
       </c>
       <c r="L46" t="n">
-        <v>82.40000000000001</v>
+        <v>61.46</v>
       </c>
     </row>
     <row r="47">
@@ -2011,28 +2011,28 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="F47" t="n">
-        <v>11.93</v>
+        <v>13.11</v>
       </c>
       <c r="G47" t="n">
-        <v>22.6</v>
+        <v>25.8</v>
       </c>
       <c r="H47" t="n">
-        <v>90.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-99.47</v>
+        <v>115.44</v>
       </c>
       <c r="K47" t="n">
-        <v>103.18</v>
+        <v>-64.72</v>
       </c>
       <c r="L47" t="n">
-        <v>143.32</v>
+        <v>132.34</v>
       </c>
     </row>
     <row r="48">
@@ -2053,28 +2053,28 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.19</v>
+        <v>4.28</v>
       </c>
       <c r="F48" t="n">
-        <v>11.43</v>
+        <v>11.68</v>
       </c>
       <c r="G48" t="n">
-        <v>23.1</v>
+        <v>14.9</v>
       </c>
       <c r="H48" t="n">
         <v>100</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>85.59999999999999</v>
+        <v>-0.89</v>
       </c>
       <c r="K48" t="n">
-        <v>0.51</v>
+        <v>-109.78</v>
       </c>
       <c r="L48" t="n">
-        <v>85.59999999999999</v>
+        <v>109.78</v>
       </c>
     </row>
     <row r="49">
@@ -2095,28 +2095,28 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.11</v>
+        <v>5.13</v>
       </c>
       <c r="F49" t="n">
-        <v>12.36</v>
+        <v>13.11</v>
       </c>
       <c r="G49" t="n">
-        <v>24.1</v>
+        <v>17</v>
       </c>
       <c r="H49" t="n">
         <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>3.44</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>71.78</v>
+        <v>-21.96</v>
       </c>
       <c r="L49" t="n">
-        <v>71.86</v>
+        <v>94.38</v>
       </c>
     </row>
     <row r="50">
@@ -2137,28 +2137,28 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.59</v>
+        <v>5</v>
       </c>
       <c r="F50" t="n">
-        <v>11.36</v>
+        <v>12.8</v>
       </c>
       <c r="G50" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="H50" t="n">
-        <v>88.2</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-89.8</v>
+        <v>143.91</v>
       </c>
       <c r="K50" t="n">
-        <v>108.25</v>
+        <v>-30.48</v>
       </c>
       <c r="L50" t="n">
-        <v>140.65</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="51">
@@ -2179,28 +2179,28 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.53</v>
+        <v>4.78</v>
       </c>
       <c r="F51" t="n">
-        <v>11.48</v>
+        <v>13.1</v>
       </c>
       <c r="G51" t="n">
-        <v>30.9</v>
+        <v>26.2</v>
       </c>
       <c r="H51" t="n">
         <v>100</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>47.61</v>
+        <v>-116.83</v>
       </c>
       <c r="K51" t="n">
-        <v>-96.64</v>
+        <v>38.01</v>
       </c>
       <c r="L51" t="n">
-        <v>107.73</v>
+        <v>122.85</v>
       </c>
     </row>
     <row r="52">
@@ -2221,28 +2221,28 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.66</v>
+        <v>4.61</v>
       </c>
       <c r="F52" t="n">
-        <v>11.08</v>
+        <v>12.08</v>
       </c>
       <c r="G52" t="n">
-        <v>20.4</v>
+        <v>17.7</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I52" t="n">
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-143.19</v>
+        <v>-35.61</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.43</v>
+        <v>98.33</v>
       </c>
       <c r="L52" t="n">
-        <v>143.39</v>
+        <v>104.58</v>
       </c>
     </row>
     <row r="53">
@@ -2263,28 +2263,28 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.74</v>
+        <v>5.4</v>
       </c>
       <c r="F53" t="n">
-        <v>11.49</v>
+        <v>12.45</v>
       </c>
       <c r="G53" t="n">
-        <v>21.1</v>
+        <v>17.7</v>
       </c>
       <c r="H53" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-44.09</v>
+        <v>-33.19</v>
       </c>
       <c r="K53" t="n">
-        <v>-81.08</v>
+        <v>321.92</v>
       </c>
       <c r="L53" t="n">
-        <v>92.3</v>
+        <v>323.62</v>
       </c>
     </row>
     <row r="54">
@@ -2305,28 +2305,28 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.43</v>
+        <v>4.59</v>
       </c>
       <c r="F54" t="n">
-        <v>11.73</v>
+        <v>8.1</v>
       </c>
       <c r="G54" t="n">
-        <v>359.3</v>
+        <v>29</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-211.29</v>
+        <v>-58.47</v>
       </c>
       <c r="K54" t="n">
-        <v>-62.4</v>
+        <v>147.36</v>
       </c>
       <c r="L54" t="n">
-        <v>220.31</v>
+        <v>158.54</v>
       </c>
     </row>
     <row r="55">
@@ -2347,28 +2347,28 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.92</v>
+        <v>4.76</v>
       </c>
       <c r="F55" t="n">
-        <v>11.13</v>
+        <v>11.93</v>
       </c>
       <c r="G55" t="n">
-        <v>34.4</v>
+        <v>41</v>
       </c>
       <c r="H55" t="n">
-        <v>98.90000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>179.63</v>
+        <v>170.09</v>
       </c>
       <c r="K55" t="n">
-        <v>131.19</v>
+        <v>-114.78</v>
       </c>
       <c r="L55" t="n">
-        <v>222.44</v>
+        <v>205.2</v>
       </c>
     </row>
     <row r="56">
@@ -2389,28 +2389,28 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.4</v>
+        <v>5.11</v>
       </c>
       <c r="F56" t="n">
-        <v>10.84</v>
+        <v>10.13</v>
       </c>
       <c r="G56" t="n">
-        <v>2.5</v>
+        <v>22.4</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-69.68000000000001</v>
+        <v>-93.94</v>
       </c>
       <c r="K56" t="n">
-        <v>-168.83</v>
+        <v>373.83</v>
       </c>
       <c r="L56" t="n">
-        <v>182.65</v>
+        <v>385.45</v>
       </c>
     </row>
     <row r="57">
@@ -2431,28 +2431,28 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.18</v>
+        <v>4.46</v>
       </c>
       <c r="F57" t="n">
-        <v>10.71</v>
+        <v>10.67</v>
       </c>
       <c r="G57" t="n">
-        <v>23.6</v>
+        <v>15.5</v>
       </c>
       <c r="H57" t="n">
-        <v>97.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-394.31</v>
+        <v>-55.5</v>
       </c>
       <c r="K57" t="n">
-        <v>-20.36</v>
+        <v>298.69</v>
       </c>
       <c r="L57" t="n">
-        <v>394.83</v>
+        <v>303.8</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>5.06</v>
       </c>
       <c r="F58" t="n">
-        <v>11.33</v>
+        <v>13.11</v>
       </c>
       <c r="G58" t="n">
-        <v>23.8</v>
+        <v>30.4</v>
       </c>
       <c r="H58" t="n">
-        <v>97.09999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.36</v>
+        <v>-486.24</v>
       </c>
       <c r="K58" t="n">
-        <v>-500.12</v>
+        <v>217.56</v>
       </c>
       <c r="L58" t="n">
-        <v>500.15</v>
+        <v>532.6900000000001</v>
       </c>
     </row>
     <row r="59">
@@ -2515,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.17</v>
+        <v>4.67</v>
       </c>
       <c r="F59" t="n">
-        <v>11.43</v>
+        <v>12.8</v>
       </c>
       <c r="G59" t="n">
-        <v>8.1</v>
+        <v>23.8</v>
       </c>
       <c r="H59" t="n">
         <v>100</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>33.52</v>
+        <v>-40.89</v>
       </c>
       <c r="K59" t="n">
-        <v>-50.91</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>60.96</v>
+        <v>84.98</v>
       </c>
     </row>
     <row r="60">
@@ -2557,28 +2557,28 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.21</v>
+        <v>4.48</v>
       </c>
       <c r="F60" t="n">
-        <v>11.52</v>
+        <v>11.59</v>
       </c>
       <c r="G60" t="n">
-        <v>18.4</v>
+        <v>16.9</v>
       </c>
       <c r="H60" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>69.53</v>
+        <v>55.89</v>
       </c>
       <c r="K60" t="n">
-        <v>18.59</v>
+        <v>23.43</v>
       </c>
       <c r="L60" t="n">
-        <v>71.97</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="61">
@@ -2599,28 +2599,28 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.88</v>
+        <v>4.95</v>
       </c>
       <c r="F61" t="n">
-        <v>11.84</v>
+        <v>13.11</v>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>20.5</v>
       </c>
       <c r="H61" t="n">
         <v>100</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>56.5</v>
+        <v>-20.65</v>
       </c>
       <c r="K61" t="n">
-        <v>-30.39</v>
+        <v>-95.09</v>
       </c>
       <c r="L61" t="n">
-        <v>64.15000000000001</v>
+        <v>97.31</v>
       </c>
     </row>
     <row r="62">
@@ -2641,28 +2641,28 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.21</v>
+        <v>4.04</v>
       </c>
       <c r="F62" t="n">
-        <v>11.92</v>
+        <v>11.46</v>
       </c>
       <c r="G62" t="n">
-        <v>23.6</v>
+        <v>21.9</v>
       </c>
       <c r="H62" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-65</v>
+        <v>-46.42</v>
       </c>
       <c r="K62" t="n">
-        <v>-46.42</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>79.88</v>
+        <v>101.67</v>
       </c>
     </row>
     <row r="63">
@@ -2683,28 +2683,28 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.38</v>
+        <v>4.4</v>
       </c>
       <c r="F63" t="n">
-        <v>11.55</v>
+        <v>13.11</v>
       </c>
       <c r="G63" t="n">
-        <v>36.6</v>
+        <v>16.8</v>
       </c>
       <c r="H63" t="n">
         <v>100</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>33.05</v>
+        <v>79.62</v>
       </c>
       <c r="K63" t="n">
-        <v>80.31</v>
+        <v>-46.18</v>
       </c>
       <c r="L63" t="n">
-        <v>86.84</v>
+        <v>92.04000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2725,28 +2725,28 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.65</v>
+        <v>4.49</v>
       </c>
       <c r="F64" t="n">
-        <v>11.9</v>
+        <v>10.73</v>
       </c>
       <c r="G64" t="n">
-        <v>13.3</v>
+        <v>14.6</v>
       </c>
       <c r="H64" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>7.96</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>76.03</v>
+        <v>88.3</v>
       </c>
       <c r="L64" t="n">
-        <v>76.45</v>
+        <v>109.25</v>
       </c>
     </row>
     <row r="65">
@@ -2767,28 +2767,28 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.37</v>
+        <v>4.98</v>
       </c>
       <c r="F65" t="n">
-        <v>11.91</v>
+        <v>11.69</v>
       </c>
       <c r="G65" t="n">
-        <v>27.7</v>
+        <v>4.5</v>
       </c>
       <c r="H65" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>168.92</v>
+        <v>-92.87</v>
       </c>
       <c r="K65" t="n">
-        <v>-54.04</v>
+        <v>123.55</v>
       </c>
       <c r="L65" t="n">
-        <v>177.35</v>
+        <v>154.57</v>
       </c>
     </row>
     <row r="66">
@@ -2809,28 +2809,28 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>5.13</v>
+        <v>4.94</v>
       </c>
       <c r="F66" t="n">
-        <v>11</v>
+        <v>12.82</v>
       </c>
       <c r="G66" t="n">
-        <v>17.8</v>
+        <v>23.7</v>
       </c>
       <c r="H66" t="n">
-        <v>99.8</v>
+        <v>96</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-29.37</v>
+        <v>-129.61</v>
       </c>
       <c r="K66" t="n">
-        <v>-141.13</v>
+        <v>-82.59999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>144.16</v>
+        <v>153.69</v>
       </c>
     </row>
     <row r="67">
@@ -2851,28 +2851,28 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.54</v>
+        <v>4.45</v>
       </c>
       <c r="F67" t="n">
-        <v>11.79</v>
+        <v>12.57</v>
       </c>
       <c r="G67" t="n">
-        <v>13.8</v>
+        <v>18.5</v>
       </c>
       <c r="H67" t="n">
         <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-81.8</v>
+        <v>10.68</v>
       </c>
       <c r="K67" t="n">
-        <v>39.01</v>
+        <v>170.42</v>
       </c>
       <c r="L67" t="n">
-        <v>90.63</v>
+        <v>170.76</v>
       </c>
     </row>
     <row r="68">
@@ -2893,28 +2893,28 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.44</v>
+        <v>4.43</v>
       </c>
       <c r="F68" t="n">
-        <v>11.39</v>
+        <v>13.11</v>
       </c>
       <c r="G68" t="n">
-        <v>27.2</v>
+        <v>29</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>-72.28</v>
+        <v>144.45</v>
       </c>
       <c r="K68" t="n">
-        <v>145.5</v>
+        <v>-57.7</v>
       </c>
       <c r="L68" t="n">
-        <v>162.46</v>
+        <v>155.55</v>
       </c>
     </row>
     <row r="69">
@@ -2935,28 +2935,28 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.74</v>
+        <v>5.29</v>
       </c>
       <c r="F69" t="n">
-        <v>11.82</v>
+        <v>13.11</v>
       </c>
       <c r="G69" t="n">
-        <v>24.9</v>
+        <v>12.9</v>
       </c>
       <c r="H69" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>125.73</v>
+        <v>-120.04</v>
       </c>
       <c r="K69" t="n">
-        <v>-125.19</v>
+        <v>-236.72</v>
       </c>
       <c r="L69" t="n">
-        <v>177.43</v>
+        <v>265.42</v>
       </c>
     </row>
     <row r="70">
@@ -2977,28 +2977,28 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.16</v>
+        <v>4.67</v>
       </c>
       <c r="F70" t="n">
-        <v>11.19</v>
+        <v>12.45</v>
       </c>
       <c r="G70" t="n">
-        <v>19.4</v>
+        <v>19.9</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>12.53</v>
+        <v>116.84</v>
       </c>
       <c r="K70" t="n">
-        <v>130.9</v>
+        <v>-190.44</v>
       </c>
       <c r="L70" t="n">
-        <v>131.49</v>
+        <v>223.43</v>
       </c>
     </row>
     <row r="71">
@@ -3019,28 +3019,28 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.37</v>
+        <v>4.92</v>
       </c>
       <c r="F71" t="n">
-        <v>11.25</v>
+        <v>11.1</v>
       </c>
       <c r="G71" t="n">
-        <v>8.5</v>
+        <v>19.6</v>
       </c>
       <c r="H71" t="n">
-        <v>94.5</v>
+        <v>98.5</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>22.12</v>
+        <v>-236.3</v>
       </c>
       <c r="K71" t="n">
-        <v>-173.33</v>
+        <v>-123.43</v>
       </c>
       <c r="L71" t="n">
-        <v>174.73</v>
+        <v>266.59</v>
       </c>
     </row>
     <row r="72">
@@ -3061,28 +3061,28 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.74</v>
+        <v>4.82</v>
       </c>
       <c r="F72" t="n">
-        <v>10.51</v>
+        <v>13.11</v>
       </c>
       <c r="G72" t="n">
-        <v>29.5</v>
+        <v>24.5</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>1.28</v>
+        <v>163.18</v>
       </c>
       <c r="K72" t="n">
-        <v>247.6</v>
+        <v>365.6</v>
       </c>
       <c r="L72" t="n">
-        <v>247.6</v>
+        <v>400.36</v>
       </c>
     </row>
     <row r="73">
@@ -3103,28 +3103,28 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.4</v>
+        <v>4.69</v>
       </c>
       <c r="F73" t="n">
-        <v>11.3</v>
+        <v>10.67</v>
       </c>
       <c r="G73" t="n">
-        <v>20.5</v>
+        <v>19.9</v>
       </c>
       <c r="H73" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>-278.78</v>
+        <v>110.15</v>
       </c>
       <c r="K73" t="n">
-        <v>207.52</v>
+        <v>377.21</v>
       </c>
       <c r="L73" t="n">
-        <v>347.54</v>
+        <v>392.96</v>
       </c>
     </row>
     <row r="74">
@@ -3145,28 +3145,28 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.58</v>
+        <v>4.65</v>
       </c>
       <c r="F74" t="n">
-        <v>11.28</v>
+        <v>13.11</v>
       </c>
       <c r="G74" t="n">
-        <v>26.3</v>
+        <v>30.4</v>
       </c>
       <c r="H74" t="n">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-53.01</v>
+        <v>-7.42</v>
       </c>
       <c r="K74" t="n">
-        <v>-10.23</v>
+        <v>-81.2</v>
       </c>
       <c r="L74" t="n">
-        <v>53.99</v>
+        <v>81.54000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3187,28 +3187,28 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.65</v>
+        <v>5.06</v>
       </c>
       <c r="F75" t="n">
-        <v>11.13</v>
+        <v>13.11</v>
       </c>
       <c r="G75" t="n">
-        <v>14.4</v>
+        <v>23.2</v>
       </c>
       <c r="H75" t="n">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>79.02</v>
+        <v>32.23</v>
       </c>
       <c r="K75" t="n">
-        <v>37.23</v>
+        <v>93.89</v>
       </c>
       <c r="L75" t="n">
-        <v>87.34999999999999</v>
+        <v>99.27</v>
       </c>
     </row>
     <row r="76">
@@ -3229,28 +3229,28 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.69</v>
+        <v>5.22</v>
       </c>
       <c r="F76" t="n">
-        <v>12</v>
+        <v>13.11</v>
       </c>
       <c r="G76" t="n">
-        <v>24.9</v>
+        <v>29.4</v>
       </c>
       <c r="H76" t="n">
         <v>100</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-65.01000000000001</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>51.09</v>
+        <v>25.78</v>
       </c>
       <c r="L76" t="n">
-        <v>82.69</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3271,28 +3271,28 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>5.12</v>
+        <v>4.96</v>
       </c>
       <c r="F77" t="n">
-        <v>10.81</v>
+        <v>11.07</v>
       </c>
       <c r="G77" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="H77" t="n">
-        <v>93.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>70.23999999999999</v>
+        <v>-75.22</v>
       </c>
       <c r="K77" t="n">
-        <v>-49.93</v>
+        <v>27.89</v>
       </c>
       <c r="L77" t="n">
-        <v>86.18000000000001</v>
+        <v>80.23</v>
       </c>
     </row>
     <row r="78">
@@ -3313,28 +3313,28 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>5.06</v>
+        <v>4.64</v>
       </c>
       <c r="F78" t="n">
-        <v>10.83</v>
+        <v>13.11</v>
       </c>
       <c r="G78" t="n">
-        <v>23.6</v>
+        <v>13.5</v>
       </c>
       <c r="H78" t="n">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>-82.42</v>
+        <v>74.27</v>
       </c>
       <c r="K78" t="n">
-        <v>37.57</v>
+        <v>38.33</v>
       </c>
       <c r="L78" t="n">
-        <v>90.58</v>
+        <v>83.58</v>
       </c>
     </row>
     <row r="79">
@@ -3355,28 +3355,28 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.1</v>
+        <v>5.51</v>
       </c>
       <c r="F79" t="n">
-        <v>11.2</v>
+        <v>13.11</v>
       </c>
       <c r="G79" t="n">
-        <v>22.2</v>
+        <v>19</v>
       </c>
       <c r="H79" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.44</v>
+        <v>126.59</v>
       </c>
       <c r="K79" t="n">
-        <v>-20.28</v>
+        <v>-15.25</v>
       </c>
       <c r="L79" t="n">
-        <v>21</v>
+        <v>127.5</v>
       </c>
     </row>
     <row r="80">
@@ -3397,28 +3397,28 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.8</v>
+        <v>5.15</v>
       </c>
       <c r="F80" t="n">
-        <v>11.96</v>
+        <v>13.11</v>
       </c>
       <c r="G80" t="n">
-        <v>23.2</v>
+        <v>30.2</v>
       </c>
       <c r="H80" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>185.84</v>
+        <v>232.71</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.15</v>
+        <v>55.67</v>
       </c>
       <c r="L80" t="n">
-        <v>185.85</v>
+        <v>239.28</v>
       </c>
     </row>
     <row r="81">
@@ -3439,28 +3439,28 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.96</v>
+        <v>4.6</v>
       </c>
       <c r="F81" t="n">
-        <v>11.43</v>
+        <v>13.11</v>
       </c>
       <c r="G81" t="n">
-        <v>30.2</v>
+        <v>25.3</v>
       </c>
       <c r="H81" t="n">
-        <v>99.2</v>
+        <v>99.8</v>
       </c>
       <c r="I81" t="n">
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>149.64</v>
+        <v>-18.05</v>
       </c>
       <c r="K81" t="n">
-        <v>-41.18</v>
+        <v>-138.51</v>
       </c>
       <c r="L81" t="n">
-        <v>155.2</v>
+        <v>139.68</v>
       </c>
     </row>
     <row r="82">
@@ -3481,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.98</v>
+        <v>5.69</v>
       </c>
       <c r="F82" t="n">
-        <v>11.47</v>
+        <v>13.11</v>
       </c>
       <c r="G82" t="n">
-        <v>9.699999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="H82" t="n">
         <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>0.84</v>
+        <v>-129.52</v>
       </c>
       <c r="K82" t="n">
-        <v>-135.61</v>
+        <v>125.16</v>
       </c>
       <c r="L82" t="n">
-        <v>135.61</v>
+        <v>180.11</v>
       </c>
     </row>
     <row r="83">
@@ -3523,28 +3523,28 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.71</v>
+        <v>4.79</v>
       </c>
       <c r="F83" t="n">
-        <v>11.55</v>
+        <v>13.11</v>
       </c>
       <c r="G83" t="n">
-        <v>2.9</v>
+        <v>17.9</v>
       </c>
       <c r="H83" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>153.72</v>
+        <v>40.82</v>
       </c>
       <c r="K83" t="n">
-        <v>-6.71</v>
+        <v>-176.59</v>
       </c>
       <c r="L83" t="n">
-        <v>153.86</v>
+        <v>181.25</v>
       </c>
     </row>
     <row r="84">
@@ -3565,28 +3565,28 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.99</v>
+        <v>4.78</v>
       </c>
       <c r="F84" t="n">
-        <v>11.3</v>
+        <v>11.27</v>
       </c>
       <c r="G84" t="n">
-        <v>12.9</v>
+        <v>17</v>
       </c>
       <c r="H84" t="n">
-        <v>95.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I84" t="n">
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>175.57</v>
+        <v>-121.88</v>
       </c>
       <c r="K84" t="n">
-        <v>-29.72</v>
+        <v>133.36</v>
       </c>
       <c r="L84" t="n">
-        <v>178.07</v>
+        <v>180.67</v>
       </c>
     </row>
     <row r="85">
@@ -3607,28 +3607,28 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.55</v>
+        <v>4.92</v>
       </c>
       <c r="F85" t="n">
-        <v>11.63</v>
+        <v>13.11</v>
       </c>
       <c r="G85" t="n">
-        <v>22.7</v>
+        <v>6.4</v>
       </c>
       <c r="H85" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>140.74</v>
+        <v>-43.8</v>
       </c>
       <c r="K85" t="n">
-        <v>-171.53</v>
+        <v>191.85</v>
       </c>
       <c r="L85" t="n">
-        <v>221.87</v>
+        <v>196.78</v>
       </c>
     </row>
     <row r="86">
@@ -3649,28 +3649,28 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.96</v>
+        <v>4.76</v>
       </c>
       <c r="F86" t="n">
-        <v>11.19</v>
+        <v>11.1</v>
       </c>
       <c r="G86" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-234.45</v>
+        <v>-230.16</v>
       </c>
       <c r="K86" t="n">
-        <v>-138.64</v>
+        <v>290.82</v>
       </c>
       <c r="L86" t="n">
-        <v>272.37</v>
+        <v>370.88</v>
       </c>
     </row>
     <row r="87">
@@ -3691,13 +3691,13 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.98</v>
+        <v>5.27</v>
       </c>
       <c r="F87" t="n">
-        <v>11.41</v>
+        <v>13.11</v>
       </c>
       <c r="G87" t="n">
-        <v>7.9</v>
+        <v>32.4</v>
       </c>
       <c r="H87" t="n">
         <v>100</v>
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>252.17</v>
+        <v>-278.05</v>
       </c>
       <c r="K87" t="n">
-        <v>340.32</v>
+        <v>-142.24</v>
       </c>
       <c r="L87" t="n">
-        <v>423.57</v>
+        <v>312.32</v>
       </c>
     </row>
     <row r="88">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>5.08</v>
+        <v>4.94</v>
       </c>
       <c r="F88" t="n">
-        <v>11.36</v>
+        <v>13.11</v>
       </c>
       <c r="G88" t="n">
-        <v>15.9</v>
+        <v>27.3</v>
       </c>
       <c r="H88" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>225.08</v>
+        <v>-298.65</v>
       </c>
       <c r="K88" t="n">
-        <v>266.25</v>
+        <v>-127.63</v>
       </c>
       <c r="L88" t="n">
-        <v>348.64</v>
+        <v>324.78</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>56.09</v>
+        <v>57.97</v>
       </c>
       <c r="K14" t="n">
-        <v>16.39</v>
+        <v>16.94</v>
       </c>
       <c r="L14" t="n">
-        <v>58.44</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>21</v>
       </c>
       <c r="J15" t="n">
-        <v>88.92</v>
+        <v>93.52</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.38</v>
+        <v>-15.13</v>
       </c>
       <c r="L15" t="n">
-        <v>90.08</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-64.26000000000001</v>
+        <v>-64.05</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.41</v>
+        <v>-3.4</v>
       </c>
       <c r="L16" t="n">
-        <v>64.34999999999999</v>
+        <v>64.14</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>31.03</v>
+        <v>30.92</v>
       </c>
       <c r="K17" t="n">
-        <v>-65.75</v>
+        <v>-65.52</v>
       </c>
       <c r="L17" t="n">
-        <v>72.7</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>22</v>
       </c>
       <c r="J18" t="n">
-        <v>-65.18000000000001</v>
+        <v>-67.48</v>
       </c>
       <c r="K18" t="n">
-        <v>-42.91</v>
+        <v>-44.43</v>
       </c>
       <c r="L18" t="n">
-        <v>78.04000000000001</v>
+        <v>80.79000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>80.88</v>
+        <v>82.02</v>
       </c>
       <c r="K19" t="n">
-        <v>71.2</v>
+        <v>72.2</v>
       </c>
       <c r="L19" t="n">
-        <v>107.75</v>
+        <v>109.27</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-62.85</v>
+        <v>-67.36</v>
       </c>
       <c r="K20" t="n">
-        <v>-119.99</v>
+        <v>-128.61</v>
       </c>
       <c r="L20" t="n">
-        <v>135.45</v>
+        <v>145.18</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-110.45</v>
+        <v>-110.19</v>
       </c>
       <c r="K21" t="n">
-        <v>131.94</v>
+        <v>131.63</v>
       </c>
       <c r="L21" t="n">
-        <v>172.07</v>
+        <v>171.66</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-56</v>
+        <v>-55.97</v>
       </c>
       <c r="K22" t="n">
-        <v>133.51</v>
+        <v>133.43</v>
       </c>
       <c r="L22" t="n">
-        <v>144.78</v>
+        <v>144.69</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>-155.25</v>
+        <v>-166.97</v>
       </c>
       <c r="K23" t="n">
-        <v>162.49</v>
+        <v>174.75</v>
       </c>
       <c r="L23" t="n">
-        <v>224.73</v>
+        <v>241.7</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>136.83</v>
+        <v>139.7</v>
       </c>
       <c r="K24" t="n">
-        <v>111.61</v>
+        <v>113.95</v>
       </c>
       <c r="L24" t="n">
-        <v>176.58</v>
+        <v>180.28</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-25.66</v>
+        <v>-26.67</v>
       </c>
       <c r="K25" t="n">
-        <v>160.89</v>
+        <v>167.26</v>
       </c>
       <c r="L25" t="n">
-        <v>162.92</v>
+        <v>169.37</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-223.3</v>
+        <v>-226.44</v>
       </c>
       <c r="K26" t="n">
-        <v>110.1</v>
+        <v>111.64</v>
       </c>
       <c r="L26" t="n">
-        <v>248.96</v>
+        <v>252.46</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-137.7</v>
+        <v>-143.96</v>
       </c>
       <c r="K27" t="n">
-        <v>-223.56</v>
+        <v>-233.73</v>
       </c>
       <c r="L27" t="n">
-        <v>262.57</v>
+        <v>274.5</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>-317.29</v>
+        <v>-322.32</v>
       </c>
       <c r="K28" t="n">
-        <v>156.64</v>
+        <v>159.12</v>
       </c>
       <c r="L28" t="n">
-        <v>353.85</v>
+        <v>359.46</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-63.81</v>
+        <v>-66.06</v>
       </c>
       <c r="K29" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="L29" t="n">
-        <v>63.83</v>
+        <v>66.08</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>66.36</v>
+        <v>70.77</v>
       </c>
       <c r="K30" t="n">
-        <v>-6.3</v>
+        <v>-6.72</v>
       </c>
       <c r="L30" t="n">
-        <v>66.66</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>78.42</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>20.88</v>
+        <v>19.93</v>
       </c>
       <c r="L31" t="n">
-        <v>81.16</v>
+        <v>77.43000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>24.61</v>
+        <v>26.29</v>
       </c>
       <c r="K32" t="n">
-        <v>-84.81999999999999</v>
+        <v>-90.59</v>
       </c>
       <c r="L32" t="n">
-        <v>88.31999999999999</v>
+        <v>94.33</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.77</v>
+        <v>-1.76</v>
       </c>
       <c r="K33" t="n">
-        <v>77.70999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="L33" t="n">
-        <v>77.73</v>
+        <v>77.31999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>20</v>
       </c>
       <c r="J34" t="n">
-        <v>-82.40000000000001</v>
+        <v>-87.98999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>27.07</v>
+        <v>28.91</v>
       </c>
       <c r="L34" t="n">
-        <v>86.73</v>
+        <v>92.62</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>-56.85</v>
+        <v>-54.27</v>
       </c>
       <c r="K35" t="n">
-        <v>123.1</v>
+        <v>117.5</v>
       </c>
       <c r="L35" t="n">
-        <v>135.6</v>
+        <v>129.42</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-97.70999999999999</v>
+        <v>-103.05</v>
       </c>
       <c r="K36" t="n">
-        <v>-88.02</v>
+        <v>-92.83</v>
       </c>
       <c r="L36" t="n">
-        <v>131.51</v>
+        <v>138.7</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-67.15000000000001</v>
+        <v>-71.98</v>
       </c>
       <c r="K37" t="n">
-        <v>154.36</v>
+        <v>165.45</v>
       </c>
       <c r="L37" t="n">
-        <v>168.33</v>
+        <v>180.43</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>-103.29</v>
+        <v>-101.32</v>
       </c>
       <c r="K38" t="n">
-        <v>172.51</v>
+        <v>169.23</v>
       </c>
       <c r="L38" t="n">
-        <v>201.07</v>
+        <v>197.24</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-263.05</v>
+        <v>-268.56</v>
       </c>
       <c r="K39" t="n">
-        <v>59.76</v>
+        <v>61.01</v>
       </c>
       <c r="L39" t="n">
-        <v>269.75</v>
+        <v>275.4</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>186.82</v>
+        <v>184.54</v>
       </c>
       <c r="K40" t="n">
-        <v>166.87</v>
+        <v>164.83</v>
       </c>
       <c r="L40" t="n">
-        <v>250.49</v>
+        <v>247.43</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>256.01</v>
+        <v>269.78</v>
       </c>
       <c r="K41" t="n">
-        <v>32.44</v>
+        <v>34.18</v>
       </c>
       <c r="L41" t="n">
-        <v>258.05</v>
+        <v>271.94</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>257.05</v>
+        <v>280.74</v>
       </c>
       <c r="K42" t="n">
-        <v>307.3</v>
+        <v>335.61</v>
       </c>
       <c r="L42" t="n">
-        <v>400.63</v>
+        <v>437.54</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-172.83</v>
+        <v>-170.33</v>
       </c>
       <c r="K43" t="n">
-        <v>-65.61</v>
+        <v>-64.66</v>
       </c>
       <c r="L43" t="n">
-        <v>184.87</v>
+        <v>182.19</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>34.27</v>
+        <v>35.37</v>
       </c>
       <c r="K44" t="n">
-        <v>-54.79</v>
+        <v>-56.57</v>
       </c>
       <c r="L44" t="n">
-        <v>64.63</v>
+        <v>66.72</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-13.56</v>
+        <v>-13.75</v>
       </c>
       <c r="K45" t="n">
-        <v>-68.59</v>
+        <v>-69.59</v>
       </c>
       <c r="L45" t="n">
-        <v>69.91</v>
+        <v>70.94</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>7.07</v>
+        <v>6.89</v>
       </c>
       <c r="K46" t="n">
-        <v>61.05</v>
+        <v>59.47</v>
       </c>
       <c r="L46" t="n">
-        <v>61.46</v>
+        <v>59.87</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>115.44</v>
+        <v>109.91</v>
       </c>
       <c r="K47" t="n">
-        <v>-64.72</v>
+        <v>-61.62</v>
       </c>
       <c r="L47" t="n">
-        <v>132.34</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.89</v>
+        <v>-0.93</v>
       </c>
       <c r="K48" t="n">
-        <v>-109.78</v>
+        <v>-115.43</v>
       </c>
       <c r="L48" t="n">
-        <v>109.78</v>
+        <v>115.43</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>91.79000000000001</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-21.96</v>
+        <v>-23.39</v>
       </c>
       <c r="L49" t="n">
-        <v>94.38</v>
+        <v>100.52</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>143.91</v>
+        <v>140.49</v>
       </c>
       <c r="K50" t="n">
-        <v>-30.48</v>
+        <v>-29.76</v>
       </c>
       <c r="L50" t="n">
-        <v>147.1</v>
+        <v>143.61</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-116.83</v>
+        <v>-121.04</v>
       </c>
       <c r="K51" t="n">
-        <v>38.01</v>
+        <v>39.38</v>
       </c>
       <c r="L51" t="n">
-        <v>122.85</v>
+        <v>127.28</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-35.61</v>
+        <v>-34.06</v>
       </c>
       <c r="K52" t="n">
-        <v>98.33</v>
+        <v>94.03</v>
       </c>
       <c r="L52" t="n">
-        <v>104.58</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-33.19</v>
+        <v>-34.81</v>
       </c>
       <c r="K53" t="n">
-        <v>321.92</v>
+        <v>337.69</v>
       </c>
       <c r="L53" t="n">
-        <v>323.62</v>
+        <v>339.48</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-58.47</v>
+        <v>-57.72</v>
       </c>
       <c r="K54" t="n">
-        <v>147.36</v>
+        <v>145.47</v>
       </c>
       <c r="L54" t="n">
-        <v>158.54</v>
+        <v>156.5</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>170.09</v>
+        <v>168.01</v>
       </c>
       <c r="K55" t="n">
-        <v>-114.78</v>
+        <v>-113.37</v>
       </c>
       <c r="L55" t="n">
-        <v>205.2</v>
+        <v>202.68</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>-93.94</v>
+        <v>-99.40000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>373.83</v>
+        <v>395.58</v>
       </c>
       <c r="L56" t="n">
-        <v>385.45</v>
+        <v>407.88</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-55.5</v>
+        <v>-59.51</v>
       </c>
       <c r="K57" t="n">
-        <v>298.69</v>
+        <v>320.24</v>
       </c>
       <c r="L57" t="n">
-        <v>303.8</v>
+        <v>325.72</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-486.24</v>
+        <v>-474.7</v>
       </c>
       <c r="K58" t="n">
-        <v>217.56</v>
+        <v>212.4</v>
       </c>
       <c r="L58" t="n">
-        <v>532.6900000000001</v>
+        <v>520.0599999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-40.89</v>
+        <v>-43.63</v>
       </c>
       <c r="K59" t="n">
-        <v>74.48999999999999</v>
+        <v>79.48</v>
       </c>
       <c r="L59" t="n">
-        <v>84.98</v>
+        <v>90.67</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>55.89</v>
+        <v>58.71</v>
       </c>
       <c r="K60" t="n">
-        <v>23.43</v>
+        <v>24.61</v>
       </c>
       <c r="L60" t="n">
-        <v>60.6</v>
+        <v>63.66</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-20.65</v>
+        <v>-21.27</v>
       </c>
       <c r="K61" t="n">
-        <v>-95.09</v>
+        <v>-97.97</v>
       </c>
       <c r="L61" t="n">
-        <v>97.31</v>
+        <v>100.26</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-46.42</v>
+        <v>-45.3</v>
       </c>
       <c r="K62" t="n">
-        <v>90.45999999999999</v>
+        <v>88.27</v>
       </c>
       <c r="L62" t="n">
-        <v>101.67</v>
+        <v>99.22</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>79.62</v>
+        <v>79.19</v>
       </c>
       <c r="K63" t="n">
-        <v>-46.18</v>
+        <v>-45.93</v>
       </c>
       <c r="L63" t="n">
-        <v>92.04000000000001</v>
+        <v>91.54000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>64.31999999999999</v>
+        <v>66.41</v>
       </c>
       <c r="K64" t="n">
-        <v>88.3</v>
+        <v>91.17</v>
       </c>
       <c r="L64" t="n">
-        <v>109.25</v>
+        <v>112.79</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-92.87</v>
+        <v>-97.8</v>
       </c>
       <c r="K65" t="n">
-        <v>123.55</v>
+        <v>130.11</v>
       </c>
       <c r="L65" t="n">
-        <v>154.57</v>
+        <v>162.76</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-129.61</v>
+        <v>-123.8</v>
       </c>
       <c r="K66" t="n">
-        <v>-82.59999999999999</v>
+        <v>-78.90000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>153.69</v>
+        <v>146.8</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>10.68</v>
+        <v>11.06</v>
       </c>
       <c r="K67" t="n">
-        <v>170.42</v>
+        <v>176.64</v>
       </c>
       <c r="L67" t="n">
-        <v>170.76</v>
+        <v>176.99</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>144.45</v>
+        <v>150.21</v>
       </c>
       <c r="K68" t="n">
-        <v>-57.7</v>
+        <v>-60</v>
       </c>
       <c r="L68" t="n">
-        <v>155.55</v>
+        <v>161.75</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>-120.04</v>
+        <v>-116.17</v>
       </c>
       <c r="K69" t="n">
-        <v>-236.72</v>
+        <v>-229.1</v>
       </c>
       <c r="L69" t="n">
-        <v>265.42</v>
+        <v>256.87</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>116.84</v>
+        <v>126.5</v>
       </c>
       <c r="K70" t="n">
-        <v>-190.44</v>
+        <v>-206.19</v>
       </c>
       <c r="L70" t="n">
-        <v>223.43</v>
+        <v>241.9</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>21</v>
       </c>
       <c r="J71" t="n">
-        <v>-236.3</v>
+        <v>-254.14</v>
       </c>
       <c r="K71" t="n">
-        <v>-123.43</v>
+        <v>-132.75</v>
       </c>
       <c r="L71" t="n">
-        <v>266.59</v>
+        <v>286.72</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>163.18</v>
+        <v>178.29</v>
       </c>
       <c r="K72" t="n">
-        <v>365.6</v>
+        <v>399.46</v>
       </c>
       <c r="L72" t="n">
-        <v>400.36</v>
+        <v>437.45</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>110.15</v>
+        <v>116.26</v>
       </c>
       <c r="K73" t="n">
-        <v>377.21</v>
+        <v>398.14</v>
       </c>
       <c r="L73" t="n">
-        <v>392.96</v>
+        <v>414.77</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.42</v>
+        <v>-7.92</v>
       </c>
       <c r="K74" t="n">
-        <v>-81.2</v>
+        <v>-86.64</v>
       </c>
       <c r="L74" t="n">
-        <v>81.54000000000001</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>32.23</v>
+        <v>31.31</v>
       </c>
       <c r="K75" t="n">
-        <v>93.89</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="L75" t="n">
-        <v>99.27</v>
+        <v>96.43000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>66.34999999999999</v>
+        <v>63.01</v>
       </c>
       <c r="K76" t="n">
-        <v>25.78</v>
+        <v>24.48</v>
       </c>
       <c r="L76" t="n">
-        <v>71.18000000000001</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-75.22</v>
+        <v>-77.51000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>27.89</v>
+        <v>28.74</v>
       </c>
       <c r="L77" t="n">
-        <v>80.23</v>
+        <v>82.67</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>22</v>
       </c>
       <c r="J78" t="n">
-        <v>74.27</v>
+        <v>76.63</v>
       </c>
       <c r="K78" t="n">
-        <v>38.33</v>
+        <v>39.55</v>
       </c>
       <c r="L78" t="n">
-        <v>83.58</v>
+        <v>86.23999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>126.59</v>
+        <v>125.34</v>
       </c>
       <c r="K79" t="n">
-        <v>-15.25</v>
+        <v>-15.1</v>
       </c>
       <c r="L79" t="n">
-        <v>127.5</v>
+        <v>126.24</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>232.71</v>
+        <v>236.42</v>
       </c>
       <c r="K80" t="n">
-        <v>55.67</v>
+        <v>56.56</v>
       </c>
       <c r="L80" t="n">
-        <v>239.28</v>
+        <v>243.09</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.05</v>
+        <v>-19.35</v>
       </c>
       <c r="K81" t="n">
-        <v>-138.51</v>
+        <v>-148.46</v>
       </c>
       <c r="L81" t="n">
-        <v>139.68</v>
+        <v>149.71</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-129.52</v>
+        <v>-133.93</v>
       </c>
       <c r="K82" t="n">
-        <v>125.16</v>
+        <v>129.43</v>
       </c>
       <c r="L82" t="n">
-        <v>180.11</v>
+        <v>186.25</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>40.82</v>
+        <v>41.16</v>
       </c>
       <c r="K83" t="n">
-        <v>-176.59</v>
+        <v>-178.08</v>
       </c>
       <c r="L83" t="n">
-        <v>181.25</v>
+        <v>182.77</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-121.88</v>
+        <v>-132.01</v>
       </c>
       <c r="K84" t="n">
-        <v>133.36</v>
+        <v>144.44</v>
       </c>
       <c r="L84" t="n">
-        <v>180.67</v>
+        <v>195.68</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-43.8</v>
+        <v>-43.29</v>
       </c>
       <c r="K85" t="n">
-        <v>191.85</v>
+        <v>189.59</v>
       </c>
       <c r="L85" t="n">
-        <v>196.78</v>
+        <v>194.47</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-230.16</v>
+        <v>-234.05</v>
       </c>
       <c r="K86" t="n">
-        <v>290.82</v>
+        <v>295.73</v>
       </c>
       <c r="L86" t="n">
-        <v>370.88</v>
+        <v>377.14</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-278.05</v>
+        <v>-277.79</v>
       </c>
       <c r="K87" t="n">
-        <v>-142.24</v>
+        <v>-142.11</v>
       </c>
       <c r="L87" t="n">
-        <v>312.32</v>
+        <v>312.03</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-298.65</v>
+        <v>-297.83</v>
       </c>
       <c r="K88" t="n">
-        <v>-127.63</v>
+        <v>-127.28</v>
       </c>
       <c r="L88" t="n">
-        <v>324.78</v>
+        <v>323.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.23</v>
+        <v>4.97</v>
       </c>
       <c r="F14" t="n">
-        <v>10.09</v>
+        <v>12.33</v>
       </c>
       <c r="G14" t="n">
-        <v>22.8</v>
+        <v>14.5</v>
       </c>
       <c r="H14" t="n">
-        <v>97.5</v>
+        <v>79</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
-        <v>57.97</v>
+        <v>25.98</v>
       </c>
       <c r="K14" t="n">
-        <v>16.94</v>
+        <v>105.62</v>
       </c>
       <c r="L14" t="n">
-        <v>60.4</v>
+        <v>108.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:17:41</t>
+          <t>07:18:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.21</v>
+        <v>4.79</v>
       </c>
       <c r="F15" t="n">
-        <v>9.890000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="G15" t="n">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>31.1</v>
       </c>
       <c r="I15" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>93.52</v>
+        <v>-84.78</v>
       </c>
       <c r="K15" t="n">
-        <v>-15.13</v>
+        <v>-10.4</v>
       </c>
       <c r="L15" t="n">
-        <v>94.73999999999999</v>
+        <v>85.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:19:25</t>
+          <t>07:20:01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.91</v>
+        <v>4.43</v>
       </c>
       <c r="F16" t="n">
-        <v>6.82</v>
+        <v>10.19</v>
       </c>
       <c r="G16" t="n">
-        <v>24.5</v>
+        <v>13.6</v>
       </c>
       <c r="H16" t="n">
-        <v>93.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-64.05</v>
+        <v>61.37</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.4</v>
+        <v>83.17</v>
       </c>
       <c r="L16" t="n">
-        <v>64.14</v>
+        <v>103.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:23:14</t>
+          <t>07:25:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="F17" t="n">
-        <v>9.550000000000001</v>
+        <v>10.94</v>
       </c>
       <c r="G17" t="n">
-        <v>25.3</v>
+        <v>19.9</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>30.92</v>
+        <v>87.61</v>
       </c>
       <c r="K17" t="n">
-        <v>-65.52</v>
+        <v>-3.97</v>
       </c>
       <c r="L17" t="n">
-        <v>72.44</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:24:30</t>
+          <t>07:27:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.88</v>
+        <v>4.04</v>
       </c>
       <c r="F18" t="n">
-        <v>9.4</v>
+        <v>8.15</v>
       </c>
       <c r="G18" t="n">
-        <v>20.2</v>
+        <v>27.1</v>
       </c>
       <c r="H18" t="n">
-        <v>99.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="I18" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-67.48</v>
+        <v>85.34</v>
       </c>
       <c r="K18" t="n">
-        <v>-44.43</v>
+        <v>6.95</v>
       </c>
       <c r="L18" t="n">
-        <v>80.79000000000001</v>
+        <v>85.62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:26:19</t>
+          <t>07:29:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>4.4</v>
+        <v>3.89</v>
       </c>
       <c r="F19" t="n">
-        <v>11.96</v>
+        <v>13.11</v>
       </c>
       <c r="G19" t="n">
-        <v>6.7</v>
+        <v>32.1</v>
       </c>
       <c r="H19" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="I19" t="n">
         <v>23</v>
       </c>
       <c r="J19" t="n">
-        <v>82.02</v>
+        <v>-66.72</v>
       </c>
       <c r="K19" t="n">
-        <v>72.2</v>
+        <v>-84.53</v>
       </c>
       <c r="L19" t="n">
-        <v>109.27</v>
+        <v>107.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:30:17</t>
+          <t>07:34:17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>4.6</v>
+        <v>3.52</v>
       </c>
       <c r="F20" t="n">
-        <v>9.390000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="G20" t="n">
-        <v>25.2</v>
+        <v>11.2</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>71.5</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>-67.36</v>
+        <v>-7.31</v>
       </c>
       <c r="K20" t="n">
-        <v>-128.61</v>
+        <v>-122.33</v>
       </c>
       <c r="L20" t="n">
-        <v>145.18</v>
+        <v>122.55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:32:13</t>
+          <t>07:35:55</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.8</v>
+        <v>4.49</v>
       </c>
       <c r="F21" t="n">
-        <v>11.53</v>
+        <v>11.65</v>
       </c>
       <c r="G21" t="n">
-        <v>11.9</v>
+        <v>11</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>85.2</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>-110.19</v>
+        <v>-158.35</v>
       </c>
       <c r="K21" t="n">
-        <v>131.63</v>
+        <v>62.74</v>
       </c>
       <c r="L21" t="n">
-        <v>171.66</v>
+        <v>170.32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:34:07</t>
+          <t>07:36:58</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.58</v>
+        <v>3.81</v>
       </c>
       <c r="F22" t="n">
-        <v>11.03</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>22.9</v>
+        <v>8.9</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>63.3</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-55.97</v>
+        <v>23.57</v>
       </c>
       <c r="K22" t="n">
-        <v>133.43</v>
+        <v>145.31</v>
       </c>
       <c r="L22" t="n">
-        <v>144.69</v>
+        <v>147.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:38:55</t>
+          <t>07:40:49</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.4</v>
+        <v>3.79</v>
       </c>
       <c r="F23" t="n">
-        <v>10.7</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>21.6</v>
+        <v>12.9</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>29.4</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-166.97</v>
+        <v>191.55</v>
       </c>
       <c r="K23" t="n">
-        <v>174.75</v>
+        <v>98.78</v>
       </c>
       <c r="L23" t="n">
-        <v>241.7</v>
+        <v>215.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:41:26</t>
+          <t>07:42:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.41</v>
+        <v>4.31</v>
       </c>
       <c r="F24" t="n">
-        <v>12.41</v>
+        <v>10.89</v>
       </c>
       <c r="G24" t="n">
-        <v>21.6</v>
+        <v>26.9</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>70.5</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>139.7</v>
+        <v>130.77</v>
       </c>
       <c r="K24" t="n">
-        <v>113.95</v>
+        <v>254.99</v>
       </c>
       <c r="L24" t="n">
-        <v>180.28</v>
+        <v>286.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:43:33</t>
+          <t>07:44:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.19</v>
+        <v>4.23</v>
       </c>
       <c r="F25" t="n">
-        <v>9.02</v>
+        <v>9.31</v>
       </c>
       <c r="G25" t="n">
-        <v>23.1</v>
+        <v>22.3</v>
       </c>
       <c r="H25" t="n">
-        <v>99.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-26.67</v>
+        <v>94.7</v>
       </c>
       <c r="K25" t="n">
-        <v>167.26</v>
+        <v>275.63</v>
       </c>
       <c r="L25" t="n">
-        <v>169.37</v>
+        <v>291.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:48:02</t>
+          <t>07:49:16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="F26" t="n">
-        <v>12.52</v>
+        <v>9.48</v>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>52.6</v>
       </c>
       <c r="I26" t="n">
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-226.44</v>
+        <v>46.17</v>
       </c>
       <c r="K26" t="n">
-        <v>111.64</v>
+        <v>292.38</v>
       </c>
       <c r="L26" t="n">
-        <v>252.46</v>
+        <v>296.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:49:17</t>
+          <t>07:50:34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.14</v>
+        <v>4.19</v>
       </c>
       <c r="F27" t="n">
-        <v>9.33</v>
+        <v>11.4</v>
       </c>
       <c r="G27" t="n">
-        <v>16.5</v>
+        <v>28.5</v>
       </c>
       <c r="H27" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-143.96</v>
+        <v>90.73</v>
       </c>
       <c r="K27" t="n">
-        <v>-233.73</v>
+        <v>-80.12</v>
       </c>
       <c r="L27" t="n">
-        <v>274.5</v>
+        <v>121.04</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:50:22</t>
+          <t>07:53:15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.61</v>
+        <v>4.57</v>
       </c>
       <c r="F28" t="n">
-        <v>13.11</v>
+        <v>10.44</v>
       </c>
       <c r="G28" t="n">
-        <v>8.1</v>
+        <v>13.9</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="I28" t="n">
         <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>-322.32</v>
+        <v>64.87</v>
       </c>
       <c r="K28" t="n">
-        <v>159.12</v>
+        <v>332.89</v>
       </c>
       <c r="L28" t="n">
-        <v>359.46</v>
+        <v>339.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:00:52</t>
+          <t>08:03:33</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="F29" t="n">
-        <v>9.029999999999999</v>
+        <v>7.19</v>
       </c>
       <c r="G29" t="n">
-        <v>24.5</v>
+        <v>23.3</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>84.3</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-66.06</v>
+        <v>-2.15</v>
       </c>
       <c r="K29" t="n">
-        <v>1.67</v>
+        <v>52.68</v>
       </c>
       <c r="L29" t="n">
-        <v>66.08</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:02:41</t>
+          <t>08:05:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.75</v>
+        <v>3.62</v>
       </c>
       <c r="F30" t="n">
-        <v>11.03</v>
+        <v>8.85</v>
       </c>
       <c r="G30" t="n">
-        <v>21.8</v>
+        <v>20.6</v>
       </c>
       <c r="H30" t="n">
-        <v>98.3</v>
+        <v>52.5</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>70.77</v>
+        <v>-41.15</v>
       </c>
       <c r="K30" t="n">
-        <v>-6.72</v>
+        <v>6.83</v>
       </c>
       <c r="L30" t="n">
-        <v>71.09</v>
+        <v>41.71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:04:11</t>
+          <t>08:07:23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.17</v>
+        <v>4.28</v>
       </c>
       <c r="F31" t="n">
-        <v>8.869999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="G31" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>98.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>74.81999999999999</v>
+        <v>-19.03</v>
       </c>
       <c r="K31" t="n">
-        <v>19.93</v>
+        <v>65.64</v>
       </c>
       <c r="L31" t="n">
-        <v>77.43000000000001</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:09:48</t>
+          <t>08:11:41</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="F32" t="n">
-        <v>12.19</v>
+        <v>10.01</v>
       </c>
       <c r="G32" t="n">
-        <v>7.3</v>
+        <v>21.8</v>
       </c>
       <c r="H32" t="n">
-        <v>98.90000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>26.29</v>
+        <v>-107.25</v>
       </c>
       <c r="K32" t="n">
-        <v>-90.59</v>
+        <v>-31.7</v>
       </c>
       <c r="L32" t="n">
-        <v>94.33</v>
+        <v>111.83</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:12:03</t>
+          <t>08:13:57</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.38</v>
+        <v>4.64</v>
       </c>
       <c r="F33" t="n">
-        <v>10.53</v>
+        <v>13.11</v>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>27.8</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>38.4</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.76</v>
+        <v>57.46</v>
       </c>
       <c r="K33" t="n">
-        <v>77.3</v>
+        <v>63.69</v>
       </c>
       <c r="L33" t="n">
-        <v>77.31999999999999</v>
+        <v>85.78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:14:23</t>
+          <t>08:15:49</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="F34" t="n">
-        <v>9.52</v>
+        <v>10.41</v>
       </c>
       <c r="G34" t="n">
-        <v>27.4</v>
+        <v>15.1</v>
       </c>
       <c r="H34" t="n">
-        <v>97.90000000000001</v>
+        <v>58</v>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J34" t="n">
-        <v>-87.98999999999999</v>
+        <v>121.62</v>
       </c>
       <c r="K34" t="n">
-        <v>28.91</v>
+        <v>5.33</v>
       </c>
       <c r="L34" t="n">
-        <v>92.62</v>
+        <v>121.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:19:20</t>
+          <t>08:20:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.52</v>
+        <v>4.29</v>
       </c>
       <c r="F35" t="n">
-        <v>11.34</v>
+        <v>11.48</v>
       </c>
       <c r="G35" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-54.27</v>
+        <v>-101.76</v>
       </c>
       <c r="K35" t="n">
-        <v>117.5</v>
+        <v>-80.77</v>
       </c>
       <c r="L35" t="n">
-        <v>129.42</v>
+        <v>129.91</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:21:39</t>
+          <t>08:22:43</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.39</v>
+        <v>5.09</v>
       </c>
       <c r="F36" t="n">
-        <v>12.35</v>
+        <v>12.53</v>
       </c>
       <c r="G36" t="n">
-        <v>3.9</v>
+        <v>24.3</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>69.2</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-103.05</v>
+        <v>29.35</v>
       </c>
       <c r="K36" t="n">
-        <v>-92.83</v>
+        <v>254.3</v>
       </c>
       <c r="L36" t="n">
-        <v>138.7</v>
+        <v>255.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:23:08</t>
+          <t>08:24:45</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="F37" t="n">
-        <v>8.84</v>
+        <v>8.01</v>
       </c>
       <c r="G37" t="n">
-        <v>22.4</v>
+        <v>31.4</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>75.8</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>-71.98</v>
+        <v>-107.08</v>
       </c>
       <c r="K37" t="n">
-        <v>165.45</v>
+        <v>68.41</v>
       </c>
       <c r="L37" t="n">
-        <v>180.43</v>
+        <v>127.07</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:28:14</t>
+          <t>08:28:08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.46</v>
+        <v>4.65</v>
       </c>
       <c r="F38" t="n">
-        <v>9.84</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>12.3</v>
+        <v>17.5</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>54.7</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-101.32</v>
+        <v>-0.33</v>
       </c>
       <c r="K38" t="n">
-        <v>169.23</v>
+        <v>150.74</v>
       </c>
       <c r="L38" t="n">
-        <v>197.24</v>
+        <v>150.74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:29:39</t>
+          <t>08:29:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="F39" t="n">
-        <v>10.97</v>
+        <v>12.62</v>
       </c>
       <c r="G39" t="n">
-        <v>39.6</v>
+        <v>13.4</v>
       </c>
       <c r="H39" t="n">
-        <v>88.8</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-268.56</v>
+        <v>91.28</v>
       </c>
       <c r="K39" t="n">
-        <v>61.01</v>
+        <v>-232.58</v>
       </c>
       <c r="L39" t="n">
-        <v>275.4</v>
+        <v>249.85</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:31:49</t>
+          <t>08:31:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.78</v>
+        <v>5.51</v>
       </c>
       <c r="F40" t="n">
-        <v>10.96</v>
+        <v>11.25</v>
       </c>
       <c r="G40" t="n">
-        <v>29.1</v>
+        <v>19.6</v>
       </c>
       <c r="H40" t="n">
-        <v>99.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>184.54</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>164.83</v>
+        <v>272.07</v>
       </c>
       <c r="L40" t="n">
-        <v>247.43</v>
+        <v>283.88</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:37:05</t>
+          <t>08:35:56</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.47</v>
+        <v>4.19</v>
       </c>
       <c r="F41" t="n">
-        <v>10.95</v>
+        <v>10.01</v>
       </c>
       <c r="G41" t="n">
-        <v>24.6</v>
+        <v>21.5</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>269.78</v>
+        <v>-300.1</v>
       </c>
       <c r="K41" t="n">
-        <v>34.18</v>
+        <v>3.14</v>
       </c>
       <c r="L41" t="n">
-        <v>271.94</v>
+        <v>300.12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:38:01</t>
+          <t>08:37:22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="F42" t="n">
-        <v>9.76</v>
+        <v>12.69</v>
       </c>
       <c r="G42" t="n">
-        <v>34.2</v>
+        <v>18.5</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>17.7</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>280.74</v>
+        <v>-287.05</v>
       </c>
       <c r="K42" t="n">
-        <v>335.61</v>
+        <v>46.8</v>
       </c>
       <c r="L42" t="n">
-        <v>437.54</v>
+        <v>290.84</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:40:15</t>
+          <t>08:39:55</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.03</v>
+        <v>4.57</v>
       </c>
       <c r="F43" t="n">
-        <v>9.800000000000001</v>
+        <v>13.11</v>
       </c>
       <c r="G43" t="n">
-        <v>30</v>
+        <v>21.8</v>
       </c>
       <c r="H43" t="n">
-        <v>98.7</v>
+        <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>-170.33</v>
+        <v>176.41</v>
       </c>
       <c r="K43" t="n">
-        <v>-64.66</v>
+        <v>264.37</v>
       </c>
       <c r="L43" t="n">
-        <v>182.19</v>
+        <v>317.82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:50:14</t>
+          <t>08:49:35</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="F44" t="n">
-        <v>10.77</v>
+        <v>11.4</v>
       </c>
       <c r="G44" t="n">
-        <v>22.7</v>
+        <v>33.7</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>31.8</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>35.37</v>
+        <v>-45.02</v>
       </c>
       <c r="K44" t="n">
-        <v>-56.57</v>
+        <v>67.98</v>
       </c>
       <c r="L44" t="n">
-        <v>66.72</v>
+        <v>81.54000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:52:06</t>
+          <t>08:52:08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.27</v>
+        <v>4.39</v>
       </c>
       <c r="F45" t="n">
-        <v>10.73</v>
+        <v>10.55</v>
       </c>
       <c r="G45" t="n">
-        <v>23.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>61.1</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J45" t="n">
-        <v>-13.75</v>
+        <v>64.02</v>
       </c>
       <c r="K45" t="n">
-        <v>-69.59</v>
+        <v>-17.65</v>
       </c>
       <c r="L45" t="n">
-        <v>70.94</v>
+        <v>66.41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:53:23</t>
+          <t>08:54:38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.42</v>
+        <v>4.74</v>
       </c>
       <c r="F46" t="n">
-        <v>10.66</v>
+        <v>12.8</v>
       </c>
       <c r="G46" t="n">
-        <v>28.8</v>
+        <v>20</v>
       </c>
       <c r="H46" t="n">
-        <v>94.59999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>6.89</v>
+        <v>-23.11</v>
       </c>
       <c r="K46" t="n">
-        <v>59.47</v>
+        <v>110.26</v>
       </c>
       <c r="L46" t="n">
-        <v>59.87</v>
+        <v>112.66</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:58:07</t>
+          <t>09:00:21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.66</v>
+        <v>4.73</v>
       </c>
       <c r="F47" t="n">
-        <v>13.11</v>
+        <v>11.59</v>
       </c>
       <c r="G47" t="n">
-        <v>25.8</v>
+        <v>12.3</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>109.91</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>-61.62</v>
+        <v>125.6</v>
       </c>
       <c r="L47" t="n">
-        <v>126</v>
+        <v>144.18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:00:10</t>
+          <t>09:01:33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.28</v>
+        <v>4.44</v>
       </c>
       <c r="F48" t="n">
-        <v>11.68</v>
+        <v>13.04</v>
       </c>
       <c r="G48" t="n">
-        <v>14.9</v>
+        <v>18.1</v>
       </c>
       <c r="H48" t="n">
-        <v>100</v>
+        <v>37.1</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.93</v>
+        <v>-103.45</v>
       </c>
       <c r="K48" t="n">
-        <v>-115.43</v>
+        <v>-26.86</v>
       </c>
       <c r="L48" t="n">
-        <v>115.43</v>
+        <v>106.88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:01:32</t>
+          <t>09:03:14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>5.13</v>
+        <v>4.61</v>
       </c>
       <c r="F49" t="n">
-        <v>13.11</v>
+        <v>9.85</v>
       </c>
       <c r="G49" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>50.8</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>97.76000000000001</v>
+        <v>53.71</v>
       </c>
       <c r="K49" t="n">
-        <v>-23.39</v>
+        <v>110.94</v>
       </c>
       <c r="L49" t="n">
-        <v>100.52</v>
+        <v>123.26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:06:40</t>
+          <t>09:07:26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="F50" t="n">
-        <v>12.8</v>
+        <v>13.11</v>
       </c>
       <c r="G50" t="n">
-        <v>18.4</v>
+        <v>28.4</v>
       </c>
       <c r="H50" t="n">
-        <v>99.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>140.49</v>
+        <v>196.68</v>
       </c>
       <c r="K50" t="n">
-        <v>-29.76</v>
+        <v>-65.15000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>143.61</v>
+        <v>207.19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:07:44</t>
+          <t>09:08:29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.78</v>
+        <v>4.83</v>
       </c>
       <c r="F51" t="n">
-        <v>13.1</v>
+        <v>10.94</v>
       </c>
       <c r="G51" t="n">
-        <v>26.2</v>
+        <v>28.2</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>62.4</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-121.04</v>
+        <v>101.99</v>
       </c>
       <c r="K51" t="n">
-        <v>39.38</v>
+        <v>131.25</v>
       </c>
       <c r="L51" t="n">
-        <v>127.28</v>
+        <v>166.21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:08:38</t>
+          <t>09:10:19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.61</v>
+        <v>4.8</v>
       </c>
       <c r="F52" t="n">
-        <v>12.08</v>
+        <v>11.63</v>
       </c>
       <c r="G52" t="n">
-        <v>17.7</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>96.8</v>
+        <v>92.8</v>
       </c>
       <c r="I52" t="n">
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-34.06</v>
+        <v>-71.95999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>94.03</v>
+        <v>-199.48</v>
       </c>
       <c r="L52" t="n">
-        <v>100.01</v>
+        <v>212.06</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:14:11</t>
+          <t>09:15:54</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.4</v>
+        <v>4.26</v>
       </c>
       <c r="F53" t="n">
-        <v>12.45</v>
+        <v>9.49</v>
       </c>
       <c r="G53" t="n">
-        <v>17.7</v>
+        <v>23.7</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>82.8</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>-34.81</v>
+        <v>-225.37</v>
       </c>
       <c r="K53" t="n">
-        <v>337.69</v>
+        <v>-79.55</v>
       </c>
       <c r="L53" t="n">
-        <v>339.48</v>
+        <v>239</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:14:53</t>
+          <t>09:16:38</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.59</v>
+        <v>4.13</v>
       </c>
       <c r="F54" t="n">
-        <v>8.1</v>
+        <v>10.51</v>
       </c>
       <c r="G54" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>30.4</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-57.72</v>
+        <v>-142.32</v>
       </c>
       <c r="K54" t="n">
-        <v>145.47</v>
+        <v>-30.52</v>
       </c>
       <c r="L54" t="n">
-        <v>156.5</v>
+        <v>145.56</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:16:26</t>
+          <t>09:18:05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.76</v>
+        <v>4.37</v>
       </c>
       <c r="F55" t="n">
-        <v>11.93</v>
+        <v>12.14</v>
       </c>
       <c r="G55" t="n">
-        <v>41</v>
+        <v>4.9</v>
       </c>
       <c r="H55" t="n">
-        <v>97.3</v>
+        <v>75</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>168.01</v>
+        <v>-46.91</v>
       </c>
       <c r="K55" t="n">
-        <v>-113.37</v>
+        <v>108.39</v>
       </c>
       <c r="L55" t="n">
-        <v>202.68</v>
+        <v>118.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:22:02</t>
+          <t>09:21:35</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.11</v>
+        <v>4.6</v>
       </c>
       <c r="F56" t="n">
-        <v>10.13</v>
+        <v>11.62</v>
       </c>
       <c r="G56" t="n">
-        <v>22.4</v>
+        <v>40.1</v>
       </c>
       <c r="H56" t="n">
-        <v>94.40000000000001</v>
+        <v>37.5</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>-99.40000000000001</v>
+        <v>-85.38</v>
       </c>
       <c r="K56" t="n">
-        <v>395.58</v>
+        <v>-250.32</v>
       </c>
       <c r="L56" t="n">
-        <v>407.88</v>
+        <v>264.48</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:24:17</t>
+          <t>09:23:28</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.46</v>
+        <v>5.14</v>
       </c>
       <c r="F57" t="n">
-        <v>10.67</v>
+        <v>13.11</v>
       </c>
       <c r="G57" t="n">
-        <v>15.5</v>
+        <v>20.5</v>
       </c>
       <c r="H57" t="n">
-        <v>93.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-59.51</v>
+        <v>240.57</v>
       </c>
       <c r="K57" t="n">
-        <v>320.24</v>
+        <v>-78.86</v>
       </c>
       <c r="L57" t="n">
-        <v>325.72</v>
+        <v>253.16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:25:53</t>
+          <t>09:25:20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>5.06</v>
+        <v>4.57</v>
       </c>
       <c r="F58" t="n">
-        <v>13.11</v>
+        <v>9.6</v>
       </c>
       <c r="G58" t="n">
-        <v>30.4</v>
+        <v>18.6</v>
       </c>
       <c r="H58" t="n">
-        <v>99.3</v>
+        <v>28.6</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>-474.7</v>
+        <v>277.19</v>
       </c>
       <c r="K58" t="n">
-        <v>212.4</v>
+        <v>-168.36</v>
       </c>
       <c r="L58" t="n">
-        <v>520.0599999999999</v>
+        <v>324.31</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:37:04</t>
+          <t>09:35:49</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.67</v>
+        <v>4.94</v>
       </c>
       <c r="F59" t="n">
-        <v>12.8</v>
+        <v>12.17</v>
       </c>
       <c r="G59" t="n">
-        <v>23.8</v>
+        <v>13.8</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>57.4</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-43.63</v>
+        <v>-73.65000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>79.48</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>90.67</v>
+        <v>118.35</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:38:19</t>
+          <t>09:36:44</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.48</v>
+        <v>5.22</v>
       </c>
       <c r="F60" t="n">
-        <v>11.59</v>
+        <v>13.11</v>
       </c>
       <c r="G60" t="n">
-        <v>16.9</v>
+        <v>11.1</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>58.71</v>
+        <v>-44.14</v>
       </c>
       <c r="K60" t="n">
-        <v>24.61</v>
+        <v>-83.98999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>63.66</v>
+        <v>94.88</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:39:35</t>
+          <t>09:39:28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.95</v>
+        <v>4.57</v>
       </c>
       <c r="F61" t="n">
         <v>13.11</v>
       </c>
       <c r="G61" t="n">
-        <v>20.5</v>
+        <v>13.5</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>56.8</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J61" t="n">
-        <v>-21.27</v>
+        <v>60.75</v>
       </c>
       <c r="K61" t="n">
-        <v>-97.97</v>
+        <v>-32.1</v>
       </c>
       <c r="L61" t="n">
-        <v>100.26</v>
+        <v>68.70999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:44:45</t>
+          <t>09:44:18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.04</v>
+        <v>5.33</v>
       </c>
       <c r="F62" t="n">
-        <v>11.46</v>
+        <v>13.11</v>
       </c>
       <c r="G62" t="n">
-        <v>21.9</v>
+        <v>17.1</v>
       </c>
       <c r="H62" t="n">
         <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>-45.3</v>
+        <v>-154.42</v>
       </c>
       <c r="K62" t="n">
-        <v>88.27</v>
+        <v>59.73</v>
       </c>
       <c r="L62" t="n">
-        <v>99.22</v>
+        <v>165.57</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:46:23</t>
+          <t>09:45:24</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.4</v>
+        <v>4.77</v>
       </c>
       <c r="F63" t="n">
-        <v>13.11</v>
+        <v>10.75</v>
       </c>
       <c r="G63" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="H63" t="n">
-        <v>100</v>
+        <v>54.4</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J63" t="n">
-        <v>79.19</v>
+        <v>36.57</v>
       </c>
       <c r="K63" t="n">
-        <v>-45.93</v>
+        <v>-130.01</v>
       </c>
       <c r="L63" t="n">
-        <v>91.54000000000001</v>
+        <v>135.05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:48:45</t>
+          <t>09:47:37</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.49</v>
+        <v>4.82</v>
       </c>
       <c r="F64" t="n">
-        <v>10.73</v>
+        <v>13.11</v>
       </c>
       <c r="G64" t="n">
-        <v>14.6</v>
+        <v>9.6</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>59.3</v>
       </c>
       <c r="I64" t="n">
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>66.41</v>
+        <v>102.25</v>
       </c>
       <c r="K64" t="n">
-        <v>91.17</v>
+        <v>-183.76</v>
       </c>
       <c r="L64" t="n">
-        <v>112.79</v>
+        <v>210.29</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:53:03</t>
+          <t>09:52:10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.98</v>
+        <v>4.77</v>
       </c>
       <c r="F65" t="n">
-        <v>11.69</v>
+        <v>12.67</v>
       </c>
       <c r="G65" t="n">
-        <v>4.5</v>
+        <v>22.3</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>44.5</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J65" t="n">
-        <v>-97.8</v>
+        <v>-162.26</v>
       </c>
       <c r="K65" t="n">
-        <v>130.11</v>
+        <v>153.91</v>
       </c>
       <c r="L65" t="n">
-        <v>162.76</v>
+        <v>223.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:55:24</t>
+          <t>09:54:09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.94</v>
+        <v>4.58</v>
       </c>
       <c r="F66" t="n">
-        <v>12.82</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>23.7</v>
+        <v>12.4</v>
       </c>
       <c r="H66" t="n">
-        <v>96</v>
+        <v>37.1</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-123.8</v>
+        <v>155.32</v>
       </c>
       <c r="K66" t="n">
-        <v>-78.90000000000001</v>
+        <v>41.85</v>
       </c>
       <c r="L66" t="n">
-        <v>146.8</v>
+        <v>160.86</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:56:51</t>
+          <t>09:55:26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="F67" t="n">
-        <v>12.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>18.5</v>
+        <v>14.3</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>38.5</v>
       </c>
       <c r="I67" t="n">
         <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>11.06</v>
+        <v>65.95</v>
       </c>
       <c r="K67" t="n">
-        <v>176.64</v>
+        <v>110.61</v>
       </c>
       <c r="L67" t="n">
-        <v>176.99</v>
+        <v>128.78</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:00:08</t>
+          <t>09:58:59</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.43</v>
+        <v>4.6</v>
       </c>
       <c r="F68" t="n">
-        <v>13.11</v>
+        <v>11.07</v>
       </c>
       <c r="G68" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H68" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="I68" t="n">
         <v>29</v>
       </c>
-      <c r="H68" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="I68" t="n">
-        <v>22</v>
-      </c>
       <c r="J68" t="n">
-        <v>150.21</v>
+        <v>-242.68</v>
       </c>
       <c r="K68" t="n">
-        <v>-60</v>
+        <v>-46.62</v>
       </c>
       <c r="L68" t="n">
-        <v>161.75</v>
+        <v>247.12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:01:07</t>
+          <t>10:00:46</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>5.29</v>
+        <v>4.85</v>
       </c>
       <c r="F69" t="n">
-        <v>13.11</v>
+        <v>11.41</v>
       </c>
       <c r="G69" t="n">
-        <v>12.9</v>
+        <v>10.7</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>62.8</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>-116.17</v>
+        <v>51.04</v>
       </c>
       <c r="K69" t="n">
-        <v>-229.1</v>
+        <v>231.99</v>
       </c>
       <c r="L69" t="n">
-        <v>256.87</v>
+        <v>237.54</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:02:39</t>
+          <t>10:01:48</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.67</v>
+        <v>5.42</v>
       </c>
       <c r="F70" t="n">
-        <v>12.45</v>
+        <v>13.11</v>
       </c>
       <c r="G70" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="H70" t="n">
-        <v>97.90000000000001</v>
+        <v>45.2</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J70" t="n">
-        <v>126.5</v>
+        <v>-103.09</v>
       </c>
       <c r="K70" t="n">
-        <v>-206.19</v>
+        <v>-271.3</v>
       </c>
       <c r="L70" t="n">
-        <v>241.9</v>
+        <v>290.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:06:51</t>
+          <t>10:07:12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.92</v>
+        <v>5.05</v>
       </c>
       <c r="F71" t="n">
-        <v>11.1</v>
+        <v>12.84</v>
       </c>
       <c r="G71" t="n">
-        <v>19.6</v>
+        <v>22.2</v>
       </c>
       <c r="H71" t="n">
-        <v>98.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J71" t="n">
-        <v>-254.14</v>
+        <v>-271.42</v>
       </c>
       <c r="K71" t="n">
-        <v>-132.75</v>
+        <v>160.72</v>
       </c>
       <c r="L71" t="n">
-        <v>286.72</v>
+        <v>315.44</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:07:40</t>
+          <t>10:08:38</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="F72" t="n">
         <v>13.11</v>
       </c>
       <c r="G72" t="n">
-        <v>24.5</v>
+        <v>16.4</v>
       </c>
       <c r="H72" t="n">
-        <v>91.09999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I72" t="n">
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>178.29</v>
+        <v>17.66</v>
       </c>
       <c r="K72" t="n">
-        <v>399.46</v>
+        <v>376.53</v>
       </c>
       <c r="L72" t="n">
-        <v>437.45</v>
+        <v>376.95</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:10:07</t>
+          <t>10:10:40</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.69</v>
+        <v>5.04</v>
       </c>
       <c r="F73" t="n">
-        <v>10.67</v>
+        <v>13.11</v>
       </c>
       <c r="G73" t="n">
-        <v>19.9</v>
+        <v>12.2</v>
       </c>
       <c r="H73" t="n">
-        <v>99</v>
+        <v>27.2</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>116.26</v>
+        <v>-293.11</v>
       </c>
       <c r="K73" t="n">
-        <v>398.14</v>
+        <v>310.93</v>
       </c>
       <c r="L73" t="n">
-        <v>414.77</v>
+        <v>427.31</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:20:02</t>
+          <t>10:17:55</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.65</v>
+        <v>5.36</v>
       </c>
       <c r="F74" t="n">
         <v>13.11</v>
       </c>
       <c r="G74" t="n">
-        <v>30.4</v>
+        <v>17.1</v>
       </c>
       <c r="H74" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-7.92</v>
+        <v>-54.2</v>
       </c>
       <c r="K74" t="n">
-        <v>-86.64</v>
+        <v>81.14</v>
       </c>
       <c r="L74" t="n">
-        <v>87</v>
+        <v>97.56999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:22:11</t>
+          <t>10:20:09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>5.06</v>
+        <v>4.31</v>
       </c>
       <c r="F75" t="n">
-        <v>13.11</v>
+        <v>12.41</v>
       </c>
       <c r="G75" t="n">
-        <v>23.2</v>
+        <v>11.2</v>
       </c>
       <c r="H75" t="n">
-        <v>97.3</v>
+        <v>15.2</v>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>31.31</v>
+        <v>24.95</v>
       </c>
       <c r="K75" t="n">
-        <v>91.20999999999999</v>
+        <v>49.91</v>
       </c>
       <c r="L75" t="n">
-        <v>96.43000000000001</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:24:02</t>
+          <t>10:21:03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.22</v>
+        <v>4.95</v>
       </c>
       <c r="F76" t="n">
-        <v>13.11</v>
+        <v>12.27</v>
       </c>
       <c r="G76" t="n">
-        <v>29.4</v>
+        <v>20.6</v>
       </c>
       <c r="H76" t="n">
-        <v>100</v>
+        <v>73.3</v>
       </c>
       <c r="I76" t="n">
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>63.01</v>
+        <v>-31.67</v>
       </c>
       <c r="K76" t="n">
-        <v>24.48</v>
+        <v>87.08</v>
       </c>
       <c r="L76" t="n">
-        <v>67.59999999999999</v>
+        <v>92.66</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:27:39</t>
+          <t>10:24:56</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.96</v>
+        <v>4.82</v>
       </c>
       <c r="F77" t="n">
-        <v>11.07</v>
+        <v>12.12</v>
       </c>
       <c r="G77" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="H77" t="n">
-        <v>94.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>-77.51000000000001</v>
+        <v>94.13</v>
       </c>
       <c r="K77" t="n">
-        <v>28.74</v>
+        <v>66.78</v>
       </c>
       <c r="L77" t="n">
-        <v>82.67</v>
+        <v>115.41</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:28:55</t>
+          <t>10:26:02</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.64</v>
+        <v>4.41</v>
       </c>
       <c r="F78" t="n">
-        <v>13.11</v>
+        <v>12.74</v>
       </c>
       <c r="G78" t="n">
-        <v>13.5</v>
+        <v>27.8</v>
       </c>
       <c r="H78" t="n">
-        <v>94.3</v>
+        <v>82</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J78" t="n">
-        <v>76.63</v>
+        <v>-0.98</v>
       </c>
       <c r="K78" t="n">
-        <v>39.55</v>
+        <v>-115.98</v>
       </c>
       <c r="L78" t="n">
-        <v>86.23999999999999</v>
+        <v>115.98</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:30:36</t>
+          <t>10:27:54</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.51</v>
+        <v>4.57</v>
       </c>
       <c r="F79" t="n">
-        <v>13.11</v>
+        <v>11.16</v>
       </c>
       <c r="G79" t="n">
-        <v>19</v>
+        <v>9.6</v>
       </c>
       <c r="H79" t="n">
-        <v>97.5</v>
+        <v>62.6</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>125.34</v>
+        <v>-89.59</v>
       </c>
       <c r="K79" t="n">
-        <v>-15.1</v>
+        <v>26.94</v>
       </c>
       <c r="L79" t="n">
-        <v>126.24</v>
+        <v>93.55</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:34:47</t>
+          <t>10:31:37</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.15</v>
+        <v>5.06</v>
       </c>
       <c r="F80" t="n">
         <v>13.11</v>
       </c>
       <c r="G80" t="n">
-        <v>30.2</v>
+        <v>11.5</v>
       </c>
       <c r="H80" t="n">
-        <v>96.8</v>
+        <v>62.3</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J80" t="n">
-        <v>236.42</v>
+        <v>171.94</v>
       </c>
       <c r="K80" t="n">
-        <v>56.56</v>
+        <v>161.84</v>
       </c>
       <c r="L80" t="n">
-        <v>243.09</v>
+        <v>236.13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:36:19</t>
+          <t>10:32:43</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="F81" t="n">
         <v>13.11</v>
       </c>
       <c r="G81" t="n">
-        <v>25.3</v>
+        <v>4.7</v>
       </c>
       <c r="H81" t="n">
-        <v>99.8</v>
+        <v>38.2</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>-19.35</v>
+        <v>-210.74</v>
       </c>
       <c r="K81" t="n">
-        <v>-148.46</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>149.71</v>
+        <v>228.74</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:37:13</t>
+          <t>10:34:39</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.69</v>
+        <v>4.79</v>
       </c>
       <c r="F82" t="n">
-        <v>13.11</v>
+        <v>11.45</v>
       </c>
       <c r="G82" t="n">
-        <v>19.4</v>
+        <v>10.6</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>21.8</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-133.93</v>
+        <v>36.08</v>
       </c>
       <c r="K82" t="n">
-        <v>129.43</v>
+        <v>4.62</v>
       </c>
       <c r="L82" t="n">
-        <v>186.25</v>
+        <v>36.38</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:43:21</t>
+          <t>10:40:19</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.79</v>
+        <v>5.27</v>
       </c>
       <c r="F83" t="n">
         <v>13.11</v>
       </c>
       <c r="G83" t="n">
-        <v>17.9</v>
+        <v>19.7</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>84.3</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J83" t="n">
-        <v>41.16</v>
+        <v>183.77</v>
       </c>
       <c r="K83" t="n">
-        <v>-178.08</v>
+        <v>-213.78</v>
       </c>
       <c r="L83" t="n">
-        <v>182.77</v>
+        <v>281.91</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:45:17</t>
+          <t>10:41:16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.78</v>
+        <v>4.61</v>
       </c>
       <c r="F84" t="n">
-        <v>11.27</v>
+        <v>13.11</v>
       </c>
       <c r="G84" t="n">
-        <v>17</v>
+        <v>7.6</v>
       </c>
       <c r="H84" t="n">
-        <v>100</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-132.01</v>
+        <v>127.88</v>
       </c>
       <c r="K84" t="n">
-        <v>144.44</v>
+        <v>164.15</v>
       </c>
       <c r="L84" t="n">
-        <v>195.68</v>
+        <v>208.08</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:47:06</t>
+          <t>10:43:20</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.92</v>
+        <v>4.51</v>
       </c>
       <c r="F85" t="n">
-        <v>13.11</v>
+        <v>11.31</v>
       </c>
       <c r="G85" t="n">
-        <v>6.4</v>
+        <v>24.3</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>58</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>-43.29</v>
+        <v>262.71</v>
       </c>
       <c r="K85" t="n">
-        <v>189.59</v>
+        <v>40.37</v>
       </c>
       <c r="L85" t="n">
-        <v>194.47</v>
+        <v>265.79</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:52:49</t>
+          <t>10:48:46</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.76</v>
+        <v>5.15</v>
       </c>
       <c r="F86" t="n">
-        <v>11.1</v>
+        <v>12.45</v>
       </c>
       <c r="G86" t="n">
-        <v>15</v>
+        <v>19.7</v>
       </c>
       <c r="H86" t="n">
-        <v>97.59999999999999</v>
+        <v>34.9</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-234.05</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>295.73</v>
+        <v>287.35</v>
       </c>
       <c r="L86" t="n">
-        <v>377.14</v>
+        <v>303.89</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:53:56</t>
+          <t>10:50:43</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.27</v>
+        <v>4.73</v>
       </c>
       <c r="F87" t="n">
         <v>13.11</v>
       </c>
       <c r="G87" t="n">
-        <v>32.4</v>
+        <v>26.4</v>
       </c>
       <c r="H87" t="n">
-        <v>100</v>
+        <v>78.7</v>
       </c>
       <c r="I87" t="n">
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-277.79</v>
+        <v>-139.68</v>
       </c>
       <c r="K87" t="n">
-        <v>-142.11</v>
+        <v>244.51</v>
       </c>
       <c r="L87" t="n">
-        <v>312.03</v>
+        <v>281.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:56:00</t>
+          <t>10:52:49</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.94</v>
+        <v>4.84</v>
       </c>
       <c r="F88" t="n">
         <v>13.11</v>
       </c>
       <c r="G88" t="n">
-        <v>27.3</v>
+        <v>19.1</v>
       </c>
       <c r="H88" t="n">
-        <v>100</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-297.83</v>
+        <v>136.73</v>
       </c>
       <c r="K88" t="n">
-        <v>-127.28</v>
+        <v>247.76</v>
       </c>
       <c r="L88" t="n">
-        <v>323.88</v>
+        <v>282.98</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>4.97</v>
+        <v>3.6</v>
       </c>
       <c r="F14" t="n">
-        <v>12.33</v>
+        <v>7.61</v>
       </c>
       <c r="G14" t="n">
-        <v>14.5</v>
+        <v>21.4</v>
       </c>
       <c r="H14" t="n">
-        <v>79</v>
+        <v>95.3</v>
       </c>
       <c r="I14" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J14" t="n">
-        <v>25.98</v>
+        <v>61.09</v>
       </c>
       <c r="K14" t="n">
-        <v>105.62</v>
+        <v>39.99</v>
       </c>
       <c r="L14" t="n">
-        <v>108.77</v>
+        <v>73.01000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:18:04</t>
+          <t>07:17:38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.79</v>
+        <v>3.94</v>
       </c>
       <c r="F15" t="n">
-        <v>8.91</v>
+        <v>8.42</v>
       </c>
       <c r="G15" t="n">
-        <v>25.6</v>
+        <v>19.2</v>
       </c>
       <c r="H15" t="n">
-        <v>31.1</v>
+        <v>52.9</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J15" t="n">
-        <v>-84.78</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.4</v>
+        <v>14.77</v>
       </c>
       <c r="L15" t="n">
-        <v>85.42</v>
+        <v>87.48999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:20:01</t>
+          <t>07:19:08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4.43</v>
+        <v>4.55</v>
       </c>
       <c r="F16" t="n">
-        <v>10.19</v>
+        <v>10.47</v>
       </c>
       <c r="G16" t="n">
-        <v>13.6</v>
+        <v>18.5</v>
       </c>
       <c r="H16" t="n">
-        <v>67.59999999999999</v>
+        <v>15.7</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>61.37</v>
+        <v>14.86</v>
       </c>
       <c r="K16" t="n">
-        <v>83.17</v>
+        <v>108.4</v>
       </c>
       <c r="L16" t="n">
-        <v>103.36</v>
+        <v>109.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:25:41</t>
+          <t>07:25:01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1</v>
+        <v>3.89</v>
       </c>
       <c r="F17" t="n">
-        <v>10.94</v>
+        <v>11.67</v>
       </c>
       <c r="G17" t="n">
-        <v>19.9</v>
+        <v>2.3</v>
       </c>
       <c r="H17" t="n">
-        <v>50</v>
+        <v>41.8</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>87.61</v>
+        <v>93.23</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.97</v>
+        <v>45.16</v>
       </c>
       <c r="L17" t="n">
-        <v>87.7</v>
+        <v>103.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:27:39</t>
+          <t>07:26:52</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>4.04</v>
+        <v>3.69</v>
       </c>
       <c r="F18" t="n">
-        <v>8.15</v>
+        <v>7.67</v>
       </c>
       <c r="G18" t="n">
-        <v>27.1</v>
+        <v>20.3</v>
       </c>
       <c r="H18" t="n">
-        <v>72.5</v>
+        <v>62.2</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>85.34</v>
+        <v>68.37</v>
       </c>
       <c r="K18" t="n">
-        <v>6.95</v>
+        <v>-61.11</v>
       </c>
       <c r="L18" t="n">
-        <v>85.62</v>
+        <v>91.69</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:29:34</t>
+          <t>07:29:03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
       <c r="F19" t="n">
-        <v>13.11</v>
+        <v>9.56</v>
       </c>
       <c r="G19" t="n">
-        <v>32.1</v>
+        <v>13.7</v>
       </c>
       <c r="H19" t="n">
-        <v>81</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-66.72</v>
+        <v>-49.68</v>
       </c>
       <c r="K19" t="n">
-        <v>-84.53</v>
+        <v>95.19</v>
       </c>
       <c r="L19" t="n">
-        <v>107.69</v>
+        <v>107.38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:34:17</t>
+          <t>07:33:58</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.52</v>
+        <v>3.98</v>
       </c>
       <c r="F20" t="n">
-        <v>9.08</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>11.2</v>
+        <v>23</v>
       </c>
       <c r="H20" t="n">
-        <v>71.5</v>
+        <v>47.3</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.31</v>
+        <v>14.07</v>
       </c>
       <c r="K20" t="n">
-        <v>-122.33</v>
+        <v>-197.95</v>
       </c>
       <c r="L20" t="n">
-        <v>122.55</v>
+        <v>198.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:35:55</t>
+          <t>07:36:25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.49</v>
+        <v>4.06</v>
       </c>
       <c r="F21" t="n">
-        <v>11.65</v>
+        <v>7.77</v>
       </c>
       <c r="G21" t="n">
-        <v>11</v>
+        <v>12.2</v>
       </c>
       <c r="H21" t="n">
-        <v>85.2</v>
+        <v>51.3</v>
       </c>
       <c r="I21" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>-158.35</v>
+        <v>-50.64</v>
       </c>
       <c r="K21" t="n">
-        <v>62.74</v>
+        <v>130.36</v>
       </c>
       <c r="L21" t="n">
-        <v>170.32</v>
+        <v>139.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:36:58</t>
+          <t>07:38:24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.81</v>
+        <v>4.36</v>
       </c>
       <c r="F22" t="n">
-        <v>8.050000000000001</v>
+        <v>11.72</v>
       </c>
       <c r="G22" t="n">
-        <v>8.9</v>
+        <v>17.3</v>
       </c>
       <c r="H22" t="n">
-        <v>63.3</v>
+        <v>54.1</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>23.57</v>
+        <v>-155.77</v>
       </c>
       <c r="K22" t="n">
-        <v>145.31</v>
+        <v>-112.58</v>
       </c>
       <c r="L22" t="n">
-        <v>147.21</v>
+        <v>192.19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:40:49</t>
+          <t>07:42:14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.79</v>
+        <v>3.6</v>
       </c>
       <c r="F23" t="n">
-        <v>9.390000000000001</v>
+        <v>7.38</v>
       </c>
       <c r="G23" t="n">
-        <v>12.9</v>
+        <v>10.9</v>
       </c>
       <c r="H23" t="n">
-        <v>29.4</v>
+        <v>51.9</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>191.55</v>
+        <v>-228.06</v>
       </c>
       <c r="K23" t="n">
-        <v>98.78</v>
+        <v>-55.93</v>
       </c>
       <c r="L23" t="n">
-        <v>215.52</v>
+        <v>234.82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:42:47</t>
+          <t>07:43:46</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.31</v>
+        <v>3.73</v>
       </c>
       <c r="F24" t="n">
-        <v>10.89</v>
+        <v>5.57</v>
       </c>
       <c r="G24" t="n">
-        <v>26.9</v>
+        <v>19.4</v>
       </c>
       <c r="H24" t="n">
-        <v>70.5</v>
+        <v>57</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>130.77</v>
+        <v>-37.64</v>
       </c>
       <c r="K24" t="n">
-        <v>254.99</v>
+        <v>227.22</v>
       </c>
       <c r="L24" t="n">
-        <v>286.57</v>
+        <v>230.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:44:49</t>
+          <t>07:45:47</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.23</v>
+        <v>4.36</v>
       </c>
       <c r="F25" t="n">
-        <v>9.31</v>
+        <v>10.17</v>
       </c>
       <c r="G25" t="n">
-        <v>22.3</v>
+        <v>4.4</v>
       </c>
       <c r="H25" t="n">
-        <v>69.40000000000001</v>
+        <v>52.7</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>94.7</v>
+        <v>260.51</v>
       </c>
       <c r="K25" t="n">
-        <v>275.63</v>
+        <v>-50.58</v>
       </c>
       <c r="L25" t="n">
-        <v>291.45</v>
+        <v>265.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:49:16</t>
+          <t>07:50:55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>4.4</v>
+        <v>4.48</v>
       </c>
       <c r="F26" t="n">
-        <v>9.48</v>
+        <v>11.28</v>
       </c>
       <c r="G26" t="n">
-        <v>15.7</v>
+        <v>23</v>
       </c>
       <c r="H26" t="n">
-        <v>52.6</v>
+        <v>18</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J26" t="n">
-        <v>46.17</v>
+        <v>-103.5</v>
       </c>
       <c r="K26" t="n">
-        <v>292.38</v>
+        <v>-416.66</v>
       </c>
       <c r="L26" t="n">
-        <v>296.01</v>
+        <v>429.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:50:34</t>
+          <t>07:51:48</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.19</v>
+        <v>4.36</v>
       </c>
       <c r="F27" t="n">
-        <v>11.4</v>
+        <v>10.41</v>
       </c>
       <c r="G27" t="n">
-        <v>28.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>83</v>
+        <v>54.5</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J27" t="n">
-        <v>90.73</v>
+        <v>233.13</v>
       </c>
       <c r="K27" t="n">
-        <v>-80.12</v>
+        <v>232.71</v>
       </c>
       <c r="L27" t="n">
-        <v>121.04</v>
+        <v>329.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:53:15</t>
+          <t>07:53:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.57</v>
+        <v>4.95</v>
       </c>
       <c r="F28" t="n">
-        <v>10.44</v>
+        <v>13.11</v>
       </c>
       <c r="G28" t="n">
-        <v>13.9</v>
+        <v>10.5</v>
       </c>
       <c r="H28" t="n">
-        <v>73</v>
+        <v>60.2</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>64.87</v>
+        <v>17.23</v>
       </c>
       <c r="K28" t="n">
-        <v>332.89</v>
+        <v>-369.79</v>
       </c>
       <c r="L28" t="n">
-        <v>339.15</v>
+        <v>370.19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:03:33</t>
+          <t>08:05:43</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.7</v>
+        <v>3.97</v>
       </c>
       <c r="F29" t="n">
-        <v>7.19</v>
+        <v>12.56</v>
       </c>
       <c r="G29" t="n">
-        <v>23.3</v>
+        <v>13</v>
       </c>
       <c r="H29" t="n">
-        <v>84.3</v>
+        <v>63.5</v>
       </c>
       <c r="I29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.15</v>
+        <v>55.29</v>
       </c>
       <c r="K29" t="n">
-        <v>52.68</v>
+        <v>-19.4</v>
       </c>
       <c r="L29" t="n">
-        <v>52.72</v>
+        <v>58.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:05:59</t>
+          <t>08:06:39</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.62</v>
+        <v>3.96</v>
       </c>
       <c r="F30" t="n">
-        <v>8.85</v>
+        <v>8.42</v>
       </c>
       <c r="G30" t="n">
-        <v>20.6</v>
+        <v>27.3</v>
       </c>
       <c r="H30" t="n">
-        <v>52.5</v>
+        <v>53.3</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>-41.15</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>6.83</v>
+        <v>0.29</v>
       </c>
       <c r="L30" t="n">
-        <v>41.71</v>
+        <v>68.95999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:07:23</t>
+          <t>08:08:38</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.28</v>
+        <v>4.55</v>
       </c>
       <c r="F31" t="n">
-        <v>9.43</v>
+        <v>10.3</v>
       </c>
       <c r="G31" t="n">
-        <v>20</v>
+        <v>21.7</v>
       </c>
       <c r="H31" t="n">
-        <v>73.40000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.03</v>
+        <v>-11.87</v>
       </c>
       <c r="K31" t="n">
-        <v>65.64</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>68.34</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:11:41</t>
+          <t>08:13:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.37</v>
+        <v>4.27</v>
       </c>
       <c r="F32" t="n">
-        <v>10.01</v>
+        <v>11.74</v>
       </c>
       <c r="G32" t="n">
-        <v>21.8</v>
+        <v>19.5</v>
       </c>
       <c r="H32" t="n">
-        <v>99.40000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>-107.25</v>
+        <v>-94.29000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-31.7</v>
+        <v>67.3</v>
       </c>
       <c r="L32" t="n">
-        <v>111.83</v>
+        <v>115.84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:13:57</t>
+          <t>08:15:30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.64</v>
+        <v>4.37</v>
       </c>
       <c r="F33" t="n">
-        <v>13.11</v>
+        <v>9.74</v>
       </c>
       <c r="G33" t="n">
-        <v>27.8</v>
+        <v>31.5</v>
       </c>
       <c r="H33" t="n">
-        <v>38.4</v>
+        <v>36.8</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J33" t="n">
-        <v>57.46</v>
+        <v>51.95</v>
       </c>
       <c r="K33" t="n">
-        <v>63.69</v>
+        <v>92.12</v>
       </c>
       <c r="L33" t="n">
-        <v>85.78</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:15:49</t>
+          <t>08:18:08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.42</v>
+        <v>4.47</v>
       </c>
       <c r="F34" t="n">
-        <v>10.41</v>
+        <v>11.2</v>
       </c>
       <c r="G34" t="n">
-        <v>15.1</v>
+        <v>23.3</v>
       </c>
       <c r="H34" t="n">
-        <v>58</v>
+        <v>36.9</v>
       </c>
       <c r="I34" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>121.62</v>
+        <v>90.02</v>
       </c>
       <c r="K34" t="n">
-        <v>5.33</v>
+        <v>-81.47</v>
       </c>
       <c r="L34" t="n">
-        <v>121.74</v>
+        <v>121.41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:20:30</t>
+          <t>08:23:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.29</v>
+        <v>4.13</v>
       </c>
       <c r="F35" t="n">
-        <v>11.48</v>
+        <v>11.99</v>
       </c>
       <c r="G35" t="n">
-        <v>18.1</v>
+        <v>28.8</v>
       </c>
       <c r="H35" t="n">
-        <v>83.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-101.76</v>
+        <v>105.19</v>
       </c>
       <c r="K35" t="n">
-        <v>-80.77</v>
+        <v>62.37</v>
       </c>
       <c r="L35" t="n">
-        <v>129.91</v>
+        <v>122.29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:22:43</t>
+          <t>08:25:13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.09</v>
+        <v>4.67</v>
       </c>
       <c r="F36" t="n">
-        <v>12.53</v>
+        <v>11.85</v>
       </c>
       <c r="G36" t="n">
-        <v>24.3</v>
+        <v>32.1</v>
       </c>
       <c r="H36" t="n">
-        <v>69.2</v>
+        <v>81</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J36" t="n">
-        <v>29.35</v>
+        <v>-119.87</v>
       </c>
       <c r="K36" t="n">
-        <v>254.3</v>
+        <v>-159.08</v>
       </c>
       <c r="L36" t="n">
-        <v>255.99</v>
+        <v>199.19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:24:45</t>
+          <t>08:27:13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="F37" t="n">
-        <v>8.01</v>
+        <v>10.23</v>
       </c>
       <c r="G37" t="n">
-        <v>31.4</v>
+        <v>32</v>
       </c>
       <c r="H37" t="n">
-        <v>75.8</v>
+        <v>41.7</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-107.08</v>
+        <v>-34.81</v>
       </c>
       <c r="K37" t="n">
-        <v>68.41</v>
+        <v>36.68</v>
       </c>
       <c r="L37" t="n">
-        <v>127.07</v>
+        <v>50.57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:28:08</t>
+          <t>08:31:55</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.65</v>
+        <v>4.86</v>
       </c>
       <c r="F38" t="n">
-        <v>9.289999999999999</v>
+        <v>13.11</v>
       </c>
       <c r="G38" t="n">
-        <v>17.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>54.7</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.33</v>
+        <v>268.19</v>
       </c>
       <c r="K38" t="n">
-        <v>150.74</v>
+        <v>9</v>
       </c>
       <c r="L38" t="n">
-        <v>150.74</v>
+        <v>268.35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:29:19</t>
+          <t>08:33:11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.34</v>
+        <v>4.48</v>
       </c>
       <c r="F39" t="n">
-        <v>12.62</v>
+        <v>9.33</v>
       </c>
       <c r="G39" t="n">
-        <v>13.4</v>
+        <v>24.9</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>40.2</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>91.28</v>
+        <v>201.96</v>
       </c>
       <c r="K39" t="n">
-        <v>-232.58</v>
+        <v>-10.31</v>
       </c>
       <c r="L39" t="n">
-        <v>249.85</v>
+        <v>202.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:31:26</t>
+          <t>08:34:17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.51</v>
+        <v>4.84</v>
       </c>
       <c r="F40" t="n">
-        <v>11.25</v>
+        <v>11.27</v>
       </c>
       <c r="G40" t="n">
-        <v>19.6</v>
+        <v>5.4</v>
       </c>
       <c r="H40" t="n">
-        <v>79.09999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>81.04000000000001</v>
+        <v>-124.72</v>
       </c>
       <c r="K40" t="n">
-        <v>272.07</v>
+        <v>187.16</v>
       </c>
       <c r="L40" t="n">
-        <v>283.88</v>
+        <v>224.91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:35:56</t>
+          <t>08:38:09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.19</v>
+        <v>5.22</v>
       </c>
       <c r="F41" t="n">
-        <v>10.01</v>
+        <v>13.11</v>
       </c>
       <c r="G41" t="n">
-        <v>21.5</v>
+        <v>22.7</v>
       </c>
       <c r="H41" t="n">
-        <v>88.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>-300.1</v>
+        <v>-276.79</v>
       </c>
       <c r="K41" t="n">
-        <v>3.14</v>
+        <v>281.2</v>
       </c>
       <c r="L41" t="n">
-        <v>300.12</v>
+        <v>394.58</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:37:22</t>
+          <t>08:39:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.65</v>
+        <v>4.41</v>
       </c>
       <c r="F42" t="n">
-        <v>12.69</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>18.5</v>
+        <v>10.4</v>
       </c>
       <c r="H42" t="n">
-        <v>17.7</v>
+        <v>50.2</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J42" t="n">
-        <v>-287.05</v>
+        <v>-216.69</v>
       </c>
       <c r="K42" t="n">
-        <v>46.8</v>
+        <v>-60.43</v>
       </c>
       <c r="L42" t="n">
-        <v>290.84</v>
+        <v>224.96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:39:55</t>
+          <t>08:40:33</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.57</v>
+        <v>4.74</v>
       </c>
       <c r="F43" t="n">
-        <v>13.11</v>
+        <v>12.44</v>
       </c>
       <c r="G43" t="n">
-        <v>21.8</v>
+        <v>15.5</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>46.6</v>
       </c>
       <c r="I43" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>176.41</v>
+        <v>-245.83</v>
       </c>
       <c r="K43" t="n">
-        <v>264.37</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>317.82</v>
+        <v>264.49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:49:35</t>
+          <t>08:49:52</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.56</v>
+        <v>4.96</v>
       </c>
       <c r="F44" t="n">
-        <v>11.4</v>
+        <v>10.23</v>
       </c>
       <c r="G44" t="n">
-        <v>33.7</v>
+        <v>36.1</v>
       </c>
       <c r="H44" t="n">
-        <v>31.8</v>
+        <v>78.5</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>-45.02</v>
+        <v>84.13</v>
       </c>
       <c r="K44" t="n">
-        <v>67.98</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>81.54000000000001</v>
+        <v>122.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:52:08</t>
+          <t>08:51:18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.39</v>
+        <v>4.88</v>
       </c>
       <c r="F45" t="n">
-        <v>10.55</v>
+        <v>11.76</v>
       </c>
       <c r="G45" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="H45" t="n">
-        <v>61.1</v>
+        <v>48.6</v>
       </c>
       <c r="I45" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>64.02</v>
+        <v>38.84</v>
       </c>
       <c r="K45" t="n">
-        <v>-17.65</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>66.41</v>
+        <v>103.57</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:54:38</t>
+          <t>08:53:26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>4.74</v>
+        <v>4.36</v>
       </c>
       <c r="F46" t="n">
-        <v>12.8</v>
+        <v>11.17</v>
       </c>
       <c r="G46" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="H46" t="n">
-        <v>93.59999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>-23.11</v>
+        <v>-11.79</v>
       </c>
       <c r="K46" t="n">
-        <v>110.26</v>
+        <v>77.17</v>
       </c>
       <c r="L46" t="n">
-        <v>112.66</v>
+        <v>78.06</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:00:21</t>
+          <t>08:57:03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.73</v>
+        <v>3.89</v>
       </c>
       <c r="F47" t="n">
-        <v>11.59</v>
+        <v>9.91</v>
       </c>
       <c r="G47" t="n">
-        <v>12.3</v>
+        <v>20.5</v>
       </c>
       <c r="H47" t="n">
-        <v>52</v>
+        <v>65.2</v>
       </c>
       <c r="I47" t="n">
         <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>70.79000000000001</v>
+        <v>4.07</v>
       </c>
       <c r="K47" t="n">
-        <v>125.6</v>
+        <v>-80.33</v>
       </c>
       <c r="L47" t="n">
-        <v>144.18</v>
+        <v>80.44</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:01:33</t>
+          <t>08:59:20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.44</v>
+        <v>4.71</v>
       </c>
       <c r="F48" t="n">
-        <v>13.04</v>
+        <v>10.55</v>
       </c>
       <c r="G48" t="n">
-        <v>18.1</v>
+        <v>21</v>
       </c>
       <c r="H48" t="n">
-        <v>37.1</v>
+        <v>47.6</v>
       </c>
       <c r="I48" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>-103.45</v>
+        <v>-118.73</v>
       </c>
       <c r="K48" t="n">
-        <v>-26.86</v>
+        <v>-91.44</v>
       </c>
       <c r="L48" t="n">
-        <v>106.88</v>
+        <v>149.86</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:03:14</t>
+          <t>09:00:52</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>4.61</v>
+        <v>4.36</v>
       </c>
       <c r="F49" t="n">
-        <v>9.85</v>
+        <v>11.02</v>
       </c>
       <c r="G49" t="n">
-        <v>21</v>
+        <v>34.2</v>
       </c>
       <c r="H49" t="n">
-        <v>50.8</v>
+        <v>51.8</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>53.71</v>
+        <v>47.35</v>
       </c>
       <c r="K49" t="n">
-        <v>110.94</v>
+        <v>78.73</v>
       </c>
       <c r="L49" t="n">
-        <v>123.26</v>
+        <v>91.88</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:07:26</t>
+          <t>09:05:39</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>5.18</v>
+        <v>4.86</v>
       </c>
       <c r="F50" t="n">
-        <v>13.11</v>
+        <v>12.91</v>
       </c>
       <c r="G50" t="n">
-        <v>28.4</v>
+        <v>0.3</v>
       </c>
       <c r="H50" t="n">
-        <v>74.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J50" t="n">
-        <v>196.68</v>
+        <v>-162.8</v>
       </c>
       <c r="K50" t="n">
-        <v>-65.15000000000001</v>
+        <v>-171.19</v>
       </c>
       <c r="L50" t="n">
-        <v>207.19</v>
+        <v>236.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:08:29</t>
+          <t>09:07:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.83</v>
+        <v>4.89</v>
       </c>
       <c r="F51" t="n">
-        <v>10.94</v>
+        <v>12.54</v>
       </c>
       <c r="G51" t="n">
-        <v>28.2</v>
+        <v>17.7</v>
       </c>
       <c r="H51" t="n">
-        <v>62.4</v>
+        <v>55</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>101.99</v>
+        <v>-187.1</v>
       </c>
       <c r="K51" t="n">
-        <v>131.25</v>
+        <v>-100.72</v>
       </c>
       <c r="L51" t="n">
-        <v>166.21</v>
+        <v>212.49</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:10:19</t>
+          <t>09:09:42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.8</v>
+        <v>4.54</v>
       </c>
       <c r="F52" t="n">
-        <v>11.63</v>
+        <v>12.49</v>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>28.1</v>
       </c>
       <c r="H52" t="n">
-        <v>92.8</v>
+        <v>72.8</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J52" t="n">
-        <v>-71.95999999999999</v>
+        <v>160.33</v>
       </c>
       <c r="K52" t="n">
-        <v>-199.48</v>
+        <v>191.4</v>
       </c>
       <c r="L52" t="n">
-        <v>212.06</v>
+        <v>249.68</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:15:54</t>
+          <t>09:13:16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.26</v>
+        <v>4.01</v>
       </c>
       <c r="F53" t="n">
-        <v>9.49</v>
+        <v>12.92</v>
       </c>
       <c r="G53" t="n">
-        <v>23.7</v>
+        <v>22.2</v>
       </c>
       <c r="H53" t="n">
-        <v>82.8</v>
+        <v>60.1</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-225.37</v>
+        <v>-165.93</v>
       </c>
       <c r="K53" t="n">
-        <v>-79.55</v>
+        <v>-135.43</v>
       </c>
       <c r="L53" t="n">
-        <v>239</v>
+        <v>214.18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:16:38</t>
+          <t>09:14:51</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.13</v>
+        <v>4.63</v>
       </c>
       <c r="F54" t="n">
-        <v>10.51</v>
+        <v>12.65</v>
       </c>
       <c r="G54" t="n">
-        <v>14</v>
+        <v>20.6</v>
       </c>
       <c r="H54" t="n">
-        <v>30.4</v>
+        <v>29.5</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-142.32</v>
+        <v>218.45</v>
       </c>
       <c r="K54" t="n">
-        <v>-30.52</v>
+        <v>-221.3</v>
       </c>
       <c r="L54" t="n">
-        <v>145.56</v>
+        <v>310.96</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:18:05</t>
+          <t>09:16:49</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.37</v>
+        <v>3.94</v>
       </c>
       <c r="F55" t="n">
-        <v>12.14</v>
+        <v>10.82</v>
       </c>
       <c r="G55" t="n">
-        <v>4.9</v>
+        <v>16.4</v>
       </c>
       <c r="H55" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J55" t="n">
-        <v>-46.91</v>
+        <v>-14.03</v>
       </c>
       <c r="K55" t="n">
-        <v>108.39</v>
+        <v>269.22</v>
       </c>
       <c r="L55" t="n">
-        <v>118.1</v>
+        <v>269.58</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:21:35</t>
+          <t>09:20:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.6</v>
+        <v>5.16</v>
       </c>
       <c r="F56" t="n">
-        <v>11.62</v>
+        <v>12.98</v>
       </c>
       <c r="G56" t="n">
-        <v>40.1</v>
+        <v>13.4</v>
       </c>
       <c r="H56" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>-85.38</v>
+        <v>25.23</v>
       </c>
       <c r="K56" t="n">
-        <v>-250.32</v>
+        <v>-440.29</v>
       </c>
       <c r="L56" t="n">
-        <v>264.48</v>
+        <v>441.01</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:23:28</t>
+          <t>09:23:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.14</v>
+        <v>5.46</v>
       </c>
       <c r="F57" t="n">
         <v>13.11</v>
       </c>
       <c r="G57" t="n">
-        <v>20.5</v>
+        <v>5.7</v>
       </c>
       <c r="H57" t="n">
-        <v>72.7</v>
+        <v>61.7</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>240.57</v>
+        <v>22.26</v>
       </c>
       <c r="K57" t="n">
-        <v>-78.86</v>
+        <v>485.17</v>
       </c>
       <c r="L57" t="n">
-        <v>253.16</v>
+        <v>485.68</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:25:20</t>
+          <t>09:24:37</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.57</v>
+        <v>4.43</v>
       </c>
       <c r="F58" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="G58" t="n">
-        <v>18.6</v>
+        <v>29.8</v>
       </c>
       <c r="H58" t="n">
-        <v>28.6</v>
+        <v>55.2</v>
       </c>
       <c r="I58" t="n">
         <v>21</v>
       </c>
       <c r="J58" t="n">
-        <v>277.19</v>
+        <v>51.94</v>
       </c>
       <c r="K58" t="n">
-        <v>-168.36</v>
+        <v>355.07</v>
       </c>
       <c r="L58" t="n">
-        <v>324.31</v>
+        <v>358.85</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:35:49</t>
+          <t>09:34:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.94</v>
+        <v>4.37</v>
       </c>
       <c r="F59" t="n">
-        <v>12.17</v>
+        <v>12.69</v>
       </c>
       <c r="G59" t="n">
-        <v>13.8</v>
+        <v>18.5</v>
       </c>
       <c r="H59" t="n">
-        <v>57.4</v>
+        <v>17.7</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-73.65000000000001</v>
+        <v>-75.16</v>
       </c>
       <c r="K59" t="n">
-        <v>92.65000000000001</v>
+        <v>-10.73</v>
       </c>
       <c r="L59" t="n">
-        <v>118.35</v>
+        <v>75.92</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:36:44</t>
+          <t>09:37:10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>5.22</v>
+        <v>4.84</v>
       </c>
       <c r="F60" t="n">
         <v>13.11</v>
       </c>
       <c r="G60" t="n">
-        <v>11.1</v>
+        <v>35.7</v>
       </c>
       <c r="H60" t="n">
-        <v>81.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>-44.14</v>
+        <v>63.79</v>
       </c>
       <c r="K60" t="n">
-        <v>-83.98999999999999</v>
+        <v>-71.26000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>94.88</v>
+        <v>95.64</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:39:28</t>
+          <t>09:38:55</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.57</v>
+        <v>4.93</v>
       </c>
       <c r="F61" t="n">
         <v>13.11</v>
       </c>
       <c r="G61" t="n">
-        <v>13.5</v>
+        <v>18.3</v>
       </c>
       <c r="H61" t="n">
-        <v>56.8</v>
+        <v>31.9</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J61" t="n">
-        <v>60.75</v>
+        <v>19.5</v>
       </c>
       <c r="K61" t="n">
-        <v>-32.1</v>
+        <v>-95.44</v>
       </c>
       <c r="L61" t="n">
-        <v>68.70999999999999</v>
+        <v>97.41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:44:18</t>
+          <t>09:43:22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>5.33</v>
+        <v>4.93</v>
       </c>
       <c r="F62" t="n">
-        <v>13.11</v>
+        <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>17.1</v>
+        <v>16</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>56.8</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J62" t="n">
-        <v>-154.42</v>
+        <v>107.63</v>
       </c>
       <c r="K62" t="n">
-        <v>59.73</v>
+        <v>18.35</v>
       </c>
       <c r="L62" t="n">
-        <v>165.57</v>
+        <v>109.19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:45:24</t>
+          <t>09:45:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.77</v>
+        <v>4.62</v>
       </c>
       <c r="F63" t="n">
-        <v>10.75</v>
+        <v>12.17</v>
       </c>
       <c r="G63" t="n">
-        <v>16.7</v>
+        <v>23</v>
       </c>
       <c r="H63" t="n">
-        <v>54.4</v>
+        <v>71.8</v>
       </c>
       <c r="I63" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>36.57</v>
+        <v>-97.61</v>
       </c>
       <c r="K63" t="n">
-        <v>-130.01</v>
+        <v>-8.92</v>
       </c>
       <c r="L63" t="n">
-        <v>135.05</v>
+        <v>98.01000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:47:37</t>
+          <t>09:47:31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.82</v>
+        <v>4.96</v>
       </c>
       <c r="F64" t="n">
         <v>13.11</v>
       </c>
       <c r="G64" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="H64" t="n">
-        <v>59.3</v>
+        <v>71.2</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J64" t="n">
-        <v>102.25</v>
+        <v>-118.66</v>
       </c>
       <c r="K64" t="n">
-        <v>-183.76</v>
+        <v>-14.21</v>
       </c>
       <c r="L64" t="n">
-        <v>210.29</v>
+        <v>119.51</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:52:10</t>
+          <t>09:52:23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.77</v>
+        <v>4.74</v>
       </c>
       <c r="F65" t="n">
-        <v>12.67</v>
+        <v>13.01</v>
       </c>
       <c r="G65" t="n">
-        <v>22.3</v>
+        <v>14.3</v>
       </c>
       <c r="H65" t="n">
-        <v>44.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J65" t="n">
-        <v>-162.26</v>
+        <v>-85.55</v>
       </c>
       <c r="K65" t="n">
-        <v>153.91</v>
+        <v>-111.13</v>
       </c>
       <c r="L65" t="n">
-        <v>223.65</v>
+        <v>140.24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:54:09</t>
+          <t>09:54:33</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>4.58</v>
+        <v>4.89</v>
       </c>
       <c r="F66" t="n">
-        <v>9.859999999999999</v>
+        <v>12.87</v>
       </c>
       <c r="G66" t="n">
-        <v>12.4</v>
+        <v>1.9</v>
       </c>
       <c r="H66" t="n">
-        <v>37.1</v>
+        <v>52.2</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J66" t="n">
-        <v>155.32</v>
+        <v>-64.7</v>
       </c>
       <c r="K66" t="n">
-        <v>41.85</v>
+        <v>128.29</v>
       </c>
       <c r="L66" t="n">
-        <v>160.86</v>
+        <v>143.68</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:55:26</t>
+          <t>09:56:43</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.43</v>
+        <v>4.77</v>
       </c>
       <c r="F67" t="n">
-        <v>8.380000000000001</v>
+        <v>13.11</v>
       </c>
       <c r="G67" t="n">
-        <v>14.3</v>
+        <v>0.5</v>
       </c>
       <c r="H67" t="n">
-        <v>38.5</v>
+        <v>45.8</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>65.95</v>
+        <v>174.07</v>
       </c>
       <c r="K67" t="n">
-        <v>110.61</v>
+        <v>103.45</v>
       </c>
       <c r="L67" t="n">
-        <v>128.78</v>
+        <v>202.49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:58:59</t>
+          <t>10:01:31</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.6</v>
+        <v>4.44</v>
       </c>
       <c r="F68" t="n">
-        <v>11.07</v>
+        <v>12.04</v>
       </c>
       <c r="G68" t="n">
-        <v>17.7</v>
+        <v>25.4</v>
       </c>
       <c r="H68" t="n">
-        <v>78.5</v>
+        <v>53.2</v>
       </c>
       <c r="I68" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-242.68</v>
+        <v>-215.67</v>
       </c>
       <c r="K68" t="n">
-        <v>-46.62</v>
+        <v>20.47</v>
       </c>
       <c r="L68" t="n">
-        <v>247.12</v>
+        <v>216.64</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:00:46</t>
+          <t>10:02:29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.85</v>
+        <v>5.29</v>
       </c>
       <c r="F69" t="n">
-        <v>11.41</v>
+        <v>13.11</v>
       </c>
       <c r="G69" t="n">
-        <v>10.7</v>
+        <v>24.4</v>
       </c>
       <c r="H69" t="n">
-        <v>62.8</v>
+        <v>84.7</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J69" t="n">
-        <v>51.04</v>
+        <v>115.99</v>
       </c>
       <c r="K69" t="n">
-        <v>231.99</v>
+        <v>248.71</v>
       </c>
       <c r="L69" t="n">
-        <v>237.54</v>
+        <v>274.43</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:01:48</t>
+          <t>10:03:53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.42</v>
+        <v>5.06</v>
       </c>
       <c r="F70" t="n">
         <v>13.11</v>
       </c>
       <c r="G70" t="n">
-        <v>19.3</v>
+        <v>11.9</v>
       </c>
       <c r="H70" t="n">
-        <v>45.2</v>
+        <v>35.5</v>
       </c>
       <c r="I70" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-103.09</v>
+        <v>31.44</v>
       </c>
       <c r="K70" t="n">
-        <v>-271.3</v>
+        <v>327.87</v>
       </c>
       <c r="L70" t="n">
-        <v>290.23</v>
+        <v>329.37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:07:12</t>
+          <t>10:07:43</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.05</v>
+        <v>5.2</v>
       </c>
       <c r="F71" t="n">
-        <v>12.84</v>
+        <v>13.11</v>
       </c>
       <c r="G71" t="n">
-        <v>22.2</v>
+        <v>35.4</v>
       </c>
       <c r="H71" t="n">
-        <v>65.09999999999999</v>
+        <v>28.7</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J71" t="n">
-        <v>-271.42</v>
+        <v>100.9</v>
       </c>
       <c r="K71" t="n">
-        <v>160.72</v>
+        <v>312.42</v>
       </c>
       <c r="L71" t="n">
-        <v>315.44</v>
+        <v>328.32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:08:38</t>
+          <t>10:09:11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3067,28 +3067,28 @@
         <v>13.11</v>
       </c>
       <c r="G72" t="n">
-        <v>16.4</v>
+        <v>37.6</v>
       </c>
       <c r="H72" t="n">
-        <v>87.59999999999999</v>
+        <v>41.1</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>17.66</v>
+        <v>-310.3</v>
       </c>
       <c r="K72" t="n">
-        <v>376.53</v>
+        <v>-228.49</v>
       </c>
       <c r="L72" t="n">
-        <v>376.95</v>
+        <v>385.35</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:10:40</t>
+          <t>10:10:37</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.04</v>
+        <v>4.85</v>
       </c>
       <c r="F73" t="n">
-        <v>13.11</v>
+        <v>12.29</v>
       </c>
       <c r="G73" t="n">
-        <v>12.2</v>
+        <v>9.5</v>
       </c>
       <c r="H73" t="n">
-        <v>27.2</v>
+        <v>57.6</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J73" t="n">
-        <v>-293.11</v>
+        <v>-233.11</v>
       </c>
       <c r="K73" t="n">
-        <v>310.93</v>
+        <v>-243.71</v>
       </c>
       <c r="L73" t="n">
-        <v>427.31</v>
+        <v>337.25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:17:55</t>
+          <t>10:21:43</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>5.36</v>
+        <v>4.81</v>
       </c>
       <c r="F74" t="n">
-        <v>13.11</v>
+        <v>10.08</v>
       </c>
       <c r="G74" t="n">
-        <v>17.1</v>
+        <v>28.2</v>
       </c>
       <c r="H74" t="n">
-        <v>98.2</v>
+        <v>87.7</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-54.2</v>
+        <v>103.11</v>
       </c>
       <c r="K74" t="n">
-        <v>81.14</v>
+        <v>19.43</v>
       </c>
       <c r="L74" t="n">
-        <v>97.56999999999999</v>
+        <v>104.92</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:20:09</t>
+          <t>10:24:18</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="F75" t="n">
-        <v>12.41</v>
+        <v>11.86</v>
       </c>
       <c r="G75" t="n">
-        <v>11.2</v>
+        <v>6</v>
       </c>
       <c r="H75" t="n">
-        <v>15.2</v>
+        <v>31.5</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>24.95</v>
+        <v>3.06</v>
       </c>
       <c r="K75" t="n">
-        <v>49.91</v>
+        <v>105.04</v>
       </c>
       <c r="L75" t="n">
-        <v>55.8</v>
+        <v>105.09</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:21:03</t>
+          <t>10:25:21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.95</v>
+        <v>5.24</v>
       </c>
       <c r="F76" t="n">
-        <v>12.27</v>
+        <v>13.11</v>
       </c>
       <c r="G76" t="n">
-        <v>20.6</v>
+        <v>15.1</v>
       </c>
       <c r="H76" t="n">
-        <v>73.3</v>
+        <v>58.7</v>
       </c>
       <c r="I76" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-31.67</v>
+        <v>-58.02</v>
       </c>
       <c r="K76" t="n">
-        <v>87.08</v>
+        <v>15.88</v>
       </c>
       <c r="L76" t="n">
-        <v>92.66</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:24:56</t>
+          <t>10:30:41</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.82</v>
+        <v>5.09</v>
       </c>
       <c r="F77" t="n">
-        <v>12.12</v>
+        <v>13.11</v>
       </c>
       <c r="G77" t="n">
-        <v>20.8</v>
+        <v>14.2</v>
       </c>
       <c r="H77" t="n">
-        <v>81.8</v>
+        <v>66.5</v>
       </c>
       <c r="I77" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J77" t="n">
-        <v>94.13</v>
+        <v>132.87</v>
       </c>
       <c r="K77" t="n">
-        <v>66.78</v>
+        <v>-109.73</v>
       </c>
       <c r="L77" t="n">
-        <v>115.41</v>
+        <v>172.32</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:26:02</t>
+          <t>10:32:15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.41</v>
+        <v>5.57</v>
       </c>
       <c r="F78" t="n">
-        <v>12.74</v>
+        <v>13.11</v>
       </c>
       <c r="G78" t="n">
-        <v>27.8</v>
+        <v>9</v>
       </c>
       <c r="H78" t="n">
-        <v>82</v>
+        <v>77.2</v>
       </c>
       <c r="I78" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.98</v>
+        <v>-141.63</v>
       </c>
       <c r="K78" t="n">
-        <v>-115.98</v>
+        <v>-130.28</v>
       </c>
       <c r="L78" t="n">
-        <v>115.98</v>
+        <v>192.44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:27:54</t>
+          <t>10:34:24</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.57</v>
+        <v>5.47</v>
       </c>
       <c r="F79" t="n">
-        <v>11.16</v>
+        <v>12.69</v>
       </c>
       <c r="G79" t="n">
-        <v>9.6</v>
+        <v>25.6</v>
       </c>
       <c r="H79" t="n">
-        <v>62.6</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-89.59</v>
+        <v>107.92</v>
       </c>
       <c r="K79" t="n">
-        <v>26.94</v>
+        <v>121.75</v>
       </c>
       <c r="L79" t="n">
-        <v>93.55</v>
+        <v>162.69</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:31:37</t>
+          <t>10:40:05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3403,28 +3403,28 @@
         <v>13.11</v>
       </c>
       <c r="G80" t="n">
-        <v>11.5</v>
+        <v>14.8</v>
       </c>
       <c r="H80" t="n">
-        <v>62.3</v>
+        <v>50.2</v>
       </c>
       <c r="I80" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J80" t="n">
-        <v>171.94</v>
+        <v>144.36</v>
       </c>
       <c r="K80" t="n">
-        <v>161.84</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>236.13</v>
+        <v>158.25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:32:43</t>
+          <t>10:41:26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>5.2</v>
+        <v>4.95</v>
       </c>
       <c r="F81" t="n">
         <v>13.11</v>
       </c>
       <c r="G81" t="n">
-        <v>4.7</v>
+        <v>24.3</v>
       </c>
       <c r="H81" t="n">
-        <v>38.2</v>
+        <v>85.3</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-210.74</v>
+        <v>216.54</v>
       </c>
       <c r="K81" t="n">
-        <v>88.93000000000001</v>
+        <v>40.62</v>
       </c>
       <c r="L81" t="n">
-        <v>228.74</v>
+        <v>220.32</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:34:39</t>
+          <t>10:43:10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.79</v>
+        <v>4.81</v>
       </c>
       <c r="F82" t="n">
-        <v>11.45</v>
+        <v>9.27</v>
       </c>
       <c r="G82" t="n">
-        <v>10.6</v>
+        <v>28.8</v>
       </c>
       <c r="H82" t="n">
-        <v>21.8</v>
+        <v>55.1</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J82" t="n">
-        <v>36.08</v>
+        <v>-149.85</v>
       </c>
       <c r="K82" t="n">
-        <v>4.62</v>
+        <v>46.2</v>
       </c>
       <c r="L82" t="n">
-        <v>36.38</v>
+        <v>156.81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:40:19</t>
+          <t>10:48:01</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>5.27</v>
+        <v>5.83</v>
       </c>
       <c r="F83" t="n">
         <v>13.11</v>
       </c>
       <c r="G83" t="n">
-        <v>19.7</v>
+        <v>15.7</v>
       </c>
       <c r="H83" t="n">
-        <v>84.3</v>
+        <v>44.3</v>
       </c>
       <c r="I83" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>183.77</v>
+        <v>-207.24</v>
       </c>
       <c r="K83" t="n">
-        <v>-213.78</v>
+        <v>-201.42</v>
       </c>
       <c r="L83" t="n">
-        <v>281.91</v>
+        <v>289</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:41:16</t>
+          <t>10:50:31</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.61</v>
+        <v>5.03</v>
       </c>
       <c r="F84" t="n">
         <v>13.11</v>
       </c>
       <c r="G84" t="n">
-        <v>7.6</v>
+        <v>28.4</v>
       </c>
       <c r="H84" t="n">
-        <v>81.59999999999999</v>
+        <v>36</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>127.88</v>
+        <v>-67.98</v>
       </c>
       <c r="K84" t="n">
-        <v>164.15</v>
+        <v>-229.16</v>
       </c>
       <c r="L84" t="n">
-        <v>208.08</v>
+        <v>239.03</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:43:20</t>
+          <t>10:52:05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.51</v>
+        <v>4.69</v>
       </c>
       <c r="F85" t="n">
-        <v>11.31</v>
+        <v>12.25</v>
       </c>
       <c r="G85" t="n">
-        <v>24.3</v>
+        <v>12.6</v>
       </c>
       <c r="H85" t="n">
-        <v>58</v>
+        <v>44.2</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J85" t="n">
-        <v>262.71</v>
+        <v>-213.34</v>
       </c>
       <c r="K85" t="n">
-        <v>40.37</v>
+        <v>156.75</v>
       </c>
       <c r="L85" t="n">
-        <v>265.79</v>
+        <v>264.73</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:48:46</t>
+          <t>10:56:03</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>5.15</v>
+        <v>5.31</v>
       </c>
       <c r="F86" t="n">
-        <v>12.45</v>
+        <v>13.11</v>
       </c>
       <c r="G86" t="n">
-        <v>19.7</v>
+        <v>11.4</v>
       </c>
       <c r="H86" t="n">
-        <v>34.9</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>98.90000000000001</v>
+        <v>-73.02</v>
       </c>
       <c r="K86" t="n">
-        <v>287.35</v>
+        <v>315.93</v>
       </c>
       <c r="L86" t="n">
-        <v>303.89</v>
+        <v>324.26</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:50:43</t>
+          <t>10:57:51</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.73</v>
+        <v>5.38</v>
       </c>
       <c r="F87" t="n">
         <v>13.11</v>
       </c>
       <c r="G87" t="n">
-        <v>26.4</v>
+        <v>30</v>
       </c>
       <c r="H87" t="n">
-        <v>78.7</v>
+        <v>62</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J87" t="n">
-        <v>-139.68</v>
+        <v>-234.94</v>
       </c>
       <c r="K87" t="n">
-        <v>244.51</v>
+        <v>248.88</v>
       </c>
       <c r="L87" t="n">
-        <v>281.6</v>
+        <v>342.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:52:49</t>
+          <t>10:59:44</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.84</v>
+        <v>5.09</v>
       </c>
       <c r="F88" t="n">
         <v>13.11</v>
       </c>
       <c r="G88" t="n">
-        <v>19.1</v>
+        <v>6.9</v>
       </c>
       <c r="H88" t="n">
-        <v>89.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J88" t="n">
-        <v>136.73</v>
+        <v>378.45</v>
       </c>
       <c r="K88" t="n">
-        <v>247.76</v>
+        <v>17.25</v>
       </c>
       <c r="L88" t="n">
-        <v>282.98</v>
+        <v>378.84</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>49.56</v>
+        <v>61.92</v>
       </c>
       <c r="K14" t="n">
-        <v>12.53</v>
+        <v>15.65</v>
       </c>
       <c r="L14" t="n">
-        <v>51.12</v>
+        <v>63.86</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>78.08</v>
+        <v>85.62</v>
       </c>
       <c r="K15" t="n">
-        <v>-13.67</v>
+        <v>-14.99</v>
       </c>
       <c r="L15" t="n">
-        <v>79.26000000000001</v>
+        <v>86.92</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-60.02</v>
+        <v>-68.52</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.09</v>
+        <v>-4.67</v>
       </c>
       <c r="L16" t="n">
-        <v>60.16</v>
+        <v>68.68000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>26.34</v>
+        <v>32.03</v>
       </c>
       <c r="K17" t="n">
-        <v>-64.34999999999999</v>
+        <v>-78.26000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>69.53</v>
+        <v>84.56</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-54.78</v>
+        <v>-65.42</v>
       </c>
       <c r="K18" t="n">
-        <v>-38.7</v>
+        <v>-46.22</v>
       </c>
       <c r="L18" t="n">
-        <v>67.06999999999999</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>75.19</v>
+        <v>84.19</v>
       </c>
       <c r="K19" t="n">
-        <v>62.73</v>
+        <v>70.23</v>
       </c>
       <c r="L19" t="n">
-        <v>97.92</v>
+        <v>109.64</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-56.39</v>
+        <v>-69.28</v>
       </c>
       <c r="K20" t="n">
-        <v>-107.96</v>
+        <v>-132.66</v>
       </c>
       <c r="L20" t="n">
-        <v>121.8</v>
+        <v>149.66</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-112</v>
+        <v>-134.54</v>
       </c>
       <c r="K21" t="n">
-        <v>116.31</v>
+        <v>139.71</v>
       </c>
       <c r="L21" t="n">
-        <v>161.47</v>
+        <v>193.96</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-55.38</v>
+        <v>-65.06999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>113.1</v>
+        <v>132.89</v>
       </c>
       <c r="L22" t="n">
-        <v>125.93</v>
+        <v>147.97</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-145.89</v>
+        <v>-180.12</v>
       </c>
       <c r="K23" t="n">
-        <v>119.47</v>
+        <v>147.49</v>
       </c>
       <c r="L23" t="n">
-        <v>188.57</v>
+        <v>232.8</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>124.99</v>
+        <v>166.75</v>
       </c>
       <c r="K24" t="n">
-        <v>76.39</v>
+        <v>101.92</v>
       </c>
       <c r="L24" t="n">
-        <v>146.48</v>
+        <v>195.43</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-45.54</v>
+        <v>-59.85</v>
       </c>
       <c r="K25" t="n">
-        <v>130.21</v>
+        <v>171.12</v>
       </c>
       <c r="L25" t="n">
-        <v>137.95</v>
+        <v>181.29</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-222.09</v>
+        <v>-317.51</v>
       </c>
       <c r="K26" t="n">
-        <v>49.9</v>
+        <v>71.34</v>
       </c>
       <c r="L26" t="n">
-        <v>227.62</v>
+        <v>325.43</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>-123.25</v>
+        <v>-161.33</v>
       </c>
       <c r="K27" t="n">
-        <v>-227.96</v>
+        <v>-298.39</v>
       </c>
       <c r="L27" t="n">
-        <v>259.14</v>
+        <v>339.21</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-294.2</v>
+        <v>-391.01</v>
       </c>
       <c r="K28" t="n">
-        <v>112.69</v>
+        <v>149.77</v>
       </c>
       <c r="L28" t="n">
-        <v>315.05</v>
+        <v>418.71</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-59.34</v>
+        <v>-72.11</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.35</v>
+        <v>-0.42</v>
       </c>
       <c r="L29" t="n">
-        <v>59.34</v>
+        <v>72.11</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>55.24</v>
+        <v>68.08</v>
       </c>
       <c r="K30" t="n">
-        <v>-7.85</v>
+        <v>-9.67</v>
       </c>
       <c r="L30" t="n">
-        <v>55.79</v>
+        <v>68.76000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>78</v>
+        <v>86.28</v>
       </c>
       <c r="K31" t="n">
-        <v>19.9</v>
+        <v>22.02</v>
       </c>
       <c r="L31" t="n">
-        <v>80.5</v>
+        <v>89.04000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>20.54</v>
+        <v>25.04</v>
       </c>
       <c r="K32" t="n">
-        <v>-75.76000000000001</v>
+        <v>-92.34999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>78.48999999999999</v>
+        <v>95.69</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.74</v>
+        <v>-0.92</v>
       </c>
       <c r="K33" t="n">
-        <v>72.98999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>72.98999999999999</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-75.13</v>
+        <v>-90.20999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>19.47</v>
+        <v>23.38</v>
       </c>
       <c r="L34" t="n">
-        <v>77.61</v>
+        <v>93.19</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-71.86</v>
+        <v>-96.43000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>101.93</v>
+        <v>136.78</v>
       </c>
       <c r="L35" t="n">
-        <v>124.71</v>
+        <v>167.35</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-67.75</v>
+        <v>-85.95999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-85.91</v>
+        <v>-108.99</v>
       </c>
       <c r="L36" t="n">
-        <v>109.41</v>
+        <v>138.81</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>-73.23999999999999</v>
+        <v>-88.36</v>
       </c>
       <c r="K37" t="n">
-        <v>137.01</v>
+        <v>165.28</v>
       </c>
       <c r="L37" t="n">
-        <v>155.36</v>
+        <v>187.42</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-102.37</v>
+        <v>-129.77</v>
       </c>
       <c r="K38" t="n">
-        <v>141.42</v>
+        <v>179.27</v>
       </c>
       <c r="L38" t="n">
-        <v>174.58</v>
+        <v>221.31</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-267.71</v>
+        <v>-310.66</v>
       </c>
       <c r="K39" t="n">
-        <v>42.13</v>
+        <v>48.89</v>
       </c>
       <c r="L39" t="n">
-        <v>271.01</v>
+        <v>314.48</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>181.5</v>
+        <v>230.37</v>
       </c>
       <c r="K40" t="n">
-        <v>154.81</v>
+        <v>196.49</v>
       </c>
       <c r="L40" t="n">
-        <v>238.55</v>
+        <v>302.79</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>151.36</v>
+        <v>204.57</v>
       </c>
       <c r="K41" t="n">
-        <v>231.59</v>
+        <v>313.01</v>
       </c>
       <c r="L41" t="n">
-        <v>276.66</v>
+        <v>373.93</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>348.4</v>
+        <v>450.59</v>
       </c>
       <c r="K42" t="n">
-        <v>-174.42</v>
+        <v>-225.58</v>
       </c>
       <c r="L42" t="n">
-        <v>389.63</v>
+        <v>503.9</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>317.18</v>
+        <v>432.22</v>
       </c>
       <c r="K43" t="n">
-        <v>27.5</v>
+        <v>37.47</v>
       </c>
       <c r="L43" t="n">
-        <v>318.37</v>
+        <v>433.84</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>24.39</v>
+        <v>27.79</v>
       </c>
       <c r="K44" t="n">
-        <v>73.44</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>77.38</v>
+        <v>88.18000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>48.52</v>
+        <v>58.86</v>
       </c>
       <c r="K45" t="n">
-        <v>27.69</v>
+        <v>33.59</v>
       </c>
       <c r="L45" t="n">
-        <v>55.87</v>
+        <v>67.77</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>65.08</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-50.54</v>
+        <v>-56.8</v>
       </c>
       <c r="L46" t="n">
-        <v>82.40000000000001</v>
+        <v>92.61</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-99.47</v>
+        <v>-104.53</v>
       </c>
       <c r="K47" t="n">
-        <v>103.18</v>
+        <v>108.43</v>
       </c>
       <c r="L47" t="n">
-        <v>143.32</v>
+        <v>150.61</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>85.59999999999999</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>0.51</v>
+        <v>0.59</v>
       </c>
       <c r="L48" t="n">
-        <v>85.59999999999999</v>
+        <v>97.84999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>3.44</v>
+        <v>4.16</v>
       </c>
       <c r="K49" t="n">
-        <v>71.78</v>
+        <v>86.8</v>
       </c>
       <c r="L49" t="n">
-        <v>71.86</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>-89.8</v>
+        <v>-108.5</v>
       </c>
       <c r="K50" t="n">
-        <v>108.25</v>
+        <v>130.8</v>
       </c>
       <c r="L50" t="n">
-        <v>140.65</v>
+        <v>169.95</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>47.61</v>
+        <v>63.86</v>
       </c>
       <c r="K51" t="n">
-        <v>-96.64</v>
+        <v>-129.63</v>
       </c>
       <c r="L51" t="n">
-        <v>107.73</v>
+        <v>144.5</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-143.19</v>
+        <v>-172.17</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.43</v>
+        <v>-8.93</v>
       </c>
       <c r="L52" t="n">
-        <v>143.39</v>
+        <v>172.41</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-44.09</v>
+        <v>-65.12</v>
       </c>
       <c r="K53" t="n">
-        <v>-81.08</v>
+        <v>-119.75</v>
       </c>
       <c r="L53" t="n">
-        <v>92.3</v>
+        <v>136.3</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>-211.29</v>
+        <v>-291.22</v>
       </c>
       <c r="K54" t="n">
-        <v>-62.4</v>
+        <v>-86</v>
       </c>
       <c r="L54" t="n">
-        <v>220.31</v>
+        <v>303.65</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>179.63</v>
+        <v>232.99</v>
       </c>
       <c r="K55" t="n">
-        <v>131.19</v>
+        <v>170.16</v>
       </c>
       <c r="L55" t="n">
-        <v>222.44</v>
+        <v>288.51</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-69.68000000000001</v>
+        <v>-104.44</v>
       </c>
       <c r="K56" t="n">
-        <v>-168.83</v>
+        <v>-253.04</v>
       </c>
       <c r="L56" t="n">
-        <v>182.65</v>
+        <v>273.75</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>-394.31</v>
+        <v>-533.92</v>
       </c>
       <c r="K57" t="n">
-        <v>-20.36</v>
+        <v>-27.57</v>
       </c>
       <c r="L57" t="n">
-        <v>394.83</v>
+        <v>534.63</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.36</v>
+        <v>-6.83</v>
       </c>
       <c r="K58" t="n">
-        <v>-500.12</v>
+        <v>-636.88</v>
       </c>
       <c r="L58" t="n">
-        <v>500.15</v>
+        <v>636.91</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>33.52</v>
+        <v>40.82</v>
       </c>
       <c r="K59" t="n">
-        <v>-50.91</v>
+        <v>-62</v>
       </c>
       <c r="L59" t="n">
-        <v>60.96</v>
+        <v>74.23999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>69.53</v>
+        <v>79.22</v>
       </c>
       <c r="K60" t="n">
-        <v>18.59</v>
+        <v>21.18</v>
       </c>
       <c r="L60" t="n">
-        <v>71.97</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>56.5</v>
+        <v>67.95</v>
       </c>
       <c r="K61" t="n">
-        <v>-30.39</v>
+        <v>-36.55</v>
       </c>
       <c r="L61" t="n">
-        <v>64.15000000000001</v>
+        <v>77.16</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-65</v>
+        <v>-74.52</v>
       </c>
       <c r="K62" t="n">
-        <v>-46.42</v>
+        <v>-53.22</v>
       </c>
       <c r="L62" t="n">
-        <v>79.88</v>
+        <v>91.58</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>33.05</v>
+        <v>40.56</v>
       </c>
       <c r="K63" t="n">
-        <v>80.31</v>
+        <v>98.56</v>
       </c>
       <c r="L63" t="n">
-        <v>86.84</v>
+        <v>106.58</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>7.96</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>76.03</v>
+        <v>89.48</v>
       </c>
       <c r="L64" t="n">
-        <v>76.45</v>
+        <v>89.97</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>168.92</v>
+        <v>201.78</v>
       </c>
       <c r="K65" t="n">
-        <v>-54.04</v>
+        <v>-64.55</v>
       </c>
       <c r="L65" t="n">
-        <v>177.35</v>
+        <v>211.86</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-29.37</v>
+        <v>-36.92</v>
       </c>
       <c r="K66" t="n">
-        <v>-141.13</v>
+        <v>-177.45</v>
       </c>
       <c r="L66" t="n">
-        <v>144.16</v>
+        <v>181.25</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>-81.8</v>
+        <v>-111.83</v>
       </c>
       <c r="K67" t="n">
-        <v>39.01</v>
+        <v>53.33</v>
       </c>
       <c r="L67" t="n">
-        <v>90.63</v>
+        <v>123.9</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-72.28</v>
+        <v>-105.62</v>
       </c>
       <c r="K68" t="n">
-        <v>145.5</v>
+        <v>212.61</v>
       </c>
       <c r="L68" t="n">
-        <v>162.46</v>
+        <v>237.4</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>125.73</v>
+        <v>168.68</v>
       </c>
       <c r="K69" t="n">
-        <v>-125.19</v>
+        <v>-167.95</v>
       </c>
       <c r="L69" t="n">
-        <v>177.43</v>
+        <v>238.03</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>12.53</v>
+        <v>16.4</v>
       </c>
       <c r="K70" t="n">
-        <v>130.9</v>
+        <v>171.3</v>
       </c>
       <c r="L70" t="n">
-        <v>131.49</v>
+        <v>172.08</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>22.12</v>
+        <v>32.82</v>
       </c>
       <c r="K71" t="n">
-        <v>-173.33</v>
+        <v>-257.21</v>
       </c>
       <c r="L71" t="n">
-        <v>174.73</v>
+        <v>259.29</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>1.28</v>
+        <v>1.85</v>
       </c>
       <c r="K72" t="n">
-        <v>247.6</v>
+        <v>358.24</v>
       </c>
       <c r="L72" t="n">
-        <v>247.6</v>
+        <v>358.24</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>-278.78</v>
+        <v>-393.83</v>
       </c>
       <c r="K73" t="n">
-        <v>207.52</v>
+        <v>293.16</v>
       </c>
       <c r="L73" t="n">
-        <v>347.54</v>
+        <v>490.96</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-53.01</v>
+        <v>-66.95999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>-10.23</v>
+        <v>-12.91</v>
       </c>
       <c r="L74" t="n">
-        <v>53.99</v>
+        <v>68.19</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>79.02</v>
+        <v>89</v>
       </c>
       <c r="K75" t="n">
-        <v>37.23</v>
+        <v>41.93</v>
       </c>
       <c r="L75" t="n">
-        <v>87.34999999999999</v>
+        <v>98.38</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-65.01000000000001</v>
+        <v>-76.06999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>51.09</v>
+        <v>59.79</v>
       </c>
       <c r="L76" t="n">
-        <v>82.69</v>
+        <v>96.75</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>70.23999999999999</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-49.93</v>
+        <v>-60.25</v>
       </c>
       <c r="L77" t="n">
-        <v>86.18000000000001</v>
+        <v>103.99</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-82.42</v>
+        <v>-94.97</v>
       </c>
       <c r="K78" t="n">
-        <v>37.57</v>
+        <v>43.29</v>
       </c>
       <c r="L78" t="n">
-        <v>90.58</v>
+        <v>104.38</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-5.44</v>
+        <v>-6.92</v>
       </c>
       <c r="K79" t="n">
-        <v>-20.28</v>
+        <v>-25.82</v>
       </c>
       <c r="L79" t="n">
-        <v>21</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>185.84</v>
+        <v>234.15</v>
       </c>
       <c r="K80" t="n">
-        <v>-2.15</v>
+        <v>-2.71</v>
       </c>
       <c r="L80" t="n">
-        <v>185.85</v>
+        <v>234.17</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>149.64</v>
+        <v>198.55</v>
       </c>
       <c r="K81" t="n">
-        <v>-41.18</v>
+        <v>-54.65</v>
       </c>
       <c r="L81" t="n">
-        <v>155.2</v>
+        <v>205.93</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>0.84</v>
+        <v>1.05</v>
       </c>
       <c r="K82" t="n">
-        <v>-135.61</v>
+        <v>-170.56</v>
       </c>
       <c r="L82" t="n">
-        <v>135.61</v>
+        <v>170.56</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>21</v>
       </c>
       <c r="J83" t="n">
-        <v>153.72</v>
+        <v>217.32</v>
       </c>
       <c r="K83" t="n">
-        <v>-6.71</v>
+        <v>-9.49</v>
       </c>
       <c r="L83" t="n">
-        <v>153.86</v>
+        <v>217.53</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>175.57</v>
+        <v>246.84</v>
       </c>
       <c r="K84" t="n">
-        <v>-29.72</v>
+        <v>-41.78</v>
       </c>
       <c r="L84" t="n">
-        <v>178.07</v>
+        <v>250.35</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>140.74</v>
+        <v>178.29</v>
       </c>
       <c r="K85" t="n">
-        <v>-171.53</v>
+        <v>-217.29</v>
       </c>
       <c r="L85" t="n">
-        <v>221.87</v>
+        <v>281.07</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-234.45</v>
+        <v>-346.16</v>
       </c>
       <c r="K86" t="n">
-        <v>-138.64</v>
+        <v>-204.69</v>
       </c>
       <c r="L86" t="n">
-        <v>272.37</v>
+        <v>402.15</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>252.17</v>
+        <v>326</v>
       </c>
       <c r="K87" t="n">
-        <v>340.32</v>
+        <v>439.96</v>
       </c>
       <c r="L87" t="n">
-        <v>423.57</v>
+        <v>547.5700000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>225.08</v>
+        <v>302.26</v>
       </c>
       <c r="K88" t="n">
-        <v>266.25</v>
+        <v>357.55</v>
       </c>
       <c r="L88" t="n">
-        <v>348.64</v>
+        <v>468.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-30.xlsx
+++ b/output/2024-09-30.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>61.92</v>
+        <v>78.25</v>
       </c>
       <c r="K14" t="n">
-        <v>15.65</v>
+        <v>19.78</v>
       </c>
       <c r="L14" t="n">
-        <v>63.86</v>
+        <v>80.70999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>85.62</v>
+        <v>107.76</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.99</v>
+        <v>-18.86</v>
       </c>
       <c r="L15" t="n">
-        <v>86.92</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>-68.52</v>
+        <v>-81.11</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.67</v>
+        <v>-5.53</v>
       </c>
       <c r="L16" t="n">
-        <v>68.68000000000001</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>32.03</v>
+        <v>36.68</v>
       </c>
       <c r="K17" t="n">
-        <v>-78.26000000000001</v>
+        <v>-89.63</v>
       </c>
       <c r="L17" t="n">
-        <v>84.56</v>
+        <v>96.84</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-65.42</v>
+        <v>-73.67</v>
       </c>
       <c r="K18" t="n">
-        <v>-46.22</v>
+        <v>-52.05</v>
       </c>
       <c r="L18" t="n">
-        <v>80.09999999999999</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>84.19</v>
+        <v>102.72</v>
       </c>
       <c r="K19" t="n">
-        <v>70.23</v>
+        <v>85.69</v>
       </c>
       <c r="L19" t="n">
-        <v>109.64</v>
+        <v>133.77</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-72.11</v>
+        <v>-84.67</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.42</v>
+        <v>-0.49</v>
       </c>
       <c r="L29" t="n">
-        <v>72.11</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>68.08</v>
+        <v>95.5</v>
       </c>
       <c r="K30" t="n">
-        <v>-9.67</v>
+        <v>-13.56</v>
       </c>
       <c r="L30" t="n">
-        <v>68.76000000000001</v>
+        <v>96.45999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>24</v>
       </c>
       <c r="J31" t="n">
-        <v>86.28</v>
+        <v>107.72</v>
       </c>
       <c r="K31" t="n">
-        <v>22.02</v>
+        <v>27.49</v>
       </c>
       <c r="L31" t="n">
-        <v>89.04000000000001</v>
+        <v>111.17</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>20</v>
       </c>
       <c r="J32" t="n">
-        <v>25.04</v>
+        <v>30.74</v>
       </c>
       <c r="K32" t="n">
-        <v>-92.34999999999999</v>
+        <v>-113.38</v>
       </c>
       <c r="L32" t="n">
-        <v>95.69</v>
+        <v>117.47</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.92</v>
+        <v>-1.12</v>
       </c>
       <c r="K33" t="n">
-        <v>90.59999999999999</v>
+        <v>110.2</v>
       </c>
       <c r="L33" t="n">
-        <v>90.59999999999999</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-90.20999999999999</v>
+        <v>-111.44</v>
       </c>
       <c r="K34" t="n">
-        <v>23.38</v>
+        <v>28.88</v>
       </c>
       <c r="L34" t="n">
-        <v>93.19</v>
+        <v>115.12</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>27.79</v>
+        <v>36.8</v>
       </c>
       <c r="K44" t="n">
-        <v>83.68000000000001</v>
+        <v>110.81</v>
       </c>
       <c r="L44" t="n">
-        <v>88.18000000000001</v>
+        <v>116.76</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>58.86</v>
+        <v>82.08</v>
       </c>
       <c r="K45" t="n">
-        <v>33.59</v>
+        <v>46.85</v>
       </c>
       <c r="L45" t="n">
-        <v>67.77</v>
+        <v>94.51000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>73.15000000000001</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>-56.8</v>
+        <v>-77.04000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>92.61</v>
+        <v>125.61</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-104.53</v>
+        <v>-133.16</v>
       </c>
       <c r="K47" t="n">
-        <v>108.43</v>
+        <v>138.14</v>
       </c>
       <c r="L47" t="n">
-        <v>150.61</v>
+        <v>191.87</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>97.84999999999999</v>
+        <v>115.58</v>
       </c>
       <c r="K48" t="n">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>97.84999999999999</v>
+        <v>115.58</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>24</v>
       </c>
       <c r="J49" t="n">
-        <v>4.16</v>
+        <v>4.86</v>
       </c>
       <c r="K49" t="n">
-        <v>86.8</v>
+        <v>101.27</v>
       </c>
       <c r="L49" t="n">
-        <v>86.90000000000001</v>
+        <v>101.38</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>40.82</v>
+        <v>62.11</v>
       </c>
       <c r="K59" t="n">
-        <v>-62</v>
+        <v>-94.34</v>
       </c>
       <c r="L59" t="n">
-        <v>74.23999999999999</v>
+        <v>112.95</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>79.22</v>
+        <v>121.44</v>
       </c>
       <c r="K60" t="n">
-        <v>21.18</v>
+        <v>32.48</v>
       </c>
       <c r="L60" t="n">
-        <v>82</v>
+        <v>125.71</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>67.95</v>
+        <v>97.78</v>
       </c>
       <c r="K61" t="n">
-        <v>-36.55</v>
+        <v>-52.59</v>
       </c>
       <c r="L61" t="n">
-        <v>77.16</v>
+        <v>111.03</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>26</v>
       </c>
       <c r="J62" t="n">
-        <v>-74.52</v>
+        <v>-88.3</v>
       </c>
       <c r="K62" t="n">
-        <v>-53.22</v>
+        <v>-63.06</v>
       </c>
       <c r="L62" t="n">
-        <v>91.58</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>40.56</v>
+        <v>57.44</v>
       </c>
       <c r="K63" t="n">
-        <v>98.56</v>
+        <v>139.57</v>
       </c>
       <c r="L63" t="n">
-        <v>106.58</v>
+        <v>150.93</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>9.369999999999999</v>
+        <v>11.89</v>
       </c>
       <c r="K64" t="n">
-        <v>89.48</v>
+        <v>113.48</v>
       </c>
       <c r="L64" t="n">
-        <v>89.97</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-66.95999999999999</v>
+        <v>-109.93</v>
       </c>
       <c r="K74" t="n">
-        <v>-12.91</v>
+        <v>-21.2</v>
       </c>
       <c r="L74" t="n">
-        <v>68.19</v>
+        <v>111.95</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>89</v>
+        <v>122.4</v>
       </c>
       <c r="K75" t="n">
-        <v>41.93</v>
+        <v>57.67</v>
       </c>
       <c r="L75" t="n">
-        <v>98.38</v>
+        <v>135.3</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-76.06999999999999</v>
+        <v>-127.41</v>
       </c>
       <c r="K76" t="n">
-        <v>59.79</v>
+        <v>100.13</v>
       </c>
       <c r="L76" t="n">
-        <v>96.75</v>
+        <v>162.04</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>84.76000000000001</v>
+        <v>115.45</v>
       </c>
       <c r="K77" t="n">
-        <v>-60.25</v>
+        <v>-82.06999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>103.99</v>
+        <v>141.65</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-94.97</v>
+        <v>-128.21</v>
       </c>
       <c r="K78" t="n">
-        <v>43.29</v>
+        <v>58.44</v>
       </c>
       <c r="L78" t="n">
-        <v>104.38</v>
+        <v>140.9</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.92</v>
+        <v>-9.4</v>
       </c>
       <c r="K79" t="n">
-        <v>-25.82</v>
+        <v>-35.07</v>
       </c>
       <c r="L79" t="n">
-        <v>26.73</v>
+        <v>36.31</v>
       </c>
     </row>
     <row r="80">
